--- a/research/traditional_assets/database/data/portugal/portugal_utility_general.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_utility_general.xlsx
@@ -650,10 +650,10 @@
         <v>0.09685383300626701</v>
       </c>
       <c r="X2">
-        <v>0.110766809164019</v>
+        <v>0.1107448149612621</v>
       </c>
       <c r="Y2">
-        <v>-0.013912976157752</v>
+        <v>-0.01389098195499508</v>
       </c>
       <c r="Z2">
         <v>0.2575667373133617</v>
@@ -662,10 +662,10 @@
         <v>0.04615546004729916</v>
       </c>
       <c r="AB2">
-        <v>0.07456185830662976</v>
+        <v>0.07455415391410755</v>
       </c>
       <c r="AC2">
-        <v>-0.0284063982593306</v>
+        <v>-0.02839869386680839</v>
       </c>
       <c r="AD2">
         <v>2904</v>
@@ -787,10 +787,10 @@
         <v>0.09685383300626701</v>
       </c>
       <c r="X3">
-        <v>0.110766809164019</v>
+        <v>0.1107448149612621</v>
       </c>
       <c r="Y3">
-        <v>-0.013912976157752</v>
+        <v>-0.01389098195499508</v>
       </c>
       <c r="Z3">
         <v>0.2575667373133617</v>
@@ -799,10 +799,10 @@
         <v>0.04615546004729916</v>
       </c>
       <c r="AB3">
-        <v>0.07456185830662976</v>
+        <v>0.07455415391410755</v>
       </c>
       <c r="AC3">
-        <v>-0.0284063982593306</v>
+        <v>-0.02839869386680839</v>
       </c>
       <c r="AD3">
         <v>2904</v>
@@ -1139,7 +1139,7 @@
         <v>2.69767441860465</v>
       </c>
       <c r="F2">
-        <v>13.2138189180076</v>
+        <v>13.5113641074059</v>
       </c>
       <c r="G2">
         <v>5.50521327014218</v>
@@ -1157,13 +1157,13 @@
         <v>1565.7</v>
       </c>
       <c r="L2">
-        <v>4135.25972183798</v>
+        <v>4140.37740096278</v>
       </c>
       <c r="M2">
         <v>4436.9</v>
       </c>
       <c r="N2">
-        <v>4549.42972183798</v>
+        <v>4554.54740096278</v>
       </c>
       <c r="O2">
         <v>2904</v>
@@ -1172,16 +1172,16 @@
         <v>446.97</v>
       </c>
       <c r="Q2">
-        <v>0.0745618583066298</v>
+        <v>0.07455415391410759</v>
       </c>
       <c r="R2">
-        <v>0.0720417817648879</v>
+        <v>0.07192244746870401</v>
       </c>
       <c r="S2">
         <v>0.0550418543268039</v>
       </c>
       <c r="T2">
-        <v>0.0502228543268039</v>
+        <v>0.0491168543268039</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.110766809164019</v>
+        <v>0.110744814961262</v>
       </c>
       <c r="X2">
-        <v>0.0744661070357861</v>
+        <v>0.07445640226224851</v>
       </c>
       <c r="Y2">
         <v>1.09506288137144</v>
@@ -1236,7 +1236,7 @@
         <v>1565.7</v>
       </c>
       <c r="AK2">
-        <v>0.05932701242019611</v>
+        <v>0.05930692754367341</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07215290738734166</v>
+        <v>0.07214398573648993</v>
       </c>
       <c r="C2">
-        <v>4577.147429916611</v>
+        <v>4577.203828750798</v>
       </c>
       <c r="D2">
-        <v>4544.347429916611</v>
+        <v>4544.403828750797</v>
       </c>
       <c r="E2">
         <v>-2904</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07215290738734166</v>
+        <v>0.07214398573648993</v>
       </c>
       <c r="T2">
         <v>0.4441974458563937</v>
       </c>
       <c r="U2">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V2">
         <v>0.21</v>
       </c>
       <c r="W2">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07214179482509628</v>
+        <v>0.07212183190971135</v>
       </c>
       <c r="C3">
-        <v>4532.958148070646</v>
+        <v>4533.519152323604</v>
       </c>
       <c r="D3">
-        <v>4544.855148070646</v>
+        <v>4545.416152323604</v>
       </c>
       <c r="E3">
         <v>-2859.303</v>
@@ -1539,37 +1539,37 @@
         <v>375.475</v>
       </c>
       <c r="M3">
-        <v>2.841532809930573</v>
+        <v>2.778957009930573</v>
       </c>
       <c r="N3">
-        <v>372.6334671900694</v>
+        <v>372.6960429900694</v>
       </c>
       <c r="O3">
-        <v>78.25302810991458</v>
+        <v>78.26616902791457</v>
       </c>
       <c r="P3">
-        <v>294.3804390801549</v>
+        <v>294.4298739621548</v>
       </c>
       <c r="Q3">
-        <v>578.2804390801548</v>
+        <v>578.3298739621548</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07236319826447297</v>
+        <v>0.0723542054206498</v>
       </c>
       <c r="T3">
         <v>0.4477420517374699</v>
       </c>
       <c r="U3">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V3">
         <v>0.21</v>
       </c>
       <c r="W3">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>132.1381891800764</v>
+        <v>135.1136410740591</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07213068226285091</v>
+        <v>0.07209967808293276</v>
       </c>
       <c r="C4">
-        <v>4488.768979687188</v>
+        <v>4489.834927012726</v>
       </c>
       <c r="D4">
-        <v>4545.362979687188</v>
+        <v>4546.428927012726</v>
       </c>
       <c r="E4">
         <v>-2814.606</v>
@@ -1621,37 +1621,37 @@
         <v>375.475</v>
       </c>
       <c r="M4">
-        <v>5.683065619861146</v>
+        <v>5.557914019861147</v>
       </c>
       <c r="N4">
-        <v>369.7919343801389</v>
+        <v>369.9170859801389</v>
       </c>
       <c r="O4">
-        <v>77.65630621982916</v>
+        <v>77.68258805582917</v>
       </c>
       <c r="P4">
-        <v>292.1356281603097</v>
+        <v>292.2344979243097</v>
       </c>
       <c r="Q4">
-        <v>576.0356281603097</v>
+        <v>576.1344979243097</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07257778079215799</v>
+        <v>0.07256871530244559</v>
       </c>
       <c r="T4">
         <v>0.4513589965140785</v>
       </c>
       <c r="U4">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V4">
         <v>0.21</v>
       </c>
       <c r="W4">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>66.06909459003818</v>
+        <v>67.55682053702957</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07211956970060553</v>
+        <v>0.07207752425615416</v>
       </c>
       <c r="C5">
-        <v>4444.579924804278</v>
+        <v>4446.151153119772</v>
       </c>
       <c r="D5">
-        <v>4545.870924804278</v>
+        <v>4547.442153119772</v>
       </c>
       <c r="E5">
         <v>-2769.909</v>
@@ -1703,37 +1703,37 @@
         <v>375.475</v>
       </c>
       <c r="M5">
-        <v>8.52459842979172</v>
+        <v>8.33687102979172</v>
       </c>
       <c r="N5">
-        <v>366.9504015702083</v>
+        <v>367.1381289702083</v>
       </c>
       <c r="O5">
-        <v>77.05958432974374</v>
+        <v>77.09900708374374</v>
       </c>
       <c r="P5">
-        <v>289.8908172404646</v>
+        <v>290.0391218864646</v>
       </c>
       <c r="Q5">
-        <v>573.7908172404645</v>
+        <v>573.9391218864646</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07279678770185712</v>
+        <v>0.07278764806840211</v>
       </c>
       <c r="T5">
         <v>0.4550505174716478</v>
       </c>
       <c r="U5">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V5">
         <v>0.21</v>
       </c>
       <c r="W5">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.04606306002545</v>
+        <v>45.03788035801971</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07210845713836013</v>
+        <v>0.07205537042937557</v>
       </c>
       <c r="C6">
-        <v>4400.390983459969</v>
+        <v>4402.467830946624</v>
       </c>
       <c r="D6">
-        <v>4546.378983459968</v>
+        <v>4548.455830946623</v>
       </c>
       <c r="E6">
         <v>-2725.212</v>
@@ -1785,37 +1785,37 @@
         <v>375.475</v>
       </c>
       <c r="M6">
-        <v>11.36613123972229</v>
+        <v>11.11582803972229</v>
       </c>
       <c r="N6">
-        <v>364.1088687602777</v>
+        <v>364.3591719602777</v>
       </c>
       <c r="O6">
-        <v>76.46286243965832</v>
+        <v>76.51542611165831</v>
       </c>
       <c r="P6">
-        <v>287.6460063206194</v>
+        <v>287.8437458486194</v>
       </c>
       <c r="Q6">
-        <v>571.5460063206194</v>
+        <v>571.7437458486194</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07302035725550832</v>
+        <v>0.0730111419336494</v>
       </c>
       <c r="T6">
         <v>0.4588189451158333</v>
       </c>
       <c r="U6">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V6">
         <v>0.21</v>
       </c>
       <c r="W6">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.03454729501909</v>
+        <v>33.77841026851478</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07209734457611477</v>
+        <v>0.07203321660259698</v>
       </c>
       <c r="C7">
-        <v>4356.202155692332</v>
+        <v>4358.784960795425</v>
       </c>
       <c r="D7">
-        <v>4546.887155692331</v>
+        <v>4549.469960795424</v>
       </c>
       <c r="E7">
         <v>-2680.515</v>
@@ -1867,37 +1867,37 @@
         <v>375.475</v>
       </c>
       <c r="M7">
-        <v>14.20766404965287</v>
+        <v>13.89478504965287</v>
       </c>
       <c r="N7">
-        <v>361.2673359503472</v>
+        <v>361.5802149503472</v>
       </c>
       <c r="O7">
-        <v>75.8661405495729</v>
+        <v>75.9318451395729</v>
       </c>
       <c r="P7">
-        <v>285.4011954007743</v>
+        <v>285.6483698107743</v>
       </c>
       <c r="Q7">
-        <v>569.3011954007743</v>
+        <v>569.5483698107743</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07324863353660482</v>
+        <v>0.07323934093290188</v>
       </c>
       <c r="T7">
         <v>0.4626667080788438</v>
       </c>
       <c r="U7">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V7">
         <v>0.21</v>
       </c>
       <c r="W7">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.42763783601527</v>
+        <v>27.02272821481182</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07208623201386939</v>
+        <v>0.0720110627758184</v>
       </c>
       <c r="C8">
-        <v>4312.01344153946</v>
+        <v>4315.102542968596</v>
       </c>
       <c r="D8">
-        <v>4547.395441539459</v>
+        <v>4550.484542968596</v>
       </c>
       <c r="E8">
         <v>-2635.818</v>
@@ -1949,37 +1949,37 @@
         <v>375.475</v>
       </c>
       <c r="M8">
-        <v>17.04919685958344</v>
+        <v>16.67374205958344</v>
       </c>
       <c r="N8">
-        <v>358.4258031404166</v>
+        <v>358.8012579404166</v>
       </c>
       <c r="O8">
-        <v>75.26941865948749</v>
+        <v>75.34826416748747</v>
       </c>
       <c r="P8">
-        <v>283.1563844809291</v>
+        <v>283.4529937729291</v>
       </c>
       <c r="Q8">
-        <v>567.0563844809291</v>
+        <v>567.352993772929</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.0734817667598523</v>
+        <v>0.07347239523001081</v>
       </c>
       <c r="T8">
         <v>0.4665963383389395</v>
       </c>
       <c r="U8">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V8">
         <v>0.21</v>
       </c>
       <c r="W8">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.02303153001273</v>
+        <v>22.51894017900985</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07207511945162401</v>
+        <v>0.07198890894903981</v>
       </c>
       <c r="C9">
-        <v>4267.824841039456</v>
+        <v>4271.420577768824</v>
       </c>
       <c r="D9">
-        <v>4547.903841039456</v>
+        <v>4551.499577768824</v>
       </c>
       <c r="E9">
         <v>-2591.121</v>
@@ -2031,37 +2031,37 @@
         <v>375.475</v>
       </c>
       <c r="M9">
-        <v>19.89072966951402</v>
+        <v>19.45269906951401</v>
       </c>
       <c r="N9">
-        <v>355.584270330486</v>
+        <v>356.022300930486</v>
       </c>
       <c r="O9">
-        <v>74.67269676940205</v>
+        <v>74.76468319540206</v>
       </c>
       <c r="P9">
-        <v>280.911573561084</v>
+        <v>281.257617735084</v>
       </c>
       <c r="Q9">
-        <v>564.8115735610839</v>
+        <v>565.1576177350839</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07371991360080402</v>
+        <v>0.07371046144748768</v>
       </c>
       <c r="T9">
         <v>0.4706104767766718</v>
       </c>
       <c r="U9">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V9">
         <v>0.21</v>
       </c>
       <c r="W9">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.87688416858233</v>
+        <v>19.30194872486559</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07206400688937863</v>
+        <v>0.07196675512226121</v>
       </c>
       <c r="C10">
-        <v>4223.636354230445</v>
+        <v>4227.739065499068</v>
       </c>
       <c r="D10">
-        <v>4548.412354230445</v>
+        <v>4552.515065499068</v>
       </c>
       <c r="E10">
         <v>-2546.424</v>
@@ -2113,37 +2113,37 @@
         <v>375.475</v>
       </c>
       <c r="M10">
-        <v>22.73226247944459</v>
+        <v>22.23165607944459</v>
       </c>
       <c r="N10">
-        <v>352.7427375205555</v>
+        <v>353.2433439205554</v>
       </c>
       <c r="O10">
-        <v>74.07597487931665</v>
+        <v>74.18110222331664</v>
       </c>
       <c r="P10">
-        <v>278.6667626412388</v>
+        <v>279.0622416972388</v>
       </c>
       <c r="Q10">
-        <v>562.5667626412388</v>
+        <v>562.9622416972388</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07396323754699383</v>
+        <v>0.07395370301751837</v>
       </c>
       <c r="T10">
         <v>0.4747118790934851</v>
       </c>
       <c r="U10">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V10">
         <v>0.21</v>
       </c>
       <c r="W10">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.51727364750955</v>
+        <v>16.88920513425739</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07205289432713324</v>
+        <v>0.07194460129548262</v>
       </c>
       <c r="C11">
-        <v>4179.447981150569</v>
+        <v>4184.058006462554</v>
       </c>
       <c r="D11">
-        <v>4548.920981150569</v>
+        <v>4553.531006462554</v>
       </c>
       <c r="E11">
         <v>-2501.727</v>
@@ -2195,37 +2195,37 @@
         <v>375.475</v>
       </c>
       <c r="M11">
-        <v>25.57379528937516</v>
+        <v>25.01061308937516</v>
       </c>
       <c r="N11">
-        <v>349.9012047106249</v>
+        <v>350.4643869106249</v>
       </c>
       <c r="O11">
-        <v>73.47925298923123</v>
+        <v>73.59752125123121</v>
       </c>
       <c r="P11">
-        <v>276.4219517213937</v>
+        <v>276.8668656593936</v>
       </c>
       <c r="Q11">
-        <v>560.3219517213936</v>
+        <v>560.7668656593936</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07421190927222077</v>
+        <v>0.07420229055612118</v>
       </c>
       <c r="T11">
         <v>0.4789034221205581</v>
       </c>
       <c r="U11">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V11">
         <v>0.21</v>
       </c>
       <c r="W11">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.68202102000848</v>
+        <v>15.01262678600657</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07204178176488789</v>
+        <v>0.07192244746870403</v>
       </c>
       <c r="C12">
-        <v>4135.259721837981</v>
+        <v>4140.377400962781</v>
       </c>
       <c r="D12">
-        <v>4549.429721837982</v>
+        <v>4554.547400962781</v>
       </c>
       <c r="E12">
         <v>-2457.03</v>
@@ -2277,37 +2277,37 @@
         <v>375.475</v>
       </c>
       <c r="M12">
-        <v>28.41532809930574</v>
+        <v>27.78957009930573</v>
       </c>
       <c r="N12">
-        <v>347.0596719006943</v>
+        <v>347.6854299006943</v>
       </c>
       <c r="O12">
-        <v>72.88253109914579</v>
+        <v>73.0139402791458</v>
       </c>
       <c r="P12">
-        <v>274.1771408015485</v>
+        <v>274.6714896215485</v>
       </c>
       <c r="Q12">
-        <v>558.0771408015485</v>
+        <v>558.5714896215485</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.0744661070357861</v>
+        <v>0.07445640226224849</v>
       </c>
       <c r="T12">
         <v>0.4831881105482327</v>
       </c>
       <c r="U12">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V12">
         <v>0.21</v>
       </c>
       <c r="W12">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>13.21381891800763</v>
+        <v>13.51136410740591</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07212625920264248</v>
+        <v>0.07203064364192546</v>
       </c>
       <c r="C13">
-        <v>4086.698140148492</v>
+        <v>4090.720771844698</v>
       </c>
       <c r="D13">
-        <v>4545.565140148492</v>
+        <v>4549.587771844698</v>
       </c>
       <c r="E13">
         <v>-2412.333</v>
@@ -2359,37 +2359,37 @@
         <v>375.475</v>
       </c>
       <c r="M13">
-        <v>31.7976946092363</v>
+        <v>31.3060276092363</v>
       </c>
       <c r="N13">
-        <v>343.6773053907637</v>
+        <v>344.1689723907637</v>
       </c>
       <c r="O13">
-        <v>72.17223413206038</v>
+        <v>72.27548420206038</v>
       </c>
       <c r="P13">
-        <v>271.5050712587033</v>
+        <v>271.8934881887033</v>
       </c>
       <c r="Q13">
-        <v>555.4050712587033</v>
+        <v>555.7934881887033</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07472601710864502</v>
+        <v>0.07471622434379441</v>
       </c>
       <c r="T13">
         <v>0.4875690841091134</v>
       </c>
       <c r="U13">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V13">
         <v>0.21</v>
       </c>
       <c r="W13">
-        <v>0.05109185432680387</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.80824599437896</v>
+        <v>11.99369669913735</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07212383664039711</v>
+        <v>0.07202033981514686</v>
       </c>
       <c r="C14">
-        <v>4042.111873439731</v>
+        <v>4046.495625920883</v>
       </c>
       <c r="D14">
-        <v>4545.675873439731</v>
+        <v>4550.059625920882</v>
       </c>
       <c r="E14">
         <v>-2367.636</v>
@@ -2441,37 +2441,37 @@
         <v>375.475</v>
       </c>
       <c r="M14">
-        <v>34.68839411916687</v>
+        <v>34.15203011916687</v>
       </c>
       <c r="N14">
-        <v>340.7866058808331</v>
+        <v>341.3229698808332</v>
       </c>
       <c r="O14">
-        <v>71.56518723497496</v>
+        <v>71.67782367497496</v>
       </c>
       <c r="P14">
-        <v>269.2214186458582</v>
+        <v>269.6451462058582</v>
       </c>
       <c r="Q14">
-        <v>553.1214186458582</v>
+        <v>553.5451462058581</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07499183422861437</v>
+        <v>0.07498195147264816</v>
       </c>
       <c r="T14">
         <v>0.4920496252509234</v>
       </c>
       <c r="U14">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V14">
         <v>0.21</v>
       </c>
       <c r="W14">
-        <v>0.05109185432680387</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.82422549484738</v>
+        <v>10.99422197420924</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07212141407815173</v>
+        <v>0.07201003598836826</v>
       </c>
       <c r="C15">
-        <v>3997.525612126189</v>
+        <v>4002.270577882578</v>
       </c>
       <c r="D15">
-        <v>4545.786612126189</v>
+        <v>4550.531577882578</v>
       </c>
       <c r="E15">
         <v>-2322.939</v>
@@ -2523,37 +2523,37 @@
         <v>375.475</v>
       </c>
       <c r="M15">
-        <v>37.57909362909745</v>
+        <v>36.99803262909745</v>
       </c>
       <c r="N15">
-        <v>337.8959063709026</v>
+        <v>338.4769673709026</v>
       </c>
       <c r="O15">
-        <v>70.95814033788955</v>
+        <v>71.08016314788954</v>
       </c>
       <c r="P15">
-        <v>266.9377660330131</v>
+        <v>267.396804223013</v>
       </c>
       <c r="Q15">
-        <v>550.8377660330131</v>
+        <v>551.2968042230129</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07526376208697383</v>
+        <v>0.07525378727113076</v>
       </c>
       <c r="T15">
         <v>0.496633167338522</v>
       </c>
       <c r="U15">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V15">
         <v>0.21</v>
       </c>
       <c r="W15">
-        <v>0.05109185432680387</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.991592764474506</v>
+        <v>10.14851259157775</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07236231151590637</v>
+        <v>0.07218775216158967</v>
       </c>
       <c r="C16">
-        <v>3941.843199068454</v>
+        <v>3949.44723790609</v>
       </c>
       <c r="D16">
-        <v>4534.801199068454</v>
+        <v>4542.405237906089</v>
       </c>
       <c r="E16">
         <v>-2278.242</v>
@@ -2605,37 +2605,37 @@
         <v>375.475</v>
       </c>
       <c r="M16">
-        <v>41.84646073902802</v>
+        <v>40.90782373902803</v>
       </c>
       <c r="N16">
-        <v>333.628539260972</v>
+        <v>334.567176260972</v>
       </c>
       <c r="O16">
-        <v>70.06199324480411</v>
+        <v>70.25910701480412</v>
       </c>
       <c r="P16">
-        <v>263.5665460161679</v>
+        <v>264.3080692461679</v>
       </c>
       <c r="Q16">
-        <v>547.4665460161679</v>
+        <v>548.208069246168</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07554201384901607</v>
+        <v>0.07553194483236876</v>
       </c>
       <c r="T16">
         <v>0.5013233034281579</v>
       </c>
       <c r="U16">
-        <v>0.0668732333250682</v>
+        <v>0.0653732333250682</v>
       </c>
       <c r="V16">
         <v>0.21</v>
       </c>
       <c r="W16">
-        <v>0.05282985432680388</v>
+        <v>0.05164485432680388</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.972682357574243</v>
+        <v>9.178562086200124</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07237726895366098</v>
+        <v>0.07219087833481108</v>
       </c>
       <c r="C17">
-        <v>3896.465859920444</v>
+        <v>3904.607548682688</v>
       </c>
       <c r="D17">
-        <v>4534.120859920444</v>
+        <v>4542.262548682687</v>
       </c>
       <c r="E17">
         <v>-2233.545</v>
@@ -2687,37 +2687,37 @@
         <v>375.475</v>
       </c>
       <c r="M17">
-        <v>44.8354936489586</v>
+        <v>43.82981114895859</v>
       </c>
       <c r="N17">
-        <v>330.6395063510414</v>
+        <v>331.6451888510414</v>
       </c>
       <c r="O17">
-        <v>69.43429633371869</v>
+        <v>69.6454896587187</v>
       </c>
       <c r="P17">
-        <v>261.2052100173227</v>
+        <v>261.9996991923227</v>
       </c>
       <c r="Q17">
-        <v>545.1052100173226</v>
+        <v>545.8996991923227</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07582681271134165</v>
+        <v>0.07581664727740059</v>
       </c>
       <c r="T17">
         <v>0.5061237956610791</v>
       </c>
       <c r="U17">
-        <v>0.0668732333250682</v>
+        <v>0.0653732333250682</v>
       </c>
       <c r="V17">
         <v>0.21</v>
       </c>
       <c r="W17">
-        <v>0.05282985432680388</v>
+        <v>0.05164485432680388</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.374503533735961</v>
+        <v>8.566657947120117</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.0723922263914156</v>
+        <v>0.0721940045080325</v>
       </c>
       <c r="C18">
-        <v>3851.088724879253</v>
+        <v>3859.767868423512</v>
       </c>
       <c r="D18">
-        <v>4533.440724879253</v>
+        <v>4542.119868423512</v>
       </c>
       <c r="E18">
         <v>-2188.848</v>
@@ -2769,37 +2769,37 @@
         <v>375.475</v>
       </c>
       <c r="M18">
-        <v>47.82452655888917</v>
+        <v>46.75179855888917</v>
       </c>
       <c r="N18">
-        <v>327.6504734411109</v>
+        <v>328.7232014411109</v>
       </c>
       <c r="O18">
-        <v>68.80659942263328</v>
+        <v>69.03187230263327</v>
       </c>
       <c r="P18">
-        <v>258.8438740184776</v>
+        <v>259.6913291384776</v>
       </c>
       <c r="Q18">
-        <v>542.7438740184775</v>
+        <v>543.5913291384776</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07611839249896069</v>
+        <v>0.07610812835207603</v>
       </c>
       <c r="T18">
         <v>0.5110385853281176</v>
       </c>
       <c r="U18">
-        <v>0.0668732333250682</v>
+        <v>0.0653732333250682</v>
       </c>
       <c r="V18">
         <v>0.21</v>
       </c>
       <c r="W18">
-        <v>0.05282985432680388</v>
+        <v>0.05164485432680388</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.851097062877464</v>
+        <v>8.031241825425109</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07260863382917021</v>
+        <v>0.0723045706812539</v>
       </c>
       <c r="C19">
-        <v>3796.574167306069</v>
+        <v>3810.030326065908</v>
       </c>
       <c r="D19">
-        <v>4523.623167306069</v>
+        <v>4537.079326065908</v>
       </c>
       <c r="E19">
         <v>-2144.151</v>
@@ -2851,37 +2851,37 @@
         <v>375.475</v>
       </c>
       <c r="M19">
-        <v>51.95333296881975</v>
+        <v>50.28166516881974</v>
       </c>
       <c r="N19">
-        <v>323.5216670311803</v>
+        <v>325.1933348311803</v>
       </c>
       <c r="O19">
-        <v>67.93955007654786</v>
+        <v>68.29060031454786</v>
       </c>
       <c r="P19">
-        <v>255.5821169546325</v>
+        <v>256.9027345166324</v>
       </c>
       <c r="Q19">
-        <v>539.4821169546324</v>
+        <v>540.8027345166324</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07641699830555851</v>
+        <v>0.07640663306710511</v>
       </c>
       <c r="T19">
         <v>0.5160718036618319</v>
       </c>
       <c r="U19">
-        <v>0.0683732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V19">
         <v>0.21</v>
       </c>
       <c r="W19">
-        <v>0.05401485432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.227159039543135</v>
+        <v>7.467433680633881</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07263544126692485</v>
+        <v>0.07231401685447532</v>
       </c>
       <c r="C20">
-        <v>3750.66397801254</v>
+        <v>3764.903208179254</v>
       </c>
       <c r="D20">
-        <v>4522.40997801254</v>
+        <v>4536.649208179254</v>
       </c>
       <c r="E20">
         <v>-2099.454</v>
@@ -2933,37 +2933,37 @@
         <v>375.475</v>
       </c>
       <c r="M20">
-        <v>55.00941137875031</v>
+        <v>53.23941017875031</v>
       </c>
       <c r="N20">
-        <v>320.4655886212497</v>
+        <v>322.2355898212497</v>
       </c>
       <c r="O20">
-        <v>67.29777361046244</v>
+        <v>67.66947386246244</v>
       </c>
       <c r="P20">
-        <v>253.1678150107873</v>
+        <v>254.5661159587873</v>
       </c>
       <c r="Q20">
-        <v>537.0678150107872</v>
+        <v>538.4661159587872</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07672288718060993</v>
+        <v>0.07671241838493978</v>
       </c>
       <c r="T20">
         <v>0.5212277834183195</v>
       </c>
       <c r="U20">
-        <v>0.0683732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V20">
         <v>0.21</v>
       </c>
       <c r="W20">
-        <v>0.05401485432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.825650204012962</v>
+        <v>7.052576253932</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07266224870467947</v>
+        <v>0.07232346302769672</v>
       </c>
       <c r="C21">
-        <v>3704.754439274366</v>
+        <v>3719.776171835746</v>
       </c>
       <c r="D21">
-        <v>4521.197439274366</v>
+        <v>4536.219171835746</v>
       </c>
       <c r="E21">
         <v>-2054.757</v>
@@ -3015,37 +3015,37 @@
         <v>375.475</v>
       </c>
       <c r="M21">
-        <v>58.06548978868089</v>
+        <v>56.19715518868088</v>
       </c>
       <c r="N21">
-        <v>317.4095102113191</v>
+        <v>319.2778448113191</v>
       </c>
       <c r="O21">
-        <v>66.65599714437701</v>
+        <v>67.04834741037702</v>
       </c>
       <c r="P21">
-        <v>250.7535130669421</v>
+        <v>252.2294974009421</v>
       </c>
       <c r="Q21">
-        <v>534.6535130669421</v>
+        <v>536.1294974009421</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07703632886739102</v>
+        <v>0.07702575395753579</v>
       </c>
       <c r="T21">
         <v>0.5265110713169427</v>
       </c>
       <c r="U21">
-        <v>0.0683732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V21">
         <v>0.21</v>
       </c>
       <c r="W21">
-        <v>0.05401485432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.466405456433331</v>
+        <v>6.681388030040842</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07268905614243409</v>
+        <v>0.07233290920091814</v>
       </c>
       <c r="C22">
-        <v>3658.845550568412</v>
+        <v>3674.649217012197</v>
       </c>
       <c r="D22">
-        <v>4519.985550568412</v>
+        <v>4535.789217012197</v>
       </c>
       <c r="E22">
         <v>-2010.06</v>
@@ -3097,37 +3097,37 @@
         <v>375.475</v>
       </c>
       <c r="M22">
-        <v>61.12156819861147</v>
+        <v>59.15490019861146</v>
       </c>
       <c r="N22">
-        <v>314.3534318013885</v>
+        <v>316.3200998013886</v>
       </c>
       <c r="O22">
-        <v>66.01422067829159</v>
+        <v>66.4272209582916</v>
       </c>
       <c r="P22">
-        <v>248.3392111230969</v>
+        <v>249.892878843097</v>
       </c>
       <c r="Q22">
-        <v>532.2392111230969</v>
+        <v>533.7928788430969</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07735760659634164</v>
+        <v>0.0773469229194467</v>
       </c>
       <c r="T22">
         <v>0.5319264414130315</v>
       </c>
       <c r="U22">
-        <v>0.0683732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V22">
         <v>0.21</v>
       </c>
       <c r="W22">
-        <v>0.05401485432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.143085183611664</v>
+        <v>6.347318628538798</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07294812358018871</v>
+        <v>0.07250825537413955</v>
       </c>
       <c r="C23">
-        <v>3602.470232659338</v>
+        <v>3621.98588114705</v>
       </c>
       <c r="D23">
-        <v>4508.307232659337</v>
+        <v>4527.82288114705</v>
       </c>
       <c r="E23">
         <v>-1965.363</v>
@@ -3179,37 +3179,37 @@
         <v>375.475</v>
       </c>
       <c r="M23">
-        <v>65.49173840854203</v>
+        <v>63.05128220854203</v>
       </c>
       <c r="N23">
-        <v>309.983261591458</v>
+        <v>312.423717791458</v>
       </c>
       <c r="O23">
-        <v>65.09648493420619</v>
+        <v>65.60898073620618</v>
       </c>
       <c r="P23">
-        <v>244.8867766572518</v>
+        <v>246.8147370552518</v>
       </c>
       <c r="Q23">
-        <v>528.7867766572518</v>
+        <v>530.7147370552518</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07768701793868341</v>
+        <v>0.07767622274115282</v>
       </c>
       <c r="T23">
         <v>0.5374789094862363</v>
       </c>
       <c r="U23">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V23">
         <v>0.21</v>
       </c>
       <c r="W23">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.73316587899623</v>
+        <v>5.955073185635099</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07298599101794333</v>
+        <v>0.07252560154736094</v>
       </c>
       <c r="C24">
-        <v>3556.07128633523</v>
+        <v>3576.502329735352</v>
       </c>
       <c r="D24">
-        <v>4506.60528633523</v>
+        <v>4527.036329735352</v>
       </c>
       <c r="E24">
         <v>-1920.666</v>
@@ -3261,37 +3261,37 @@
         <v>375.475</v>
       </c>
       <c r="M24">
-        <v>68.6103926184726</v>
+        <v>66.05372421847261</v>
       </c>
       <c r="N24">
-        <v>306.8646073815274</v>
+        <v>309.4212757815274</v>
       </c>
       <c r="O24">
-        <v>64.44156755012077</v>
+        <v>64.97846791412076</v>
       </c>
       <c r="P24">
-        <v>242.4230398314067</v>
+        <v>244.4428078674067</v>
       </c>
       <c r="Q24">
-        <v>526.3230398314066</v>
+        <v>528.3428078674067</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.0780248757257006</v>
+        <v>0.07801396614803088</v>
       </c>
       <c r="T24">
         <v>0.5431737485356772</v>
       </c>
       <c r="U24">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V24">
         <v>0.21</v>
       </c>
       <c r="W24">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.472567429950947</v>
+        <v>5.684388040833503</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07302385845569795</v>
+        <v>0.07254294772058235</v>
       </c>
       <c r="C25">
-        <v>3509.673624541229</v>
+        <v>3531.019051547975</v>
       </c>
       <c r="D25">
-        <v>4504.904624541229</v>
+        <v>4526.250051547975</v>
       </c>
       <c r="E25">
         <v>-1875.969</v>
@@ -3343,37 +3343,37 @@
         <v>375.475</v>
       </c>
       <c r="M25">
-        <v>71.72904682840318</v>
+        <v>69.05616622840317</v>
       </c>
       <c r="N25">
-        <v>303.7459531715969</v>
+        <v>306.4188337715968</v>
       </c>
       <c r="O25">
-        <v>63.78665016603534</v>
+        <v>64.34795509203533</v>
       </c>
       <c r="P25">
-        <v>239.9593030055615</v>
+        <v>242.0708786795615</v>
       </c>
       <c r="Q25">
-        <v>523.8593030055615</v>
+        <v>525.9708786795615</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07837150903965331</v>
+        <v>0.07836048211093177</v>
       </c>
       <c r="T25">
         <v>0.5490165054825064</v>
       </c>
       <c r="U25">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V25">
         <v>0.21</v>
       </c>
       <c r="W25">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.234629715605253</v>
+        <v>5.437240734710308</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07306172589345257</v>
+        <v>0.07256029389380378</v>
       </c>
       <c r="C26">
-        <v>3463.277245823654</v>
+        <v>3485.536046442579</v>
       </c>
       <c r="D26">
-        <v>4503.205245823654</v>
+        <v>4525.464046442579</v>
       </c>
       <c r="E26">
         <v>-1831.272</v>
@@ -3425,37 +3425,37 @@
         <v>375.475</v>
       </c>
       <c r="M26">
-        <v>74.84770103833375</v>
+        <v>72.05860823833375</v>
       </c>
       <c r="N26">
-        <v>300.6272989616663</v>
+        <v>303.4163917616663</v>
       </c>
       <c r="O26">
-        <v>63.13173278194991</v>
+        <v>63.71744226994991</v>
       </c>
       <c r="P26">
-        <v>237.4955661797163</v>
+        <v>239.6989494917163</v>
       </c>
       <c r="Q26">
-        <v>521.3955661797163</v>
+        <v>523.5989494917163</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07872726428292058</v>
+        <v>0.07871611691496164</v>
       </c>
       <c r="T26">
         <v>0.555013019191094</v>
       </c>
       <c r="U26">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V26">
         <v>0.21</v>
       </c>
       <c r="W26">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.016520144121701</v>
+        <v>5.210689037430711</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07309959333120718</v>
+        <v>0.07257764006702518</v>
       </c>
       <c r="C27">
-        <v>3416.882148731011</v>
+        <v>3440.053314276928</v>
       </c>
       <c r="D27">
-        <v>4501.507148731011</v>
+        <v>4524.678314276928</v>
       </c>
       <c r="E27">
         <v>-1786.575</v>
@@ -3507,37 +3507,37 @@
         <v>375.475</v>
       </c>
       <c r="M27">
-        <v>77.96635524826434</v>
+        <v>75.06105024826432</v>
       </c>
       <c r="N27">
-        <v>297.5086447517357</v>
+        <v>300.4139497517357</v>
       </c>
       <c r="O27">
-        <v>62.47681539786449</v>
+        <v>63.08692944786449</v>
       </c>
       <c r="P27">
-        <v>235.0318293538712</v>
+        <v>237.3270203038712</v>
       </c>
       <c r="Q27">
-        <v>518.9318293538712</v>
+        <v>521.2270203038712</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07909250633267495</v>
+        <v>0.07908123531376561</v>
       </c>
       <c r="T27">
         <v>0.5611694399319106</v>
       </c>
       <c r="U27">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V27">
         <v>0.21</v>
       </c>
       <c r="W27">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.815859338356832</v>
+        <v>5.002261475933483</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07313746076896181</v>
+        <v>0.07259498624024659</v>
       </c>
       <c r="C28">
-        <v>3370.488331813996</v>
+        <v>3394.570854908875</v>
       </c>
       <c r="D28">
-        <v>4499.810331813996</v>
+        <v>4523.892854908875</v>
       </c>
       <c r="E28">
         <v>-1741.878</v>
@@ -3589,37 +3589,37 @@
         <v>375.475</v>
       </c>
       <c r="M28">
-        <v>81.0850094581949</v>
+        <v>78.0634922581949</v>
       </c>
       <c r="N28">
-        <v>294.3899905418051</v>
+        <v>297.4115077418051</v>
       </c>
       <c r="O28">
-        <v>61.82189801377907</v>
+        <v>62.45641662577907</v>
       </c>
       <c r="P28">
-        <v>232.568092528026</v>
+        <v>234.955091116026</v>
       </c>
       <c r="Q28">
-        <v>516.468092528026</v>
+        <v>518.855091116026</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07946761978917946</v>
+        <v>0.07945622177740214</v>
       </c>
       <c r="T28">
         <v>0.5674922504224792</v>
       </c>
       <c r="U28">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V28">
         <v>0.21</v>
       </c>
       <c r="W28">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.630633979189263</v>
+        <v>4.809866803782195</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07372990820671645</v>
+        <v>0.07261233241346801</v>
       </c>
       <c r="C29">
-        <v>3299.409711395554</v>
+        <v>3349.088668196376</v>
       </c>
       <c r="D29">
-        <v>4473.428711395554</v>
+        <v>4523.107668196376</v>
       </c>
       <c r="E29">
         <v>-1697.181</v>
@@ -3671,45 +3671,45 @@
         <v>375.475</v>
       </c>
       <c r="M29">
-        <v>87.34139306812548</v>
+        <v>81.06593426812547</v>
       </c>
       <c r="N29">
-        <v>288.1336069318745</v>
+        <v>294.4090657318745</v>
       </c>
       <c r="O29">
-        <v>60.50805745569365</v>
+        <v>61.82590380369365</v>
       </c>
       <c r="P29">
-        <v>227.6255494761809</v>
+        <v>232.5831619281809</v>
       </c>
       <c r="Q29">
-        <v>511.5255494761809</v>
+        <v>516.4831619281808</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.0798530103266841</v>
+        <v>0.07984148184278214</v>
       </c>
       <c r="T29">
         <v>0.5739882885977208</v>
       </c>
       <c r="U29">
-        <v>0.0723732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V29">
         <v>0.21</v>
       </c>
       <c r="W29">
-        <v>0.05717485432680389</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.298935325054101</v>
+        <v>4.631723588827299</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07378831564447105</v>
+        <v>0.07318267858668941</v>
       </c>
       <c r="C30">
-        <v>3252.12857662014</v>
+        <v>3278.725501697364</v>
       </c>
       <c r="D30">
-        <v>4470.84457662014</v>
+        <v>4497.441501697363</v>
       </c>
       <c r="E30">
         <v>-1652.484</v>
@@ -3753,37 +3753,37 @@
         <v>375.475</v>
       </c>
       <c r="M30">
-        <v>90.57625947805606</v>
+        <v>87.19716627805606</v>
       </c>
       <c r="N30">
-        <v>284.898740521944</v>
+        <v>288.277833721944</v>
       </c>
       <c r="O30">
-        <v>59.82873550960824</v>
+        <v>60.53834508160823</v>
       </c>
       <c r="P30">
-        <v>225.0700050123357</v>
+        <v>227.7394886403357</v>
       </c>
       <c r="Q30">
-        <v>508.9700050123357</v>
+        <v>511.6394886403357</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08024910615689718</v>
+        <v>0.08023744357664489</v>
       </c>
       <c r="T30">
         <v>0.5806647722778302</v>
       </c>
       <c r="U30">
-        <v>0.0723732333250682</v>
+        <v>0.0696732333250682</v>
       </c>
       <c r="V30">
         <v>0.21</v>
       </c>
       <c r="W30">
-        <v>0.05717485432680389</v>
+        <v>0.05504185432680388</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.145401920587883</v>
+        <v>4.306045896063616</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07384672308222567</v>
+        <v>0.07321977475991083</v>
       </c>
       <c r="C31">
-        <v>3204.850425639799</v>
+        <v>3232.369220752458</v>
       </c>
       <c r="D31">
-        <v>4468.263425639799</v>
+        <v>4495.782220752458</v>
       </c>
       <c r="E31">
         <v>-1607.787</v>
@@ -3835,37 +3835,37 @@
         <v>375.475</v>
       </c>
       <c r="M31">
-        <v>93.81112588798663</v>
+        <v>90.31135078798661</v>
       </c>
       <c r="N31">
-        <v>281.6638741120134</v>
+        <v>285.1636492120134</v>
       </c>
       <c r="O31">
-        <v>59.14941356352281</v>
+        <v>59.88436633452282</v>
       </c>
       <c r="P31">
-        <v>222.5144605484906</v>
+        <v>225.2792828774906</v>
       </c>
       <c r="Q31">
-        <v>506.4144605484905</v>
+        <v>509.1792828774906</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08065635961613035</v>
+        <v>0.08064455916216579</v>
       </c>
       <c r="T31">
         <v>0.5875293259207597</v>
       </c>
       <c r="U31">
-        <v>0.0723732333250682</v>
+        <v>0.0696732333250682</v>
       </c>
       <c r="V31">
         <v>0.21</v>
       </c>
       <c r="W31">
-        <v>0.05717485432680389</v>
+        <v>0.05504185432680388</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.002457026774508</v>
+        <v>4.157561554820044</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07454503051998029</v>
+        <v>0.07325687093313223</v>
       </c>
       <c r="C32">
-        <v>3129.522950976724</v>
+        <v>3186.014163702454</v>
       </c>
       <c r="D32">
-        <v>4437.632950976724</v>
+        <v>4494.124163702454</v>
       </c>
       <c r="E32">
         <v>-1563.09</v>
@@ -3917,45 +3917,45 @@
         <v>375.475</v>
       </c>
       <c r="M32">
-        <v>100.6664492979172</v>
+        <v>93.42553529791718</v>
       </c>
       <c r="N32">
-        <v>274.8085507020828</v>
+        <v>282.0494647020828</v>
       </c>
       <c r="O32">
-        <v>57.70979564743739</v>
+        <v>59.23038758743739</v>
       </c>
       <c r="P32">
-        <v>217.0987550546454</v>
+        <v>222.8190771146454</v>
       </c>
       <c r="Q32">
-        <v>500.9987550546454</v>
+        <v>506.7190771146454</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08107524888848447</v>
+        <v>0.08106330662155867</v>
       </c>
       <c r="T32">
         <v>0.5945900096677726</v>
       </c>
       <c r="U32">
-        <v>0.0750732333250682</v>
+        <v>0.0696732333250682</v>
       </c>
       <c r="V32">
         <v>0.21</v>
       </c>
       <c r="W32">
-        <v>0.05930785432680388</v>
+        <v>0.05504185432680388</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.729892159887362</v>
+        <v>4.018976169659377</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07462476795773493</v>
+        <v>0.07415111710635365</v>
       </c>
       <c r="C33">
-        <v>3081.35505077172</v>
+        <v>3101.714604383147</v>
       </c>
       <c r="D33">
-        <v>4434.16205077172</v>
+        <v>4454.521604383147</v>
       </c>
       <c r="E33">
         <v>-1518.393</v>
@@ -3999,37 +3999,37 @@
         <v>375.475</v>
       </c>
       <c r="M33">
-        <v>104.0219976078478</v>
+        <v>101.3893443078478</v>
       </c>
       <c r="N33">
-        <v>271.4530023921523</v>
+        <v>274.0856556921523</v>
       </c>
       <c r="O33">
-        <v>57.00513050235197</v>
+        <v>57.55798769535198</v>
       </c>
       <c r="P33">
-        <v>214.4478718898003</v>
+        <v>216.5276679968003</v>
       </c>
       <c r="Q33">
-        <v>498.3478718898003</v>
+        <v>500.4276679968003</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08150627987887786</v>
+        <v>0.08149419168847022</v>
       </c>
       <c r="T33">
         <v>0.6018553509146993</v>
       </c>
       <c r="U33">
-        <v>0.0750732333250682</v>
+        <v>0.0731732333250682</v>
       </c>
       <c r="V33">
         <v>0.21</v>
       </c>
       <c r="W33">
-        <v>0.05930785432680388</v>
+        <v>0.05780685432680388</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.609573057955512</v>
+        <v>3.703298434004543</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07589266539548953</v>
+        <v>0.07421586327957505</v>
       </c>
       <c r="C34">
-        <v>2982.188199775001</v>
+        <v>3054.177336718691</v>
       </c>
       <c r="D34">
-        <v>4379.692199775001</v>
+        <v>4451.681336718691</v>
       </c>
       <c r="E34">
         <v>-1473.696</v>
@@ -4081,45 +4081,45 @@
         <v>375.475</v>
       </c>
       <c r="M34">
-        <v>114.0999747177783</v>
+        <v>104.6599683177783</v>
       </c>
       <c r="N34">
-        <v>261.3750252822217</v>
+        <v>270.8150316822217</v>
       </c>
       <c r="O34">
-        <v>54.88875530926656</v>
+        <v>56.87115665326655</v>
       </c>
       <c r="P34">
-        <v>206.4862699729551</v>
+        <v>213.9438750289551</v>
       </c>
       <c r="Q34">
-        <v>490.3862699729551</v>
+        <v>497.8438750289551</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08194998825134162</v>
+        <v>0.08193774984558502</v>
       </c>
       <c r="T34">
         <v>0.6093343786688883</v>
       </c>
       <c r="U34">
-        <v>0.07977323332506819</v>
+        <v>0.0731732333250682</v>
       </c>
       <c r="V34">
         <v>0.21</v>
       </c>
       <c r="W34">
-        <v>0.06302085432680388</v>
+        <v>0.05780685432680388</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.290754453966553</v>
+        <v>3.5875703579419</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07600953283324416</v>
+        <v>0.07501056945279647</v>
       </c>
       <c r="C35">
-        <v>2932.537768411702</v>
+        <v>2974.91115431123</v>
       </c>
       <c r="D35">
-        <v>4374.738768411702</v>
+        <v>4417.11215431123</v>
       </c>
       <c r="E35">
         <v>-1428.999</v>
@@ -4163,37 +4163,37 @@
         <v>375.475</v>
       </c>
       <c r="M35">
-        <v>117.6655989277089</v>
+        <v>112.0605951277089</v>
       </c>
       <c r="N35">
-        <v>257.8094010722911</v>
+        <v>263.4144048722911</v>
       </c>
       <c r="O35">
-        <v>54.13997422518113</v>
+        <v>55.31702502318114</v>
       </c>
       <c r="P35">
-        <v>203.66942684711</v>
+        <v>208.09737984911</v>
       </c>
       <c r="Q35">
-        <v>487.56942684711</v>
+        <v>491.99737984911</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08240694164984907</v>
+        <v>0.08239454854470327</v>
       </c>
       <c r="T35">
         <v>0.6170366609829039</v>
       </c>
       <c r="U35">
-        <v>0.07977323332506819</v>
+        <v>0.0759732333250682</v>
       </c>
       <c r="V35">
         <v>0.21</v>
       </c>
       <c r="W35">
-        <v>0.06302085432680388</v>
+        <v>0.06001885432680388</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.191034622028171</v>
+        <v>3.350642565944729</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07612640027099878</v>
+        <v>0.07509743562601787</v>
       </c>
       <c r="C36">
-        <v>2882.898529050831</v>
+        <v>2926.468056670222</v>
       </c>
       <c r="D36">
-        <v>4369.796529050831</v>
+        <v>4413.366056670222</v>
       </c>
       <c r="E36">
         <v>-1384.302</v>
@@ -4245,37 +4245,37 @@
         <v>375.475</v>
       </c>
       <c r="M36">
-        <v>121.2312231376395</v>
+        <v>115.4563707376395</v>
       </c>
       <c r="N36">
-        <v>254.2437768623605</v>
+        <v>260.0186292623605</v>
       </c>
       <c r="O36">
-        <v>53.39119314109571</v>
+        <v>54.60391214509571</v>
       </c>
       <c r="P36">
-        <v>200.8525837212648</v>
+        <v>205.4147171172648</v>
       </c>
       <c r="Q36">
-        <v>484.7525837212648</v>
+        <v>489.3147171172648</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08287774212103859</v>
+        <v>0.08286518962864327</v>
       </c>
       <c r="T36">
         <v>0.6249723457912837</v>
       </c>
       <c r="U36">
-        <v>0.07977323332506819</v>
+        <v>0.0759732333250682</v>
       </c>
       <c r="V36">
         <v>0.21</v>
       </c>
       <c r="W36">
-        <v>0.06302085432680388</v>
+        <v>0.06001885432680388</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.097180662556755</v>
+        <v>3.252094255181649</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07624326770875341</v>
+        <v>0.07518430179923928</v>
       </c>
       <c r="C37">
-        <v>2833.270443803629</v>
+        <v>2878.031307682228</v>
       </c>
       <c r="D37">
-        <v>4364.865443803629</v>
+        <v>4409.626307682228</v>
       </c>
       <c r="E37">
         <v>-1339.605</v>
@@ -4327,37 +4327,37 @@
         <v>375.475</v>
       </c>
       <c r="M37">
-        <v>124.7968473475701</v>
+        <v>118.8521463475701</v>
       </c>
       <c r="N37">
-        <v>250.67815265243</v>
+        <v>256.62285365243</v>
       </c>
       <c r="O37">
-        <v>52.64241205701029</v>
+        <v>53.89079926701029</v>
       </c>
       <c r="P37">
-        <v>198.0357405954197</v>
+        <v>202.7320543854197</v>
       </c>
       <c r="Q37">
-        <v>481.9357405954196</v>
+        <v>486.6320543854197</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08336302876057239</v>
+        <v>0.08335031197670451</v>
       </c>
       <c r="T37">
         <v>0.6331522055168443</v>
       </c>
       <c r="U37">
-        <v>0.07977323332506819</v>
+        <v>0.0759732333250682</v>
       </c>
       <c r="V37">
         <v>0.21</v>
       </c>
       <c r="W37">
-        <v>0.06302085432680388</v>
+        <v>0.06001885432680388</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.008689786483705</v>
+        <v>3.159177276462173</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07900505514650802</v>
+        <v>0.0752711679724607</v>
       </c>
       <c r="C38">
-        <v>2675.197953130347</v>
+        <v>2829.600891221961</v>
       </c>
       <c r="D38">
-        <v>4251.489953130346</v>
+        <v>4405.892891221961</v>
       </c>
       <c r="E38">
         <v>-1294.908</v>
@@ -4409,45 +4409,45 @@
         <v>375.475</v>
       </c>
       <c r="M38">
-        <v>143.3270271575006</v>
+        <v>122.2479219575006</v>
       </c>
       <c r="N38">
-        <v>232.1479728424994</v>
+        <v>253.2270780424994</v>
       </c>
       <c r="O38">
-        <v>48.75107429692487</v>
+        <v>53.17768638892487</v>
       </c>
       <c r="P38">
-        <v>183.3968985455745</v>
+        <v>200.0493916535745</v>
       </c>
       <c r="Q38">
-        <v>467.2968985455745</v>
+        <v>483.9493916535745</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08386348060759161</v>
+        <v>0.08385059439814266</v>
       </c>
       <c r="T38">
         <v>0.6415876858588286</v>
       </c>
       <c r="U38">
-        <v>0.0890732333250682</v>
+        <v>0.0759732333250682</v>
       </c>
       <c r="V38">
         <v>0.21</v>
       </c>
       <c r="W38">
-        <v>0.07036785432680388</v>
+        <v>0.06001885432680388</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.619708281449209</v>
+        <v>3.071422352116002</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07919539258426264</v>
+        <v>0.07763797414568209</v>
       </c>
       <c r="C39">
-        <v>2622.903873108668</v>
+        <v>2685.558908705764</v>
       </c>
       <c r="D39">
-        <v>4243.892873108668</v>
+        <v>4306.547908705764</v>
       </c>
       <c r="E39">
         <v>-1250.211</v>
@@ -4491,37 +4491,37 @@
         <v>375.475</v>
       </c>
       <c r="M39">
-        <v>147.3083334674312</v>
+        <v>138.5432517674312</v>
       </c>
       <c r="N39">
-        <v>228.1666665325688</v>
+        <v>236.9317482325688</v>
       </c>
       <c r="O39">
-        <v>47.91499997183945</v>
+        <v>49.75566712883945</v>
       </c>
       <c r="P39">
-        <v>180.2516665607294</v>
+        <v>187.1760811037294</v>
       </c>
       <c r="Q39">
-        <v>464.1516665607294</v>
+        <v>471.0760811037293</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08437981981483367</v>
+        <v>0.08436675880121375</v>
       </c>
       <c r="T39">
         <v>0.6502909592275427</v>
       </c>
       <c r="U39">
-        <v>0.0890732333250682</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V39">
         <v>0.21</v>
       </c>
       <c r="W39">
-        <v>0.07036785432680388</v>
+        <v>0.06618085432680387</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.548905354923554</v>
+        <v>2.710164480838805</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08079667002201729</v>
+        <v>0.07778646031890352</v>
       </c>
       <c r="C40">
-        <v>2515.352988068421</v>
+        <v>2634.778448300885</v>
       </c>
       <c r="D40">
-        <v>4181.038988068421</v>
+        <v>4300.464448300884</v>
       </c>
       <c r="E40">
         <v>-1205.514</v>
@@ -4573,45 +4573,45 @@
         <v>375.475</v>
       </c>
       <c r="M40">
-        <v>159.2725239773618</v>
+        <v>142.2876639773618</v>
       </c>
       <c r="N40">
-        <v>216.2024760226383</v>
+        <v>233.1873360226382</v>
       </c>
       <c r="O40">
-        <v>45.40251996475403</v>
+        <v>48.96934056475403</v>
       </c>
       <c r="P40">
-        <v>170.7999560578842</v>
+        <v>184.2179954578842</v>
       </c>
       <c r="Q40">
-        <v>454.6999560578842</v>
+        <v>468.1179954578842</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08491281512553517</v>
+        <v>0.08489957366890008</v>
       </c>
       <c r="T40">
         <v>0.6592749833500864</v>
       </c>
       <c r="U40">
-        <v>0.09377323332506821</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V40">
         <v>0.21</v>
       </c>
       <c r="W40">
-        <v>0.07408085432680389</v>
+        <v>0.06618085432680387</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.357437369758567</v>
+        <v>2.638844362921994</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.0810241374597719</v>
+        <v>0.07793494649212493</v>
       </c>
       <c r="C41">
-        <v>2461.878063582239</v>
+        <v>2584.015150731095</v>
       </c>
       <c r="D41">
-        <v>4172.261063582238</v>
+        <v>4294.398150731095</v>
       </c>
       <c r="E41">
         <v>-1160.817</v>
@@ -4655,45 +4655,45 @@
         <v>375.475</v>
       </c>
       <c r="M41">
-        <v>163.4639061872924</v>
+        <v>146.0320761872923</v>
       </c>
       <c r="N41">
-        <v>212.0110938127077</v>
+        <v>229.4429238127077</v>
       </c>
       <c r="O41">
-        <v>44.52232970066861</v>
+        <v>48.18301400066861</v>
       </c>
       <c r="P41">
-        <v>167.4887641120391</v>
+        <v>181.2599098120391</v>
       </c>
       <c r="Q41">
-        <v>451.388764112039</v>
+        <v>465.159909812039</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08546328569232521</v>
+        <v>0.08544985787651052</v>
       </c>
       <c r="T41">
         <v>0.6685535656405821</v>
       </c>
       <c r="U41">
-        <v>0.09377323332506821</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V41">
         <v>0.21</v>
       </c>
       <c r="W41">
-        <v>0.07408085432680389</v>
+        <v>0.06618085432680387</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.296990257713475</v>
+        <v>2.571181686949635</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08125160489752652</v>
+        <v>0.07808343266534633</v>
       </c>
       <c r="C42">
-        <v>2408.439919680933</v>
+        <v>2533.268943468274</v>
       </c>
       <c r="D42">
-        <v>4163.519919680933</v>
+        <v>4288.348943468274</v>
       </c>
       <c r="E42">
         <v>-1116.12</v>
@@ -4737,45 +4737,45 @@
         <v>375.475</v>
       </c>
       <c r="M42">
-        <v>167.655288397223</v>
+        <v>149.7764883972229</v>
       </c>
       <c r="N42">
-        <v>207.8197116027771</v>
+        <v>225.6985116027771</v>
       </c>
       <c r="O42">
-        <v>43.64213943658318</v>
+        <v>47.39668743658319</v>
       </c>
       <c r="P42">
-        <v>164.1775721661939</v>
+        <v>178.3018241661939</v>
       </c>
       <c r="Q42">
-        <v>448.0775721661939</v>
+        <v>462.2018241661939</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08603210527800827</v>
+        <v>0.0860184848910413</v>
       </c>
       <c r="T42">
         <v>0.6781414340074278</v>
       </c>
       <c r="U42">
-        <v>0.09377323332506821</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V42">
         <v>0.21</v>
       </c>
       <c r="W42">
-        <v>0.07408085432680389</v>
+        <v>0.06618085432680387</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.239565501270638</v>
+        <v>2.506902144775894</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08147907233528114</v>
+        <v>0.07949512883856774</v>
       </c>
       <c r="C43">
-        <v>2355.038325675039</v>
+        <v>2431.900542733355</v>
       </c>
       <c r="D43">
-        <v>4154.815325675039</v>
+        <v>4231.677542733355</v>
       </c>
       <c r="E43">
         <v>-1071.423</v>
@@ -4819,37 +4819,37 @@
         <v>375.475</v>
       </c>
       <c r="M43">
-        <v>171.8466706071535</v>
+        <v>160.6679509071535</v>
       </c>
       <c r="N43">
-        <v>203.6283293928465</v>
+        <v>214.8070490928465</v>
       </c>
       <c r="O43">
-        <v>42.76194917249776</v>
+        <v>45.10948030949777</v>
       </c>
       <c r="P43">
-        <v>160.8663802203487</v>
+        <v>169.6975687833487</v>
       </c>
       <c r="Q43">
-        <v>444.7663802203487</v>
+        <v>453.5975687833487</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08662020688354499</v>
+        <v>0.08660638739759009</v>
       </c>
       <c r="T43">
         <v>0.6880543148612851</v>
       </c>
       <c r="U43">
-        <v>0.09377323332506821</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V43">
         <v>0.21</v>
       </c>
       <c r="W43">
-        <v>0.07408085432680389</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.184941952459159</v>
+        <v>2.336962647995547</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08170653977303577</v>
+        <v>0.07967442501178915</v>
       </c>
       <c r="C44">
-        <v>2301.673052800265</v>
+        <v>2380.112863201748</v>
       </c>
       <c r="D44">
-        <v>4146.147052800265</v>
+        <v>4224.586863201748</v>
       </c>
       <c r="E44">
         <v>-1026.726</v>
@@ -4901,37 +4901,37 @@
         <v>375.475</v>
       </c>
       <c r="M44">
-        <v>176.0380528170841</v>
+        <v>164.5866814170841</v>
       </c>
       <c r="N44">
-        <v>199.4369471829159</v>
+        <v>210.888318582916</v>
       </c>
       <c r="O44">
-        <v>41.88175890841234</v>
+        <v>44.28654690241235</v>
       </c>
       <c r="P44">
-        <v>157.5551882745036</v>
+        <v>166.6017716805036</v>
       </c>
       <c r="Q44">
-        <v>441.4551882745036</v>
+        <v>450.5017716805036</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08722858785478987</v>
+        <v>0.08721456240436469</v>
       </c>
       <c r="T44">
         <v>0.6983090191928616</v>
       </c>
       <c r="U44">
-        <v>0.09377323332506821</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V44">
         <v>0.21</v>
       </c>
       <c r="W44">
-        <v>0.07408085432680389</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.132919525019656</v>
+        <v>2.28132068018613</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08193400721079039</v>
+        <v>0.07985372118501056</v>
       </c>
       <c r="C45">
-        <v>2248.343874197439</v>
+        <v>2328.34890647525</v>
       </c>
       <c r="D45">
-        <v>4137.514874197439</v>
+        <v>4217.51990647525</v>
       </c>
       <c r="E45">
         <v>-982.029</v>
@@ -4983,37 +4983,37 @@
         <v>375.475</v>
       </c>
       <c r="M45">
-        <v>180.2294350270147</v>
+        <v>168.5054119270146</v>
       </c>
       <c r="N45">
-        <v>195.2455649729854</v>
+        <v>206.9695880729854</v>
       </c>
       <c r="O45">
-        <v>41.00156864432692</v>
+        <v>43.46361349532692</v>
       </c>
       <c r="P45">
-        <v>154.2439963286585</v>
+        <v>163.5059745776584</v>
       </c>
       <c r="Q45">
-        <v>438.1439963286584</v>
+        <v>447.4059745776584</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08785831552678018</v>
+        <v>0.08784407688506121</v>
       </c>
       <c r="T45">
         <v>0.7089235377115111</v>
       </c>
       <c r="U45">
-        <v>0.09377323332506821</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V45">
         <v>0.21</v>
       </c>
       <c r="W45">
-        <v>0.07408085432680389</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.083316745368036</v>
+        <v>2.228266710879475</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08216147464854501</v>
+        <v>0.08003301735823197</v>
       </c>
       <c r="C46">
-        <v>2195.050564892731</v>
+        <v>2276.608553701012</v>
       </c>
       <c r="D46">
-        <v>4128.918564892731</v>
+        <v>4210.476553701012</v>
       </c>
       <c r="E46">
         <v>-937.3320000000001</v>
@@ -5065,37 +5065,37 @@
         <v>375.475</v>
       </c>
       <c r="M46">
-        <v>184.4208172369452</v>
+        <v>172.4241424369452</v>
       </c>
       <c r="N46">
-        <v>191.0541827630548</v>
+        <v>203.0508575630548</v>
       </c>
       <c r="O46">
-        <v>40.12137838024151</v>
+        <v>42.64068008824151</v>
       </c>
       <c r="P46">
-        <v>150.9328043828133</v>
+        <v>160.4101774748133</v>
       </c>
       <c r="Q46">
-        <v>434.8328043828133</v>
+        <v>444.3101774748133</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08851053347277016</v>
+        <v>0.08849607402578262</v>
       </c>
       <c r="T46">
         <v>0.7199171461772552</v>
       </c>
       <c r="U46">
-        <v>0.09377323332506821</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V46">
         <v>0.21</v>
       </c>
       <c r="W46">
-        <v>0.07408085432680389</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.035968637518762</v>
+        <v>2.177624285632215</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08818359208629964</v>
+        <v>0.08021231353145339</v>
       </c>
       <c r="C47">
-        <v>1935.083205921344</v>
+        <v>2224.89168681881</v>
       </c>
       <c r="D47">
-        <v>3913.648205921344</v>
+        <v>4203.456686818809</v>
       </c>
       <c r="E47">
         <v>-892.635</v>
@@ -5147,45 +5147,45 @@
         <v>375.475</v>
       </c>
       <c r="M47">
-        <v>221.3974489468758</v>
+        <v>176.3428729468758</v>
       </c>
       <c r="N47">
-        <v>154.0775510531242</v>
+        <v>199.1321270531242</v>
       </c>
       <c r="O47">
-        <v>32.35628572115608</v>
+        <v>41.81774668115609</v>
       </c>
       <c r="P47">
-        <v>121.7212653319681</v>
+        <v>157.3143803719682</v>
       </c>
       <c r="Q47">
-        <v>405.6212653319681</v>
+        <v>441.2143803719681</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08918646843497796</v>
+        <v>0.08917178015343935</v>
       </c>
       <c r="T47">
         <v>0.7313105222235718</v>
       </c>
       <c r="U47">
-        <v>0.1100732333250682</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V47">
         <v>0.21</v>
       </c>
       <c r="W47">
-        <v>0.08695785432680389</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.695931916948578</v>
+        <v>2.129232634840387</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08853982952405424</v>
+        <v>0.08039160970467479</v>
       </c>
       <c r="C48">
-        <v>1878.352963560389</v>
+        <v>2173.198188554446</v>
       </c>
       <c r="D48">
-        <v>3901.614963560389</v>
+        <v>4196.460188554446</v>
       </c>
       <c r="E48">
         <v>-847.9380000000001</v>
@@ -5229,45 +5229,45 @@
         <v>375.475</v>
       </c>
       <c r="M48">
-        <v>226.3173922568064</v>
+        <v>180.2616034568064</v>
       </c>
       <c r="N48">
-        <v>149.1576077431936</v>
+        <v>195.2133965431937</v>
       </c>
       <c r="O48">
-        <v>31.32309762607066</v>
+        <v>40.99481327407067</v>
       </c>
       <c r="P48">
-        <v>117.834510117123</v>
+        <v>154.218583269123</v>
       </c>
       <c r="Q48">
-        <v>401.734510117123</v>
+        <v>438.118583269123</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08988743802541566</v>
+        <v>0.08987251243397223</v>
       </c>
       <c r="T48">
         <v>0.7431258751604928</v>
       </c>
       <c r="U48">
-        <v>0.1100732333250682</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V48">
         <v>0.21</v>
       </c>
       <c r="W48">
-        <v>0.08695785432680389</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.659063831797522</v>
+        <v>2.082944968865596</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08889606696180888</v>
+        <v>0.0805709058778962</v>
       </c>
       <c r="C49">
-        <v>1821.696491281709</v>
+        <v>2121.52794241322</v>
       </c>
       <c r="D49">
-        <v>3889.655491281709</v>
+        <v>4189.48694241322</v>
       </c>
       <c r="E49">
         <v>-803.241</v>
@@ -5311,45 +5311,45 @@
         <v>375.475</v>
       </c>
       <c r="M49">
-        <v>231.237335566737</v>
+        <v>184.180333966737</v>
       </c>
       <c r="N49">
-        <v>144.237664433263</v>
+        <v>191.2946660332631</v>
       </c>
       <c r="O49">
-        <v>30.28990953098524</v>
+        <v>40.17187986698524</v>
       </c>
       <c r="P49">
-        <v>113.9477549022778</v>
+        <v>151.1227861662778</v>
       </c>
       <c r="Q49">
-        <v>397.8477549022778</v>
+        <v>435.0227861662778</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.0906148592985114</v>
+        <v>0.09059968744207242</v>
       </c>
       <c r="T49">
         <v>0.7553870904723918</v>
       </c>
       <c r="U49">
-        <v>0.1100732333250682</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V49">
         <v>0.21</v>
       </c>
       <c r="W49">
-        <v>0.08695785432680389</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.623764601333745</v>
+        <v>2.038626990804626</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08925230439956348</v>
+        <v>0.0861348420511176</v>
       </c>
       <c r="C50">
-        <v>1765.113112784448</v>
+        <v>1871.389841503454</v>
       </c>
       <c r="D50">
-        <v>3877.769112784447</v>
+        <v>3984.045841503453</v>
       </c>
       <c r="E50">
         <v>-758.5440000000003</v>
@@ -5393,37 +5393,37 @@
         <v>375.475</v>
       </c>
       <c r="M50">
-        <v>236.1572788766675</v>
+        <v>218.5645396766675</v>
       </c>
       <c r="N50">
-        <v>139.3177211233325</v>
+        <v>156.9104603233325</v>
       </c>
       <c r="O50">
-        <v>29.25672143589983</v>
+        <v>32.95119666789983</v>
       </c>
       <c r="P50">
-        <v>110.0609996874327</v>
+        <v>123.9592636554327</v>
       </c>
       <c r="Q50">
-        <v>393.9609996874327</v>
+        <v>407.8592636554326</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09137025831288004</v>
+        <v>0.0913548307197149</v>
       </c>
       <c r="T50">
         <v>0.7681198909885946</v>
       </c>
       <c r="U50">
-        <v>0.1100732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V50">
         <v>0.21</v>
       </c>
       <c r="W50">
-        <v>0.08695785432680389</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.589936172139292</v>
+        <v>1.717913622015069</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08960854183731812</v>
+        <v>0.08642631822433902</v>
       </c>
       <c r="C51">
-        <v>1708.602160009371</v>
+        <v>1816.484445471647</v>
       </c>
       <c r="D51">
-        <v>3865.955160009371</v>
+        <v>3973.837445471646</v>
       </c>
       <c r="E51">
         <v>-713.8470000000002</v>
@@ -5475,37 +5475,37 @@
         <v>375.475</v>
       </c>
       <c r="M51">
-        <v>241.0772221865981</v>
+        <v>223.1179675865981</v>
       </c>
       <c r="N51">
-        <v>134.3977778134019</v>
+        <v>152.357032413402</v>
       </c>
       <c r="O51">
-        <v>28.2235333408144</v>
+        <v>31.99497680681441</v>
       </c>
       <c r="P51">
-        <v>106.1742444725875</v>
+        <v>120.3620556065875</v>
       </c>
       <c r="Q51">
-        <v>390.0742444725875</v>
+        <v>404.2620556065875</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09215528081800824</v>
+        <v>0.09213958745922574</v>
       </c>
       <c r="T51">
         <v>0.7813520170152368</v>
       </c>
       <c r="U51">
-        <v>0.1100732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V51">
         <v>0.21</v>
       </c>
       <c r="W51">
-        <v>0.08695785432680389</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.557488495156857</v>
+        <v>1.682854160341292</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08996477927507274</v>
+        <v>0.08671779439756043</v>
       </c>
       <c r="C52">
-        <v>1652.162973013722</v>
+        <v>1761.631230068986</v>
       </c>
       <c r="D52">
-        <v>3854.212973013722</v>
+        <v>3963.681230068986</v>
       </c>
       <c r="E52">
         <v>-669.1500000000001</v>
@@ -5557,37 +5557,37 @@
         <v>375.475</v>
       </c>
       <c r="M52">
-        <v>245.9971654965287</v>
+        <v>227.6713954965287</v>
       </c>
       <c r="N52">
-        <v>129.4778345034713</v>
+        <v>147.8036045034713</v>
       </c>
       <c r="O52">
-        <v>27.19034524572898</v>
+        <v>31.03875694572898</v>
       </c>
       <c r="P52">
-        <v>102.2874892577424</v>
+        <v>116.7648475577424</v>
       </c>
       <c r="Q52">
-        <v>386.1874892577424</v>
+        <v>400.6648475577423</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09297170422334157</v>
+        <v>0.09295573446831698</v>
       </c>
       <c r="T52">
         <v>0.7951134280829447</v>
       </c>
       <c r="U52">
-        <v>0.1100732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V52">
         <v>0.21</v>
       </c>
       <c r="W52">
-        <v>0.08695785432680389</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.52633872525372</v>
+        <v>1.649197077134466</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1179959556961863</v>
+        <v>0.08700927057078184</v>
       </c>
       <c r="C53">
-        <v>864.0033981462607</v>
+        <v>1706.829796230297</v>
       </c>
       <c r="D53">
-        <v>3110.750398146261</v>
+        <v>3953.576796230297</v>
       </c>
       <c r="E53">
         <v>-624.453</v>
@@ -5639,45 +5639,45 @@
         <v>375.475</v>
       </c>
       <c r="M53">
-        <v>399.9994826064593</v>
+        <v>232.2248234064593</v>
       </c>
       <c r="N53">
-        <v>-24.52448260645923</v>
+        <v>143.2501765935408</v>
       </c>
       <c r="O53">
-        <v>-5.150141347356438</v>
+        <v>30.08253708464356</v>
       </c>
       <c r="P53">
-        <v>-19.37434125910279</v>
+        <v>113.1676395088972</v>
       </c>
       <c r="Q53">
-        <v>264.5256587408972</v>
+        <v>397.0676395088972</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09417460358650037</v>
+        <v>0.09380519360022829</v>
       </c>
       <c r="T53">
-        <v>0.8153891728758732</v>
+        <v>0.8094365293983142</v>
       </c>
       <c r="U53">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V53">
-        <v>0.1971246299775257</v>
+        <v>0.21</v>
       </c>
       <c r="W53">
-        <v>0.1408831371349041</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.9386887141786938</v>
+        <v>1.616859879543594</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1192926880294369</v>
+        <v>0.08730074674400326</v>
       </c>
       <c r="C54">
-        <v>791.7933080628618</v>
+        <v>1652.079748949331</v>
       </c>
       <c r="D54">
-        <v>3083.237308062862</v>
+        <v>3943.523748949331</v>
       </c>
       <c r="E54">
         <v>-579.7559999999999</v>
@@ -5721,45 +5721,45 @@
         <v>375.475</v>
       </c>
       <c r="M54">
-        <v>407.8426097163899</v>
+        <v>236.7782513163898</v>
       </c>
       <c r="N54">
-        <v>-32.36760971638984</v>
+        <v>138.6967486836102</v>
       </c>
       <c r="O54">
-        <v>-6.797198040441866</v>
+        <v>29.12631722355814</v>
       </c>
       <c r="P54">
-        <v>-25.57041167594797</v>
+        <v>109.570431460052</v>
       </c>
       <c r="Q54">
-        <v>258.329588324052</v>
+        <v>393.4704314600521</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09518240782788578</v>
+        <v>0.09469004686263591</v>
       </c>
       <c r="T54">
-        <v>0.8323764473107873</v>
+        <v>0.8243564266018241</v>
       </c>
       <c r="U54">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V54">
-        <v>0.1933337717087271</v>
+        <v>0.21</v>
       </c>
       <c r="W54">
-        <v>0.1415483312924073</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.9206370081367957</v>
+        <v>1.585766420321602</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1205894203626876</v>
+        <v>0.08759222291722465</v>
       </c>
       <c r="C55">
-        <v>720.0656313451832</v>
+        <v>1597.380697227297</v>
       </c>
       <c r="D55">
-        <v>3056.206631345183</v>
+        <v>3933.521697227297</v>
       </c>
       <c r="E55">
         <v>-535.0590000000002</v>
@@ -5803,45 +5803,45 @@
         <v>375.475</v>
       </c>
       <c r="M55">
-        <v>415.6857368263204</v>
+        <v>241.3316792263204</v>
       </c>
       <c r="N55">
-        <v>-40.21073682632033</v>
+        <v>134.1433207736796</v>
       </c>
       <c r="O55">
-        <v>-8.444254733527268</v>
+        <v>28.17009736247272</v>
       </c>
       <c r="P55">
-        <v>-31.76648209279306</v>
+        <v>105.9732234112069</v>
       </c>
       <c r="Q55">
-        <v>252.1335179072069</v>
+        <v>389.8732234112069</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09623309735613868</v>
+        <v>0.09561255345535874</v>
       </c>
       <c r="T55">
-        <v>0.8500865844876124</v>
+        <v>0.8399112130480364</v>
       </c>
       <c r="U55">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V55">
-        <v>0.1896859646953549</v>
+        <v>0.21</v>
       </c>
       <c r="W55">
-        <v>0.1421884237835895</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.9032664985493092</v>
+        <v>1.555846299183458</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1218861526959383</v>
+        <v>0.08788369909044608</v>
       </c>
       <c r="C56">
-        <v>648.8077903377321</v>
+        <v>1542.732254022163</v>
       </c>
       <c r="D56">
-        <v>3029.645790337732</v>
+        <v>3923.570254022163</v>
       </c>
       <c r="E56">
         <v>-490.3620000000001</v>
@@ -5885,45 +5885,45 @@
         <v>375.475</v>
       </c>
       <c r="M56">
-        <v>423.528863936251</v>
+        <v>245.885107136251</v>
       </c>
       <c r="N56">
-        <v>-48.05386393625093</v>
+        <v>129.5898928637491</v>
       </c>
       <c r="O56">
-        <v>-10.0913114266127</v>
+        <v>27.21387750138731</v>
       </c>
       <c r="P56">
-        <v>-37.96255250963824</v>
+        <v>102.3760153623618</v>
       </c>
       <c r="Q56">
-        <v>245.9374474903617</v>
+        <v>386.2760153623618</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09732946903779388</v>
+        <v>0.09657516903037386</v>
       </c>
       <c r="T56">
-        <v>0.8685667276286476</v>
+        <v>0.8561422945571275</v>
       </c>
       <c r="U56">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V56">
-        <v>0.1861732616454409</v>
+        <v>0.21</v>
       </c>
       <c r="W56">
-        <v>0.1428048091454688</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.8865393411687664</v>
+        <v>1.527034330680061</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.123182885029189</v>
+        <v>0.1136544472932001</v>
       </c>
       <c r="C57">
-        <v>578.0076408567111</v>
+        <v>780.8327206526733</v>
       </c>
       <c r="D57">
-        <v>3003.542640856711</v>
+        <v>3206.367720652673</v>
       </c>
       <c r="E57">
         <v>-445.665</v>
@@ -5967,37 +5967,37 @@
         <v>375.475</v>
       </c>
       <c r="M57">
-        <v>431.3719910461816</v>
+        <v>390.0719630461816</v>
       </c>
       <c r="N57">
-        <v>-55.89699104618154</v>
+        <v>-14.59696304618154</v>
       </c>
       <c r="O57">
-        <v>-11.73836811969812</v>
+        <v>-3.065362239698124</v>
       </c>
       <c r="P57">
-        <v>-44.15862292648342</v>
+        <v>-11.53160080648342</v>
       </c>
       <c r="Q57">
-        <v>239.7413770735166</v>
+        <v>272.3683991935166</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09847456834974486</v>
+        <v>0.09783359560310273</v>
       </c>
       <c r="T57">
-        <v>0.8878682104648399</v>
+        <v>0.8773611744561437</v>
       </c>
       <c r="U57">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V57">
-        <v>0.1827882932518874</v>
+        <v>0.2021415468680193</v>
       </c>
       <c r="W57">
-        <v>0.1433987804941888</v>
+        <v>0.1265987804941888</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8704204440566069</v>
+        <v>0.9625787946096157</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1244796173624397</v>
+        <v>0.1147831796264507</v>
       </c>
       <c r="C58">
-        <v>507.6534536757658</v>
+        <v>710.6689157635783</v>
       </c>
       <c r="D58">
-        <v>2977.885453675766</v>
+        <v>3180.900915763578</v>
       </c>
       <c r="E58">
         <v>-400.9679999999998</v>
@@ -6049,37 +6049,37 @@
         <v>375.475</v>
       </c>
       <c r="M58">
-        <v>439.2151181561121</v>
+        <v>397.1641805561122</v>
       </c>
       <c r="N58">
-        <v>-63.74011815611209</v>
+        <v>-21.68918055611215</v>
       </c>
       <c r="O58">
-        <v>-13.38542481278354</v>
+        <v>-4.554727916783551</v>
       </c>
       <c r="P58">
-        <v>-50.35469334332855</v>
+        <v>-17.1344526393286</v>
       </c>
       <c r="Q58">
-        <v>233.5453066566714</v>
+        <v>266.7655473606714</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09967171763042086</v>
+        <v>0.09901617732135506</v>
       </c>
       <c r="T58">
-        <v>0.9080470334299497</v>
+        <v>0.8973012011483288</v>
       </c>
       <c r="U58">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V58">
-        <v>0.1795242165866752</v>
+        <v>0.1985318763882332</v>
       </c>
       <c r="W58">
-        <v>0.1439715385804545</v>
+        <v>0.1271715385804545</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8548772218413104</v>
+        <v>0.9453898875630153</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1257763496956904</v>
+        <v>0.1159119119597014</v>
       </c>
       <c r="C59">
-        <v>437.7338969526363</v>
+        <v>640.9064669130635</v>
       </c>
       <c r="D59">
-        <v>2952.662896952636</v>
+        <v>3155.835466913064</v>
       </c>
       <c r="E59">
         <v>-356.2709999999997</v>
@@ -6131,37 +6131,37 @@
         <v>375.475</v>
       </c>
       <c r="M59">
-        <v>447.0582452660427</v>
+        <v>404.2563980660428</v>
       </c>
       <c r="N59">
-        <v>-71.5832452660427</v>
+        <v>-28.78139806604275</v>
       </c>
       <c r="O59">
-        <v>-15.03248150586897</v>
+        <v>-6.044093593868978</v>
       </c>
       <c r="P59">
-        <v>-56.55076376017373</v>
+        <v>-22.73730447217378</v>
       </c>
       <c r="Q59">
-        <v>227.3492362398262</v>
+        <v>261.1626955278262</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1009245482729888</v>
+        <v>0.1002537628404563</v>
       </c>
       <c r="T59">
-        <v>0.9291644063004139</v>
+        <v>0.918168670942476</v>
       </c>
       <c r="U59">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V59">
-        <v>0.1763746689272598</v>
+        <v>0.195048861013001</v>
       </c>
       <c r="W59">
-        <v>0.1445241998917635</v>
+        <v>0.1277241998917635</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8398793758440943</v>
+        <v>0.9288041000619097</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.127073082028941</v>
+        <v>0.1170406442929521</v>
       </c>
       <c r="C60">
-        <v>368.2380195413734</v>
+        <v>571.5359602444832</v>
       </c>
       <c r="D60">
-        <v>2927.864019541373</v>
+        <v>3131.161960244483</v>
       </c>
       <c r="E60">
         <v>-311.5740000000001</v>
@@ -6213,37 +6213,37 @@
         <v>375.475</v>
       </c>
       <c r="M60">
-        <v>454.9013723759733</v>
+        <v>411.3486155759733</v>
       </c>
       <c r="N60">
-        <v>-79.42637237597324</v>
+        <v>-35.87361557597325</v>
       </c>
       <c r="O60">
-        <v>-16.67953819895438</v>
+        <v>-7.533459270954381</v>
       </c>
       <c r="P60">
-        <v>-62.74683417701887</v>
+        <v>-28.34015630501887</v>
       </c>
       <c r="Q60">
-        <v>221.1531658229811</v>
+        <v>255.5598436949811</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1022370375175838</v>
+        <v>0.1015502810033243</v>
       </c>
       <c r="T60">
-        <v>0.9512873683551853</v>
+        <v>0.9400298297744395</v>
       </c>
       <c r="U60">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V60">
-        <v>0.1733337263595484</v>
+        <v>0.1916859496162252</v>
       </c>
       <c r="W60">
-        <v>0.1450578039164756</v>
+        <v>0.1282578039164756</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8253986969502307</v>
+        <v>0.9127902362677391</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1283698143621917</v>
+        <v>0.1181693766262028</v>
       </c>
       <c r="C61">
-        <v>299.1552351384926</v>
+        <v>502.5482740215502</v>
       </c>
       <c r="D61">
-        <v>2903.478235138492</v>
+        <v>3106.87127402155</v>
       </c>
       <c r="E61">
         <v>-266.8770000000004</v>
@@ -6295,37 +6295,37 @@
         <v>375.475</v>
       </c>
       <c r="M61">
-        <v>462.7444994859038</v>
+        <v>418.4408330859038</v>
       </c>
       <c r="N61">
-        <v>-87.26949948590374</v>
+        <v>-42.9658330859038</v>
       </c>
       <c r="O61">
-        <v>-18.32659489203978</v>
+        <v>-9.022824948039796</v>
       </c>
       <c r="P61">
-        <v>-68.94290459386396</v>
+        <v>-33.943008137864</v>
       </c>
       <c r="Q61">
-        <v>214.957095406136</v>
+        <v>249.956991862136</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1036135506277687</v>
+        <v>0.1029100439546249</v>
       </c>
       <c r="T61">
-        <v>0.9744894992906775</v>
+        <v>0.9629573865982063</v>
       </c>
       <c r="U61">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V61">
-        <v>0.1703958665907426</v>
+        <v>0.1884370352159502</v>
       </c>
       <c r="W61">
-        <v>0.1455733196691636</v>
+        <v>0.1287733196691636</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8114088885273456</v>
+        <v>0.8973192153140487</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1615939793438217</v>
+        <v>0.1192981089594535</v>
       </c>
       <c r="C62">
-        <v>-256.170204997637</v>
+        <v>433.9345673846133</v>
       </c>
       <c r="D62">
-        <v>2392.849795002362</v>
+        <v>3082.954567384613</v>
       </c>
       <c r="E62">
         <v>-222.1800000000003</v>
@@ -6377,45 +6377,45 @@
         <v>375.475</v>
       </c>
       <c r="M62">
-        <v>610.5786305958344</v>
+        <v>425.5330505958344</v>
       </c>
       <c r="N62">
-        <v>-235.1036305958344</v>
+        <v>-50.0580505958344</v>
       </c>
       <c r="O62">
-        <v>-49.37176242512522</v>
+        <v>-10.51219062512522</v>
       </c>
       <c r="P62">
-        <v>-185.7318681707092</v>
+        <v>-39.54585997070917</v>
       </c>
       <c r="Q62">
-        <v>98.16813182929081</v>
+        <v>244.3541400292908</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1065774710144112</v>
+        <v>0.1043377950534906</v>
       </c>
       <c r="T62">
-        <v>1.024448535920568</v>
+        <v>0.9870313212631614</v>
       </c>
       <c r="U62">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V62">
-        <v>0.129139386884625</v>
+        <v>0.185296417962351</v>
       </c>
       <c r="W62">
-        <v>0.1982716515634287</v>
+        <v>0.1292716515634287</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.6149494613553572</v>
+        <v>0.8823638950588144</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1634127116770724</v>
+        <v>0.1204268412927041</v>
       </c>
       <c r="C63">
-        <v>-323.6840463406784</v>
+        <v>365.6862696223066</v>
       </c>
       <c r="D63">
-        <v>2370.032953659321</v>
+        <v>3059.403269622306</v>
       </c>
       <c r="E63">
         <v>-177.4830000000002</v>
@@ -6459,45 +6459,45 @@
         <v>375.475</v>
       </c>
       <c r="M63">
-        <v>620.7549411057651</v>
+        <v>432.625268105765</v>
       </c>
       <c r="N63">
-        <v>-245.279941105765</v>
+        <v>-57.15026810576495</v>
       </c>
       <c r="O63">
-        <v>-51.50878763221066</v>
+        <v>-12.00155630221064</v>
       </c>
       <c r="P63">
-        <v>-193.7711534735544</v>
+        <v>-45.14871180355431</v>
       </c>
       <c r="Q63">
-        <v>90.12884652644561</v>
+        <v>238.7512881964457</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1081358677070884</v>
+        <v>0.1058387641574262</v>
       </c>
       <c r="T63">
-        <v>1.050716447098018</v>
+        <v>1.012339816680166</v>
       </c>
       <c r="U63">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V63">
-        <v>0.1270223477553689</v>
+        <v>0.1822587717662469</v>
       </c>
       <c r="W63">
-        <v>0.1987536447070622</v>
+        <v>0.1297536447070622</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.6048683226446137</v>
+        <v>0.8678989131726045</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1652314440103231</v>
+        <v>0.1215555736259548</v>
       </c>
       <c r="C64">
-        <v>-390.7668611165268</v>
+        <v>297.7950699311873</v>
       </c>
       <c r="D64">
-        <v>2347.647138883473</v>
+        <v>3036.209069931187</v>
       </c>
       <c r="E64">
         <v>-132.7860000000001</v>
@@ -6541,45 +6541,45 @@
         <v>375.475</v>
       </c>
       <c r="M64">
-        <v>630.9312516156956</v>
+        <v>439.7174856156956</v>
       </c>
       <c r="N64">
-        <v>-255.4562516156956</v>
+        <v>-64.24248561569556</v>
       </c>
       <c r="O64">
-        <v>-53.64581283929607</v>
+        <v>-13.49092197929607</v>
       </c>
       <c r="P64">
-        <v>-201.8104387763995</v>
+        <v>-50.75156363639949</v>
       </c>
       <c r="Q64">
-        <v>82.08956122360047</v>
+        <v>233.1484363636005</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1097762852783276</v>
+        <v>0.1074187316352532</v>
       </c>
       <c r="T64">
-        <v>1.078366879916387</v>
+        <v>1.038980338171749</v>
       </c>
       <c r="U64">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V64">
-        <v>0.1249736002109274</v>
+        <v>0.1793191141571139</v>
       </c>
       <c r="W64">
-        <v>0.199220089684772</v>
+        <v>0.1302200896847719</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.5951123819567973</v>
+        <v>0.8539005436053043</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1670501763435738</v>
+        <v>0.1226843059592055</v>
       </c>
       <c r="C65">
-        <v>-457.4307486461998</v>
+        <v>230.2529076376959</v>
       </c>
       <c r="D65">
-        <v>2325.6802513538</v>
+        <v>3013.363907637696</v>
       </c>
       <c r="E65">
         <v>-88.08899999999994</v>
@@ -6623,45 +6623,45 @@
         <v>375.475</v>
       </c>
       <c r="M65">
-        <v>641.1075621256263</v>
+        <v>446.8097031256262</v>
       </c>
       <c r="N65">
-        <v>-265.6325621256262</v>
+        <v>-71.33470312562616</v>
       </c>
       <c r="O65">
-        <v>-55.78283804638151</v>
+        <v>-14.98028765638149</v>
       </c>
       <c r="P65">
-        <v>-209.8497240792447</v>
+        <v>-56.35441546924467</v>
       </c>
       <c r="Q65">
-        <v>74.05027592075524</v>
+        <v>227.5455845307553</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1115053740696338</v>
+        <v>0.1090841027605303</v>
       </c>
       <c r="T65">
-        <v>1.107511930724938</v>
+        <v>1.067060887852067</v>
       </c>
       <c r="U65">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V65">
-        <v>0.1229898922710714</v>
+        <v>0.1764727790117629</v>
       </c>
       <c r="W65">
-        <v>0.1996717268854116</v>
+        <v>0.1306717268854116</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.5856661536717687</v>
+        <v>0.8403465667226804</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1688689086768244</v>
+        <v>0.1238130382924562</v>
       </c>
       <c r="C66">
-        <v>-523.6873595963425</v>
+        <v>163.0519628582451</v>
       </c>
       <c r="D66">
-        <v>2304.120640403657</v>
+        <v>2990.859962858245</v>
       </c>
       <c r="E66">
         <v>-43.39200000000028</v>
@@ -6705,45 +6705,45 @@
         <v>375.475</v>
       </c>
       <c r="M66">
-        <v>651.2838726355567</v>
+        <v>453.9019206355567</v>
       </c>
       <c r="N66">
-        <v>-275.8088726355567</v>
+        <v>-78.42692063555666</v>
       </c>
       <c r="O66">
-        <v>-57.9198632534669</v>
+        <v>-16.4696533334669</v>
       </c>
       <c r="P66">
-        <v>-217.8890093820898</v>
+        <v>-61.95726730208976</v>
       </c>
       <c r="Q66">
-        <v>66.01099061791021</v>
+        <v>221.9427326979102</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1133305233493458</v>
+        <v>0.1108419945038784</v>
       </c>
       <c r="T66">
-        <v>1.138276151022853</v>
+        <v>1.096701468070179</v>
       </c>
       <c r="U66">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V66">
-        <v>0.121068175204336</v>
+        <v>0.1737153918397041</v>
       </c>
       <c r="W66">
-        <v>0.2001092504235312</v>
+        <v>0.1311092504235312</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.5765151200206474</v>
+        <v>0.8272161516176386</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1706876410100752</v>
+        <v>0.1249417706257069</v>
       </c>
       <c r="C67">
-        <v>-589.5479165838847</v>
+        <v>96.18464757470974</v>
       </c>
       <c r="D67">
-        <v>2282.957083416115</v>
+        <v>2968.689647574709</v>
       </c>
       <c r="E67">
         <v>1.304999999999836</v>
@@ -6787,45 +6787,45 @@
         <v>375.475</v>
       </c>
       <c r="M67">
-        <v>661.4601831454873</v>
+        <v>460.9941381454873</v>
       </c>
       <c r="N67">
-        <v>-285.9851831454873</v>
+        <v>-85.51913814548726</v>
       </c>
       <c r="O67">
-        <v>-60.05688846055234</v>
+        <v>-17.95901901055232</v>
       </c>
       <c r="P67">
-        <v>-225.928294684935</v>
+        <v>-67.56011913493494</v>
       </c>
       <c r="Q67">
-        <v>57.97170531506498</v>
+        <v>216.339880865065</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1152599668736128</v>
+        <v>0.1127003372039892</v>
       </c>
       <c r="T67">
-        <v>1.170798326766363</v>
+        <v>1.128035795729328</v>
       </c>
       <c r="U67">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V67">
-        <v>0.1192055878935</v>
+        <v>0.1710428473498625</v>
       </c>
       <c r="W67">
-        <v>0.2005333116989395</v>
+        <v>0.1315333116989395</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5676456566357143</v>
+        <v>0.8144897492850595</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1725063733433259</v>
+        <v>0.1260705029589576</v>
       </c>
       <c r="C68">
-        <v>-655.0232336554909</v>
+        <v>29.64359710393683</v>
       </c>
       <c r="D68">
-        <v>2262.178766344509</v>
+        <v>2946.845597103937</v>
       </c>
       <c r="E68">
         <v>46.00199999999995</v>
@@ -6869,45 +6869,45 @@
         <v>375.475</v>
       </c>
       <c r="M68">
-        <v>671.6364936554179</v>
+        <v>468.0863556554179</v>
       </c>
       <c r="N68">
-        <v>-296.1614936554179</v>
+        <v>-92.61135565541787</v>
       </c>
       <c r="O68">
-        <v>-62.19391366763775</v>
+        <v>-19.44838468763775</v>
       </c>
       <c r="P68">
-        <v>-233.9675799877801</v>
+        <v>-73.16297096778011</v>
       </c>
       <c r="Q68">
-        <v>49.93242001221986</v>
+        <v>210.7370290322199</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.117302907075778</v>
+        <v>0.1146679941805771</v>
       </c>
       <c r="T68">
-        <v>1.205233571671256</v>
+        <v>1.161213319133131</v>
       </c>
       <c r="U68">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V68">
-        <v>0.1173994426223864</v>
+        <v>0.1684512890566827</v>
       </c>
       <c r="W68">
-        <v>0.2009445226326687</v>
+        <v>0.1319445226326687</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.5590449648685065</v>
+        <v>0.8021489955080131</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1743251056765765</v>
+        <v>0.1641229060125067</v>
       </c>
       <c r="C69">
-        <v>-720.123734712864</v>
+        <v>-600.7610099005137</v>
       </c>
       <c r="D69">
-        <v>2241.775265287136</v>
+        <v>2361.137990099486</v>
       </c>
       <c r="E69">
         <v>90.69900000000007</v>
@@ -6951,37 +6951,37 @@
         <v>375.475</v>
       </c>
       <c r="M69">
-        <v>681.8128041653486</v>
+        <v>636.8923191653485</v>
       </c>
       <c r="N69">
-        <v>-306.3378041653485</v>
+        <v>-261.4173191653484</v>
       </c>
       <c r="O69">
-        <v>-64.33093887472319</v>
+        <v>-54.89763702472317</v>
       </c>
       <c r="P69">
-        <v>-242.0068652906253</v>
+        <v>-206.5196821406253</v>
       </c>
       <c r="Q69">
-        <v>41.89313470937464</v>
+        <v>77.38031785937471</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.11946966183565</v>
+        <v>0.1190084507324082</v>
       </c>
       <c r="T69">
-        <v>1.24175580111584</v>
+        <v>1.234399652190678</v>
       </c>
       <c r="U69">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V69">
-        <v>0.1156472121354851</v>
+        <v>0.1238038953010662</v>
       </c>
       <c r="W69">
-        <v>0.2013434586131523</v>
+        <v>0.1863434586131522</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5507010101689765</v>
+        <v>0.5895423585765054</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1761438380098272</v>
+        <v>0.1657916383457574</v>
       </c>
       <c r="C70">
-        <v>-784.8594709498466</v>
+        <v>-665.8603715581858</v>
       </c>
       <c r="D70">
-        <v>2221.736529050153</v>
+        <v>2340.735628441814</v>
       </c>
       <c r="E70">
         <v>135.3960000000002</v>
@@ -7033,37 +7033,37 @@
         <v>375.475</v>
       </c>
       <c r="M70">
-        <v>691.9891146752791</v>
+        <v>646.3981746752791</v>
       </c>
       <c r="N70">
-        <v>-316.5141146752791</v>
+        <v>-270.923174675279</v>
       </c>
       <c r="O70">
-        <v>-66.4679640818086</v>
+        <v>-56.8938666818086</v>
       </c>
       <c r="P70">
-        <v>-250.0461505934705</v>
+        <v>-214.0293079934704</v>
       </c>
       <c r="Q70">
-        <v>33.85384940652949</v>
+        <v>69.87069200652954</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1217718387680141</v>
+        <v>0.121296214817796</v>
       </c>
       <c r="T70">
-        <v>1.28056066990071</v>
+        <v>1.272974641321637</v>
       </c>
       <c r="U70">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V70">
-        <v>0.113946517839375</v>
+        <v>0.1219832497819328</v>
       </c>
       <c r="W70">
-        <v>0.2017306611824451</v>
+        <v>0.1867306611824451</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5426024659017857</v>
+        <v>0.5808726180092039</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1779625703430779</v>
+        <v>0.1674603706790081</v>
       </c>
       <c r="C71">
-        <v>-849.2401373626044</v>
+        <v>-730.6101641977193</v>
       </c>
       <c r="D71">
-        <v>2202.052862637396</v>
+        <v>2320.682835802281</v>
       </c>
       <c r="E71">
         <v>180.0930000000003</v>
@@ -7115,37 +7115,37 @@
         <v>375.475</v>
       </c>
       <c r="M71">
-        <v>702.1654251852098</v>
+        <v>655.9040301852096</v>
       </c>
       <c r="N71">
-        <v>-326.6904251852097</v>
+        <v>-280.4290301852096</v>
       </c>
       <c r="O71">
-        <v>-68.60498928889405</v>
+        <v>-58.89009633889402</v>
       </c>
       <c r="P71">
-        <v>-258.0854358963157</v>
+        <v>-221.5389338463156</v>
       </c>
       <c r="Q71">
-        <v>25.81456410368429</v>
+        <v>62.36106615368436</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1242225432444016</v>
+        <v>0.123731576586112</v>
       </c>
       <c r="T71">
-        <v>1.321869078607184</v>
+        <v>1.314038339428786</v>
       </c>
       <c r="U71">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V71">
-        <v>0.1122951190301087</v>
+        <v>0.1202153765966874</v>
       </c>
       <c r="W71">
-        <v>0.20210664048886</v>
+        <v>0.18710664048886</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5347386620481366</v>
+        <v>0.5724541742699401</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1797813026763286</v>
+        <v>0.1691291030122588</v>
       </c>
       <c r="C72">
-        <v>-913.2750883898811</v>
+        <v>-795.0192956504607</v>
       </c>
       <c r="D72">
-        <v>2182.714911610119</v>
+        <v>2300.970704349539</v>
       </c>
       <c r="E72">
         <v>224.79</v>
@@ -7197,37 +7197,37 @@
         <v>375.475</v>
       </c>
       <c r="M72">
-        <v>712.3417356951402</v>
+        <v>665.4098856951401</v>
       </c>
       <c r="N72">
-        <v>-336.8667356951402</v>
+        <v>-289.9348856951401</v>
       </c>
       <c r="O72">
-        <v>-70.74201449597943</v>
+        <v>-60.88632599597942</v>
       </c>
       <c r="P72">
-        <v>-266.1247211991607</v>
+        <v>-229.0485596991607</v>
       </c>
       <c r="Q72">
-        <v>17.77527880083926</v>
+        <v>54.85144030083927</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.126836628019215</v>
+        <v>0.126329295805649</v>
       </c>
       <c r="T72">
-        <v>1.365931381227424</v>
+        <v>1.357839617409746</v>
       </c>
       <c r="U72">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V72">
-        <v>0.1106909030439643</v>
+        <v>0.1184980140738776</v>
       </c>
       <c r="W72">
-        <v>0.2024718775293772</v>
+        <v>0.1874718775293772</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5270995383045919</v>
+        <v>0.5642762574946553</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1816000350095792</v>
+        <v>0.1707978353455094</v>
       </c>
       <c r="C73">
-        <v>-976.9733527363337</v>
+        <v>-859.0963736405638</v>
       </c>
       <c r="D73">
-        <v>2163.713647263666</v>
+        <v>2281.590626359436</v>
       </c>
       <c r="E73">
         <v>269.4869999999996</v>
@@ -7279,37 +7279,37 @@
         <v>375.475</v>
       </c>
       <c r="M73">
-        <v>722.5180462050707</v>
+        <v>674.9157412050706</v>
       </c>
       <c r="N73">
-        <v>-347.0430462050707</v>
+        <v>-299.4407412050706</v>
       </c>
       <c r="O73">
-        <v>-72.87903970306485</v>
+        <v>-62.88255565306482</v>
       </c>
       <c r="P73">
-        <v>-274.1640065020059</v>
+        <v>-236.5581855520058</v>
       </c>
       <c r="Q73">
-        <v>9.735993497994116</v>
+        <v>47.34181444799421</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1296309945026362</v>
+        <v>0.1291061680748093</v>
       </c>
       <c r="T73">
-        <v>1.413032463338714</v>
+        <v>1.404661673182495</v>
       </c>
       <c r="U73">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V73">
-        <v>0.1091318762405282</v>
+        <v>0.116829027960161</v>
       </c>
       <c r="W73">
-        <v>0.202826826202556</v>
+        <v>0.187826826202556</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5196756011453723</v>
+        <v>0.5563287045721954</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1834187673428299</v>
+        <v>0.1724665676787601</v>
       </c>
       <c r="C74">
-        <v>-1040.343647428291</v>
+        <v>-922.8497183177883</v>
       </c>
       <c r="D74">
-        <v>2145.040352571709</v>
+        <v>2262.534281682211</v>
       </c>
       <c r="E74">
         <v>314.1839999999997</v>
@@ -7361,37 +7361,37 @@
         <v>375.475</v>
       </c>
       <c r="M74">
-        <v>732.6943567150013</v>
+        <v>684.4215967150012</v>
       </c>
       <c r="N74">
-        <v>-357.2193567150013</v>
+        <v>-308.9465967150012</v>
       </c>
       <c r="O74">
-        <v>-75.01606491015026</v>
+        <v>-64.87878531015025</v>
       </c>
       <c r="P74">
-        <v>-282.203291804851</v>
+        <v>-244.0678114048509</v>
       </c>
       <c r="Q74">
-        <v>1.696708195148972</v>
+        <v>39.83218859514903</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.132624958592016</v>
+        <v>0.1320813883631954</v>
       </c>
       <c r="T74">
-        <v>1.463497908457954</v>
+        <v>1.454828161510442</v>
       </c>
       <c r="U74">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V74">
-        <v>0.1076161557371875</v>
+        <v>0.1152064025718254</v>
       </c>
       <c r="W74">
-        <v>0.2031719151903686</v>
+        <v>0.1881719151903686</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5124578844627977</v>
+        <v>0.5486019170086927</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1852374996760806</v>
+        <v>0.1741353000120108</v>
       </c>
       <c r="C75">
-        <v>-1103.394391147916</v>
+        <v>-986.2873741674548</v>
       </c>
       <c r="D75">
-        <v>2126.686608852084</v>
+        <v>2243.793625832545</v>
       </c>
       <c r="E75">
         <v>358.8809999999999</v>
@@ -7443,37 +7443,37 @@
         <v>375.475</v>
       </c>
       <c r="M75">
-        <v>742.8706672249319</v>
+        <v>693.9274522249318</v>
       </c>
       <c r="N75">
-        <v>-367.3956672249319</v>
+        <v>-318.4524522249318</v>
       </c>
       <c r="O75">
-        <v>-77.15309011723569</v>
+        <v>-66.87501496723567</v>
       </c>
       <c r="P75">
-        <v>-290.2425771076962</v>
+        <v>-251.5774372576961</v>
       </c>
       <c r="Q75">
-        <v>-6.342577107696229</v>
+        <v>32.32256274230386</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1358406977991277</v>
+        <v>0.13527699533961</v>
       </c>
       <c r="T75">
-        <v>1.517701534697137</v>
+        <v>1.508710686010828</v>
       </c>
       <c r="U75">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V75">
-        <v>0.1061419618229795</v>
+        <v>0.1136282326735813</v>
       </c>
       <c r="W75">
-        <v>0.2035075496853646</v>
+        <v>0.1885075496853645</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5054379134427593</v>
+        <v>0.5410868222551489</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2094939655474906</v>
+        <v>0.1758040323452615</v>
       </c>
       <c r="C76">
-        <v>-1365.922988666498</v>
+        <v>-1049.417121333343</v>
       </c>
       <c r="D76">
-        <v>1908.855011333502</v>
+        <v>2225.360878666657</v>
       </c>
       <c r="E76">
         <v>403.578</v>
@@ -7525,45 +7525,45 @@
         <v>375.475</v>
       </c>
       <c r="M76">
-        <v>852.2743177348624</v>
+        <v>703.4333077348624</v>
       </c>
       <c r="N76">
-        <v>-476.7993177348624</v>
+        <v>-327.9583077348624</v>
       </c>
       <c r="O76">
-        <v>-100.1278567243211</v>
+        <v>-68.87124462432109</v>
       </c>
       <c r="P76">
-        <v>-376.6714610105413</v>
+        <v>-259.0870631105413</v>
       </c>
       <c r="Q76">
-        <v>-92.77146101054132</v>
+        <v>24.81293688945868</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1402181613227838</v>
+        <v>0.1387184182372873</v>
       </c>
       <c r="T76">
-        <v>1.591486870332307</v>
+        <v>1.566738020088168</v>
       </c>
       <c r="U76">
-        <v>0.2576732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V76">
-        <v>0.09251686735036606</v>
+        <v>0.1120927160158302</v>
       </c>
       <c r="W76">
-        <v>0.2338341129777929</v>
+        <v>0.188834112977793</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.4405565111922194</v>
+        <v>0.5337748381706199</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2116126978807413</v>
+        <v>0.1774727646785122</v>
       </c>
       <c r="C77">
-        <v>-1427.546624088264</v>
+        <v>-1112.246486387045</v>
       </c>
       <c r="D77">
-        <v>1891.928375911736</v>
+        <v>2207.228513612954</v>
       </c>
       <c r="E77">
         <v>448.2749999999996</v>
@@ -7607,45 +7607,45 @@
         <v>375.475</v>
       </c>
       <c r="M77">
-        <v>863.7915382447929</v>
+        <v>712.939163244793</v>
       </c>
       <c r="N77">
-        <v>-488.3165382447929</v>
+        <v>-337.464163244793</v>
       </c>
       <c r="O77">
-        <v>-102.5464730314065</v>
+        <v>-70.86747428140653</v>
       </c>
       <c r="P77">
-        <v>-385.7700652133864</v>
+        <v>-266.5966889633864</v>
       </c>
       <c r="Q77">
-        <v>-101.8700652133865</v>
+        <v>17.30331103661354</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1439948877756952</v>
+        <v>0.1424351549667788</v>
       </c>
       <c r="T77">
-        <v>1.655146345145599</v>
+        <v>1.629407540891695</v>
       </c>
       <c r="U77">
-        <v>0.2576732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V77">
-        <v>0.09128330911902785</v>
+        <v>0.1105981464689524</v>
       </c>
       <c r="W77">
-        <v>0.2341519679157566</v>
+        <v>0.1891519679157566</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4346824243763231</v>
+        <v>0.5266578403283448</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2137314302139919</v>
+        <v>0.1791414970117629</v>
       </c>
       <c r="C78">
-        <v>-1488.872706579058</v>
+        <v>-1174.782752575074</v>
       </c>
       <c r="D78">
-        <v>1875.299293420942</v>
+        <v>2189.389247424926</v>
       </c>
       <c r="E78">
         <v>492.9719999999998</v>
@@ -7689,45 +7689,45 @@
         <v>375.475</v>
       </c>
       <c r="M78">
-        <v>875.3087587547235</v>
+        <v>722.4450187547236</v>
       </c>
       <c r="N78">
-        <v>-499.8337587547235</v>
+        <v>-346.9700187547236</v>
       </c>
       <c r="O78">
-        <v>-104.9650893384919</v>
+        <v>-72.86370393849195</v>
       </c>
       <c r="P78">
-        <v>-394.8686694162316</v>
+        <v>-274.1063148162316</v>
       </c>
       <c r="Q78">
-        <v>-110.9686694162316</v>
+        <v>9.793685183768332</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1480863414330158</v>
+        <v>0.1464616197570613</v>
       </c>
       <c r="T78">
-        <v>1.724110776193333</v>
+        <v>1.697299521762182</v>
       </c>
       <c r="U78">
-        <v>0.2576732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V78">
-        <v>0.09008221294640907</v>
+        <v>0.1091429076996241</v>
       </c>
       <c r="W78">
-        <v>0.2344614582500897</v>
+        <v>0.1894614582500897</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.4289629187924241</v>
+        <v>0.519728131902972</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2158501625472426</v>
+        <v>0.1808102293450135</v>
       </c>
       <c r="C79">
-        <v>-1549.909013791389</v>
+        <v>-1237.032969573036</v>
       </c>
       <c r="D79">
-        <v>1858.959986208611</v>
+        <v>2171.836030426964</v>
       </c>
       <c r="E79">
         <v>537.6689999999999</v>
@@ -7771,45 +7771,45 @@
         <v>375.475</v>
       </c>
       <c r="M79">
-        <v>886.8259792646541</v>
+        <v>731.9508742646542</v>
       </c>
       <c r="N79">
-        <v>-511.350979264654</v>
+        <v>-356.4758742646542</v>
       </c>
       <c r="O79">
-        <v>-107.3837056455773</v>
+        <v>-74.85993359557737</v>
       </c>
       <c r="P79">
-        <v>-403.9672736190767</v>
+        <v>-281.6159406690768</v>
       </c>
       <c r="Q79">
-        <v>-120.0672736190767</v>
+        <v>2.284059330923185</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1525335736692339</v>
+        <v>0.1508382119204118</v>
       </c>
       <c r="T79">
-        <v>1.799072114288695</v>
+        <v>1.771095153143147</v>
       </c>
       <c r="U79">
-        <v>0.2576732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V79">
-        <v>0.08891231407697518</v>
+        <v>0.1077254673398887</v>
       </c>
       <c r="W79">
-        <v>0.23476290987444</v>
+        <v>0.18976290987444</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4233919717951199</v>
+        <v>0.5129784159042321</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2179688948804933</v>
+        <v>0.1824789616782642</v>
       </c>
       <c r="C80">
-        <v>-1610.663054655287</v>
+        <v>-1299.003962774325</v>
       </c>
       <c r="D80">
-        <v>1842.902945344713</v>
+        <v>2154.562037225675</v>
       </c>
       <c r="E80">
         <v>582.366</v>
@@ -7853,45 +7853,45 @@
         <v>375.475</v>
       </c>
       <c r="M80">
-        <v>898.3431997745847</v>
+        <v>741.4567297745848</v>
       </c>
       <c r="N80">
-        <v>-522.8681997745847</v>
+        <v>-365.9817297745848</v>
       </c>
       <c r="O80">
-        <v>-109.8023219526628</v>
+        <v>-76.8561632526628</v>
       </c>
       <c r="P80">
-        <v>-413.0658778219219</v>
+        <v>-289.125566521922</v>
       </c>
       <c r="Q80">
-        <v>-129.1658778219219</v>
+        <v>-5.225566521922019</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1573850997451082</v>
+        <v>0.1556126760986123</v>
       </c>
       <c r="T80">
-        <v>1.880848119483636</v>
+        <v>1.851599478286017</v>
       </c>
       <c r="U80">
-        <v>0.2576732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V80">
-        <v>0.08777241261444985</v>
+        <v>0.1063443716047619</v>
       </c>
       <c r="W80">
-        <v>0.2350566319699609</v>
+        <v>0.1900566319699609</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.4179638695926183</v>
+        <v>0.5064017695464854</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.220087627213744</v>
+        <v>0.2121064956280281</v>
       </c>
       <c r="C81">
-        <v>-1671.142080884563</v>
+        <v>-1610.305075893431</v>
       </c>
       <c r="D81">
-        <v>1827.120919115438</v>
+        <v>1887.957924106569</v>
       </c>
       <c r="E81">
         <v>627.0630000000001</v>
@@ -7935,37 +7935,37 @@
         <v>375.475</v>
       </c>
       <c r="M81">
-        <v>909.8604202845153</v>
+        <v>874.5497902845153</v>
       </c>
       <c r="N81">
-        <v>-534.3854202845152</v>
+        <v>-499.0747902845153</v>
       </c>
       <c r="O81">
-        <v>-112.2209382597482</v>
+        <v>-104.8057059597482</v>
       </c>
       <c r="P81">
-        <v>-422.164482024767</v>
+        <v>-394.2690843247671</v>
       </c>
       <c r="Q81">
-        <v>-138.2644820247671</v>
+        <v>-110.3690843247671</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1626986759234467</v>
+        <v>0.1623123350390853</v>
       </c>
       <c r="T81">
-        <v>1.970412315649523</v>
+        <v>1.964565352897198</v>
       </c>
       <c r="U81">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V81">
-        <v>0.0866613694167986</v>
+        <v>0.09016038980965051</v>
       </c>
       <c r="W81">
-        <v>0.2353429180630635</v>
+        <v>0.2253429180630636</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4126731876990409</v>
+        <v>0.4293351895697644</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2222063595469947</v>
+        <v>0.2141252279612788</v>
       </c>
       <c r="C82">
-        <v>-1731.353097896881</v>
+        <v>-1670.786803786481</v>
       </c>
       <c r="D82">
-        <v>1811.60690210312</v>
+        <v>1872.17319621352</v>
       </c>
       <c r="E82">
         <v>671.7600000000002</v>
@@ -8017,37 +8017,37 @@
         <v>375.475</v>
       </c>
       <c r="M82">
-        <v>921.3776407944459</v>
+        <v>885.620040794446</v>
       </c>
       <c r="N82">
-        <v>-545.9026407944459</v>
+        <v>-510.145040794446</v>
       </c>
       <c r="O82">
-        <v>-114.6395545668336</v>
+        <v>-107.1304585668337</v>
       </c>
       <c r="P82">
-        <v>-431.2630862276123</v>
+        <v>-403.0145822276123</v>
       </c>
       <c r="Q82">
-        <v>-147.3630862276123</v>
+        <v>-119.1145822276123</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.168543609719619</v>
+        <v>0.1681379517910396</v>
       </c>
       <c r="T82">
-        <v>2.068932931432</v>
+        <v>2.062793620542058</v>
       </c>
       <c r="U82">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V82">
-        <v>0.08557810229908859</v>
+        <v>0.08903338493702986</v>
       </c>
       <c r="W82">
-        <v>0.2356220470038386</v>
+        <v>0.2256220470038386</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4075147728528029</v>
+        <v>0.4239684997001422</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2243250918802453</v>
+        <v>0.2161439602945295</v>
       </c>
       <c r="C83">
-        <v>-1791.302875182174</v>
+        <v>-1731.006776095711</v>
       </c>
       <c r="D83">
-        <v>1796.354124817826</v>
+        <v>1856.650223904289</v>
       </c>
       <c r="E83">
         <v>716.4569999999999</v>
@@ -8099,37 +8099,37 @@
         <v>375.475</v>
       </c>
       <c r="M83">
-        <v>932.8948613043764</v>
+        <v>896.6902913043765</v>
       </c>
       <c r="N83">
-        <v>-557.4198613043764</v>
+        <v>-521.2152913043765</v>
       </c>
       <c r="O83">
-        <v>-117.058170873919</v>
+        <v>-109.4552111739191</v>
       </c>
       <c r="P83">
-        <v>-440.3616904304573</v>
+        <v>-411.7600801304574</v>
       </c>
       <c r="Q83">
-        <v>-156.4616904304573</v>
+        <v>-127.8600801304574</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1750037997048621</v>
+        <v>0.174576791358989</v>
       </c>
       <c r="T83">
-        <v>2.177824138349473</v>
+        <v>2.171361705833745</v>
       </c>
       <c r="U83">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V83">
-        <v>0.08452158251761838</v>
+        <v>0.08793420734521469</v>
       </c>
       <c r="W83">
-        <v>0.2358942838720019</v>
+        <v>0.2258942838720019</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4024837262743732</v>
+        <v>0.4187343206914985</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.226443824213496</v>
+        <v>0.2181626926277802</v>
       </c>
       <c r="C84">
-        <v>-1850.997956151666</v>
+        <v>-1790.97145025545</v>
       </c>
       <c r="D84">
-        <v>1781.356043848334</v>
+        <v>1841.38254974455</v>
       </c>
       <c r="E84">
         <v>761.154</v>
@@ -8181,37 +8181,37 @@
         <v>375.475</v>
       </c>
       <c r="M84">
-        <v>944.412081814307</v>
+        <v>907.7605418143071</v>
       </c>
       <c r="N84">
-        <v>-568.937081814307</v>
+        <v>-532.2855418143071</v>
       </c>
       <c r="O84">
-        <v>-119.4767871810045</v>
+        <v>-111.7799637810045</v>
       </c>
       <c r="P84">
-        <v>-449.4602946333026</v>
+        <v>-420.5055780333026</v>
       </c>
       <c r="Q84">
-        <v>-165.5602946333026</v>
+        <v>-136.6055780333026</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1821817885773545</v>
+        <v>0.1817310575455995</v>
       </c>
       <c r="T84">
-        <v>2.298814368257777</v>
+        <v>2.291992911713398</v>
       </c>
       <c r="U84">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V84">
-        <v>0.08349083151130596</v>
+        <v>0.08686183896295598</v>
       </c>
       <c r="W84">
-        <v>0.2361598808165515</v>
+        <v>0.2261598808165515</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.397575388149076</v>
+        <v>0.4136278045855046</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2285625565467467</v>
+        <v>0.2201814249610309</v>
       </c>
       <c r="C85">
-        <v>-1910.444667497571</v>
+        <v>-1850.687073028387</v>
       </c>
       <c r="D85">
-        <v>1766.606332502429</v>
+        <v>1826.363926971614</v>
       </c>
       <c r="E85">
         <v>805.8510000000001</v>
@@ -8263,37 +8263,37 @@
         <v>375.475</v>
       </c>
       <c r="M85">
-        <v>955.9293023242376</v>
+        <v>918.8307923242377</v>
       </c>
       <c r="N85">
-        <v>-580.4543023242376</v>
+        <v>-543.3557923242377</v>
       </c>
       <c r="O85">
-        <v>-121.8954034880899</v>
+        <v>-114.1047163880899</v>
       </c>
       <c r="P85">
-        <v>-458.5588988361477</v>
+        <v>-429.2510759361477</v>
       </c>
       <c r="Q85">
-        <v>-174.6588988361477</v>
+        <v>-145.3510759361478</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1902042467289635</v>
+        <v>0.1897270021071054</v>
       </c>
       <c r="T85">
-        <v>2.434038742861176</v>
+        <v>2.426816024167127</v>
       </c>
       <c r="U85">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V85">
-        <v>0.08248491787863962</v>
+        <v>0.08581531078267939</v>
       </c>
       <c r="W85">
-        <v>0.2364190778347264</v>
+        <v>0.2264190778347264</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3927853232316172</v>
+        <v>0.4086443370603781</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2306812888799974</v>
+        <v>0.2222001572942815</v>
       </c>
       <c r="C86">
-        <v>-1969.649128091638</v>
+        <v>-1910.159689027424</v>
       </c>
       <c r="D86">
-        <v>1752.098871908362</v>
+        <v>1811.588310972576</v>
       </c>
       <c r="E86">
         <v>850.5479999999998</v>
@@ -8345,37 +8345,37 @@
         <v>375.475</v>
       </c>
       <c r="M86">
-        <v>967.446522834168</v>
+        <v>929.9010428341682</v>
       </c>
       <c r="N86">
-        <v>-591.971522834168</v>
+        <v>-554.4260428341681</v>
       </c>
       <c r="O86">
-        <v>-124.3140197951753</v>
+        <v>-116.4294689951753</v>
       </c>
       <c r="P86">
-        <v>-467.6575030389927</v>
+        <v>-437.9965738389928</v>
       </c>
       <c r="Q86">
-        <v>-183.7575030389928</v>
+        <v>-154.0965738389929</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1992295121495237</v>
+        <v>0.1987224397387994</v>
       </c>
       <c r="T86">
-        <v>2.586166164289998</v>
+        <v>2.578492025677571</v>
       </c>
       <c r="U86">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V86">
-        <v>0.08150295457056059</v>
+        <v>0.08479369994002846</v>
       </c>
       <c r="W86">
-        <v>0.2366721034953257</v>
+        <v>0.2266721034953257</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.38810930747886</v>
+        <v>0.4037795235239451</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2328000212132481</v>
+        <v>0.2242188896275322</v>
       </c>
       <c r="C87">
-        <v>-2028.617257448808</v>
+        <v>-1969.395148827212</v>
       </c>
       <c r="D87">
-        <v>1737.827742551192</v>
+        <v>1797.049851172788</v>
       </c>
       <c r="E87">
         <v>895.2449999999999</v>
@@ -8427,37 +8427,37 @@
         <v>375.475</v>
       </c>
       <c r="M87">
-        <v>978.9637433440987</v>
+        <v>940.9712933440987</v>
       </c>
       <c r="N87">
-        <v>-603.4887433440987</v>
+        <v>-565.4962933440987</v>
       </c>
       <c r="O87">
-        <v>-126.7326361022607</v>
+        <v>-118.7542216022607</v>
       </c>
       <c r="P87">
-        <v>-476.756107241838</v>
+        <v>-446.742071741838</v>
       </c>
       <c r="Q87">
-        <v>-192.856107241838</v>
+        <v>-162.842071741838</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2094581462928253</v>
+        <v>0.2089172690547194</v>
       </c>
       <c r="T87">
-        <v>2.758577241909332</v>
+        <v>2.750391494056076</v>
       </c>
       <c r="U87">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V87">
-        <v>0.08054409628149516</v>
+        <v>0.08379612699955753</v>
       </c>
       <c r="W87">
-        <v>0.2369191756109697</v>
+        <v>0.2269191756109697</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3835433156261674</v>
+        <v>0.3990291761883692</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2349187535464988</v>
+        <v>0.2262376219607829</v>
       </c>
       <c r="C88">
-        <v>-2087.354783780584</v>
+        <v>-2028.399116688178</v>
       </c>
       <c r="D88">
-        <v>1723.787216219416</v>
+        <v>1782.742883311822</v>
       </c>
       <c r="E88">
         <v>939.942</v>
@@ -8509,37 +8509,37 @@
         <v>375.475</v>
       </c>
       <c r="M88">
-        <v>990.4809638540293</v>
+        <v>952.0415438540293</v>
       </c>
       <c r="N88">
-        <v>-615.0059638540292</v>
+        <v>-576.5665438540293</v>
       </c>
       <c r="O88">
-        <v>-129.1512524093461</v>
+        <v>-121.0789742093461</v>
       </c>
       <c r="P88">
-        <v>-485.8547114446831</v>
+        <v>-455.4875696446832</v>
       </c>
       <c r="Q88">
-        <v>-201.9547114446831</v>
+        <v>-171.5875696446832</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.22114801388517</v>
+        <v>0.2205685025586279</v>
       </c>
       <c r="T88">
-        <v>2.955618473474285</v>
+        <v>2.946848029345796</v>
       </c>
       <c r="U88">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V88">
-        <v>0.07960753702240801</v>
+        <v>0.08282175342979523</v>
       </c>
       <c r="W88">
-        <v>0.2371605018634593</v>
+        <v>0.2271605018634593</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3790835096305143</v>
+        <v>0.394389302046644</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2370374858797494</v>
+        <v>0.2282563542940336</v>
       </c>
       <c r="C89">
-        <v>-2145.867251661133</v>
+        <v>-2087.177077914532</v>
       </c>
       <c r="D89">
-        <v>1709.971748338867</v>
+        <v>1768.661922085467</v>
       </c>
       <c r="E89">
         <v>984.6389999999997</v>
@@ -8591,37 +8591,37 @@
         <v>375.475</v>
       </c>
       <c r="M89">
-        <v>1001.99818436396</v>
+        <v>963.1117943639598</v>
       </c>
       <c r="N89">
-        <v>-626.5231843639598</v>
+        <v>-587.6367943639598</v>
       </c>
       <c r="O89">
-        <v>-131.5698687164316</v>
+        <v>-123.4037268164315</v>
       </c>
       <c r="P89">
-        <v>-494.9533156475283</v>
+        <v>-464.2330675475282</v>
       </c>
       <c r="Q89">
-        <v>-211.0533156475283</v>
+        <v>-180.3330675475282</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2346363226455676</v>
+        <v>0.2340122335246762</v>
       </c>
       <c r="T89">
-        <v>3.182973740664614</v>
+        <v>3.17352864698778</v>
       </c>
       <c r="U89">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V89">
-        <v>0.0786925078612309</v>
+        <v>0.08186977925244127</v>
       </c>
       <c r="W89">
-        <v>0.2373962803860065</v>
+        <v>0.2273962803860065</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3747262279106234</v>
+        <v>0.3898560916782918</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2391562182130001</v>
+        <v>0.2302750866272843</v>
       </c>
       <c r="C90">
-        <v>-2204.160029327683</v>
+        <v>-2145.734345866295</v>
       </c>
       <c r="D90">
-        <v>1696.375970672317</v>
+        <v>1754.801654133704</v>
       </c>
       <c r="E90">
         <v>1029.336</v>
@@ -8673,37 +8673,37 @@
         <v>375.475</v>
       </c>
       <c r="M90">
-        <v>1013.51540487389</v>
+        <v>974.1820448738905</v>
       </c>
       <c r="N90">
-        <v>-638.0404048738903</v>
+        <v>-598.7070448738905</v>
       </c>
       <c r="O90">
-        <v>-133.988485023517</v>
+        <v>-125.728479423517</v>
       </c>
       <c r="P90">
-        <v>-504.0519198503733</v>
+        <v>-472.9785654503735</v>
       </c>
       <c r="Q90">
-        <v>-220.1519198503734</v>
+        <v>-189.0785654503735</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2503726828660316</v>
+        <v>0.2496965863183993</v>
       </c>
       <c r="T90">
-        <v>3.448221552386666</v>
+        <v>3.437989367570096</v>
       </c>
       <c r="U90">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V90">
-        <v>0.07779827481735328</v>
+        <v>0.08093944085184533</v>
       </c>
       <c r="W90">
-        <v>0.2376267003057685</v>
+        <v>0.2276267003057686</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3704679753207299</v>
+        <v>0.3854259088183112</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2412749505462508</v>
+        <v>0.2322938189605349</v>
       </c>
       <c r="C91">
-        <v>-2262.238315635386</v>
+        <v>-2204.076068644182</v>
       </c>
       <c r="D91">
-        <v>1682.994684364614</v>
+        <v>1741.156931355818</v>
       </c>
       <c r="E91">
         <v>1074.033</v>
@@ -8755,37 +8755,37 @@
         <v>375.475</v>
       </c>
       <c r="M91">
-        <v>1025.032625383821</v>
+        <v>985.2522953838211</v>
       </c>
       <c r="N91">
-        <v>-649.5576253838209</v>
+        <v>-609.7772953838211</v>
       </c>
       <c r="O91">
-        <v>-136.4071013306024</v>
+        <v>-128.0532320306024</v>
       </c>
       <c r="P91">
-        <v>-513.1505240532185</v>
+        <v>-481.7240633532186</v>
       </c>
       <c r="Q91">
-        <v>-229.2505240532186</v>
+        <v>-197.8240633532187</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2689701994902163</v>
+        <v>0.2682326396200719</v>
       </c>
       <c r="T91">
-        <v>3.761696238967271</v>
+        <v>3.750533855531014</v>
       </c>
       <c r="U91">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V91">
-        <v>0.07692413689805719</v>
+        <v>0.08003000893216168</v>
       </c>
       <c r="W91">
-        <v>0.2378519422498056</v>
+        <v>0.2278519422498056</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3663054138002723</v>
+        <v>0.3810952806293414</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2433936828795015</v>
+        <v>0.2343125512937856</v>
       </c>
       <c r="C92">
-        <v>-2320.107146685605</v>
+        <v>-2262.207235465026</v>
       </c>
       <c r="D92">
-        <v>1669.822853314395</v>
+        <v>1727.722764534974</v>
       </c>
       <c r="E92">
         <v>1118.73</v>
@@ -8837,37 +8837,37 @@
         <v>375.475</v>
       </c>
       <c r="M92">
-        <v>1036.549845893752</v>
+        <v>996.3225458937517</v>
       </c>
       <c r="N92">
-        <v>-661.0748458937516</v>
+        <v>-620.8475458937517</v>
       </c>
       <c r="O92">
-        <v>-138.8257176376878</v>
+        <v>-130.3779846376878</v>
       </c>
       <c r="P92">
-        <v>-522.2491282560637</v>
+        <v>-490.4695612560638</v>
       </c>
       <c r="Q92">
-        <v>-238.3491282560638</v>
+        <v>-206.5695612560638</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.291287219439238</v>
+        <v>0.2904759035820791</v>
       </c>
       <c r="T92">
-        <v>4.137865862863999</v>
+        <v>4.125587241084116</v>
       </c>
       <c r="U92">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V92">
-        <v>0.07606942426585654</v>
+        <v>0.07914078661069322</v>
       </c>
       <c r="W92">
-        <v>0.2380721788173085</v>
+        <v>0.2280721788173085</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3622353536469359</v>
+        <v>0.3768608886223487</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2455124152127522</v>
+        <v>0.2363312836270363</v>
       </c>
       <c r="C93">
-        <v>-2377.77140214535</v>
+        <v>-2320.13268274431</v>
       </c>
       <c r="D93">
-        <v>1656.85559785465</v>
+        <v>1714.49431725569</v>
       </c>
       <c r="E93">
         <v>1163.427</v>
@@ -8919,37 +8919,37 @@
         <v>375.475</v>
       </c>
       <c r="M93">
-        <v>1048.067066403682</v>
+        <v>1007.392796403682</v>
       </c>
       <c r="N93">
-        <v>-672.5920664036822</v>
+        <v>-631.9177964036822</v>
       </c>
       <c r="O93">
-        <v>-141.2443339447733</v>
+        <v>-132.7027372447733</v>
       </c>
       <c r="P93">
-        <v>-531.3477324589089</v>
+        <v>-499.215059158909</v>
       </c>
       <c r="Q93">
-        <v>-247.4477324589089</v>
+        <v>-215.315059158909</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3185635771547089</v>
+        <v>0.3176621150911991</v>
       </c>
       <c r="T93">
-        <v>4.597628736515555</v>
+        <v>4.583985823426795</v>
       </c>
       <c r="U93">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V93">
-        <v>0.0752334965266713</v>
+        <v>0.07827110763694933</v>
       </c>
       <c r="W93">
-        <v>0.2382875750206905</v>
+        <v>0.2282875750206905</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3582547453651014</v>
+        <v>0.3727195601759492</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2476311475460028</v>
+        <v>0.238350015960287</v>
       </c>
       <c r="C94">
-        <v>-2435.235811274551</v>
+        <v>-2377.857099901402</v>
       </c>
       <c r="D94">
-        <v>1644.088188725449</v>
+        <v>1701.466900098598</v>
       </c>
       <c r="E94">
         <v>1208.124</v>
@@ -9001,37 +9001,37 @@
         <v>375.475</v>
       </c>
       <c r="M94">
-        <v>1059.584286913613</v>
+        <v>1018.463046913613</v>
       </c>
       <c r="N94">
-        <v>-684.1092869136127</v>
+        <v>-642.9880469136127</v>
       </c>
       <c r="O94">
-        <v>-143.6629502518587</v>
+        <v>-135.0274898518587</v>
       </c>
       <c r="P94">
-        <v>-540.446336661754</v>
+        <v>-507.9605570617541</v>
       </c>
       <c r="Q94">
-        <v>-256.546336661754</v>
+        <v>-224.0605570617541</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3526590242990476</v>
+        <v>0.351644879477599</v>
       </c>
       <c r="T94">
-        <v>5.172332328580001</v>
+        <v>5.156984051355146</v>
       </c>
       <c r="U94">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V94">
-        <v>0.07441574112964228</v>
+        <v>0.07742033472785208</v>
       </c>
       <c r="W94">
-        <v>0.238498288697912</v>
+        <v>0.228498288697912</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3543606720459156</v>
+        <v>0.3686682606088194</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2497498798792535</v>
+        <v>0.2403687482935377</v>
       </c>
       <c r="C95">
-        <v>-2492.504958676774</v>
+        <v>-2435.385034902115</v>
       </c>
       <c r="D95">
-        <v>1631.516041323226</v>
+        <v>1688.635965097885</v>
       </c>
       <c r="E95">
         <v>1252.821</v>
@@ -9083,37 +9083,37 @@
         <v>375.475</v>
       </c>
       <c r="M95">
-        <v>1071.101507423543</v>
+        <v>1029.533297423543</v>
       </c>
       <c r="N95">
-        <v>-695.6265074235433</v>
+        <v>-654.0582974235434</v>
       </c>
       <c r="O95">
-        <v>-146.0815665589441</v>
+        <v>-137.3522424589441</v>
       </c>
       <c r="P95">
-        <v>-549.5449408645992</v>
+        <v>-516.7060549645993</v>
       </c>
       <c r="Q95">
-        <v>-265.6449408645992</v>
+        <v>-232.8060549645993</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3964960277703402</v>
+        <v>0.3953370051172561</v>
       </c>
       <c r="T95">
-        <v>5.911236946948573</v>
+        <v>5.893696058691597</v>
       </c>
       <c r="U95">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V95">
-        <v>0.07361557187018374</v>
+        <v>0.07658785801034827</v>
       </c>
       <c r="W95">
-        <v>0.238704470898204</v>
+        <v>0.228704470898204</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3505503422389702</v>
+        <v>0.3647040857635632</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2518686122125042</v>
+        <v>0.2423874806267883</v>
       </c>
       <c r="C96">
-        <v>-2549.583289788106</v>
+        <v>-2492.720899552365</v>
       </c>
       <c r="D96">
-        <v>1619.134710211895</v>
+        <v>1675.997100447635</v>
       </c>
       <c r="E96">
         <v>1297.518</v>
@@ -9165,37 +9165,37 @@
         <v>375.475</v>
       </c>
       <c r="M96">
-        <v>1082.618727933474</v>
+        <v>1040.603547933474</v>
       </c>
       <c r="N96">
-        <v>-707.1437279334738</v>
+        <v>-665.1285479334739</v>
       </c>
       <c r="O96">
-        <v>-148.5001828660295</v>
+        <v>-139.6769950660295</v>
       </c>
       <c r="P96">
-        <v>-558.6435450674443</v>
+        <v>-525.4515528674444</v>
       </c>
       <c r="Q96">
-        <v>-274.7435450674443</v>
+        <v>-241.5515528674445</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4549453657320636</v>
+        <v>0.4535931726367989</v>
       </c>
       <c r="T96">
-        <v>6.896443104773337</v>
+        <v>6.875978735140198</v>
       </c>
       <c r="U96">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V96">
-        <v>0.07283242748858605</v>
+        <v>0.07577309356342968</v>
       </c>
       <c r="W96">
-        <v>0.2389062662431706</v>
+        <v>0.2289062662431707</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3468210832789812</v>
+        <v>0.3608242550639509</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2539873445457549</v>
+        <v>0.244406212960039</v>
       </c>
       <c r="C97">
-        <v>-2606.475116117985</v>
+        <v>-2549.86897455587</v>
       </c>
       <c r="D97">
-        <v>1606.939883882016</v>
+        <v>1663.54602544413</v>
       </c>
       <c r="E97">
         <v>1342.215</v>
@@ -9247,37 +9247,37 @@
         <v>375.475</v>
       </c>
       <c r="M97">
-        <v>1094.135948443404</v>
+        <v>1051.673798443405</v>
       </c>
       <c r="N97">
-        <v>-718.6609484434044</v>
+        <v>-676.1987984434046</v>
       </c>
       <c r="O97">
-        <v>-150.9187991731149</v>
+        <v>-142.0017476731149</v>
       </c>
       <c r="P97">
-        <v>-567.7421492702895</v>
+        <v>-534.1970507702897</v>
       </c>
       <c r="Q97">
-        <v>-283.8421492702895</v>
+        <v>-250.2970507702897</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5367744388784766</v>
+        <v>0.5351518071641589</v>
       </c>
       <c r="T97">
-        <v>8.27573172572801</v>
+        <v>8.251174482168242</v>
       </c>
       <c r="U97">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V97">
-        <v>0.07206577035712725</v>
+        <v>0.07497548205223567</v>
       </c>
       <c r="W97">
-        <v>0.2391038132650854</v>
+        <v>0.2291038132650854</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3431703350339392</v>
+        <v>0.3570261050106461</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2561060768790056</v>
+        <v>0.2464249452932897</v>
       </c>
       <c r="C98">
-        <v>-2663.18462025497</v>
+        <v>-2606.833414348064</v>
       </c>
       <c r="D98">
-        <v>1594.927379745029</v>
+        <v>1651.278585651936</v>
       </c>
       <c r="E98">
         <v>1386.911999999999</v>
@@ -9329,37 +9329,37 @@
         <v>375.475</v>
       </c>
       <c r="M98">
-        <v>1105.653168953335</v>
+        <v>1062.744048953335</v>
       </c>
       <c r="N98">
-        <v>-730.1781689533349</v>
+        <v>-687.2690489533348</v>
       </c>
       <c r="O98">
-        <v>-153.3374154802003</v>
+        <v>-144.3265002802003</v>
       </c>
       <c r="P98">
-        <v>-576.8407534731346</v>
+        <v>-542.9425486731345</v>
       </c>
       <c r="Q98">
-        <v>-292.9407534731346</v>
+        <v>-259.0425486731345</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6595180485980944</v>
+        <v>0.6574897589551971</v>
       </c>
       <c r="T98">
-        <v>10.34466465715999</v>
+        <v>10.31396810271028</v>
       </c>
       <c r="U98">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V98">
-        <v>0.0713150852492405</v>
+        <v>0.07419448744752491</v>
       </c>
       <c r="W98">
-        <v>0.2392972447240435</v>
+        <v>0.2292972447240435</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3395956440440024</v>
+        <v>0.3533070830834519</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2582248092122563</v>
+        <v>0.2484436776265404</v>
       </c>
       <c r="C99">
-        <v>-2719.715860649665</v>
+        <v>-2663.618251717701</v>
       </c>
       <c r="D99">
-        <v>1583.093139350335</v>
+        <v>1639.190748282299</v>
       </c>
       <c r="E99">
         <v>1431.608999999999</v>
@@ -9411,37 +9411,37 @@
         <v>375.475</v>
       </c>
       <c r="M99">
-        <v>1117.170389463266</v>
+        <v>1073.814299463266</v>
       </c>
       <c r="N99">
-        <v>-741.6953894632655</v>
+        <v>-698.3392994632655</v>
       </c>
       <c r="O99">
-        <v>-155.7560317872858</v>
+        <v>-146.6512528872858</v>
       </c>
       <c r="P99">
-        <v>-585.9393576759797</v>
+        <v>-551.6880465759798</v>
       </c>
       <c r="Q99">
-        <v>-302.0393576759798</v>
+        <v>-267.7880465759798</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8640907314641257</v>
+        <v>0.8613863452735964</v>
       </c>
       <c r="T99">
-        <v>13.79288620954665</v>
+        <v>13.75195747028037</v>
       </c>
       <c r="U99">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V99">
-        <v>0.07057987818481536</v>
+        <v>0.07342959582435454</v>
       </c>
       <c r="W99">
-        <v>0.2394866879054974</v>
+        <v>0.2294866879054974</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3360946580229303</v>
+        <v>0.3496647420207359</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2603435415455069</v>
+        <v>0.2504624099597911</v>
       </c>
       <c r="C100">
-        <v>-2776.072776186254</v>
+        <v>-2720.227402226942</v>
       </c>
       <c r="D100">
-        <v>1571.433223813746</v>
+        <v>1627.278597773058</v>
       </c>
       <c r="E100">
         <v>1476.306</v>
@@ -9493,37 +9493,37 @@
         <v>375.475</v>
       </c>
       <c r="M100">
-        <v>1128.687609973196</v>
+        <v>1084.884549973196</v>
       </c>
       <c r="N100">
-        <v>-753.212609973196</v>
+        <v>-709.409549973196</v>
       </c>
       <c r="O100">
-        <v>-158.1746480943712</v>
+        <v>-148.9760054943712</v>
       </c>
       <c r="P100">
-        <v>-595.0379618788248</v>
+        <v>-560.4335444788248</v>
       </c>
       <c r="Q100">
-        <v>-311.1379618788249</v>
+        <v>-276.5335444788249</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.273236097196189</v>
+        <v>1.269179517910394</v>
       </c>
       <c r="T100">
-        <v>20.68932931431998</v>
+        <v>20.62793620542055</v>
       </c>
       <c r="U100">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V100">
-        <v>0.06985967534619479</v>
+        <v>0.07268031423431011</v>
       </c>
       <c r="W100">
-        <v>0.2396722648995746</v>
+        <v>0.2296722648995747</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3326651206961657</v>
+        <v>0.3460967344490958</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2624622738787576</v>
+        <v>0.2524811422930417</v>
       </c>
       <c r="C101">
-        <v>-2832.25919055352</v>
+        <v>-2776.664668440106</v>
       </c>
       <c r="D101">
-        <v>1559.94380944648</v>
+        <v>1615.538331559894</v>
       </c>
       <c r="E101">
         <v>1521.003</v>
@@ -9575,37 +9575,37 @@
         <v>375.475</v>
       </c>
       <c r="M101">
-        <v>1140.204830483127</v>
+        <v>1095.954800483127</v>
       </c>
       <c r="N101">
-        <v>-764.7298304831266</v>
+        <v>-720.4798004831267</v>
       </c>
       <c r="O101">
-        <v>-160.5932644014566</v>
+        <v>-151.3007581014566</v>
       </c>
       <c r="P101">
-        <v>-604.13656608167</v>
+        <v>-569.1790423816701</v>
       </c>
       <c r="Q101">
-        <v>-320.23656608167</v>
+        <v>-285.2790423816701</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.500672194392378</v>
+        <v>2.492559035820789</v>
       </c>
       <c r="T101">
-        <v>41.37865862863995</v>
+        <v>41.25587241084111</v>
       </c>
       <c r="U101">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V101">
-        <v>0.06915402205986958</v>
+        <v>0.07194616964608475</v>
       </c>
       <c r="W101">
-        <v>0.2398540928634685</v>
+        <v>0.2298540928634685</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.32930486695176</v>
+        <v>0.3426008078384988</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/portugal/portugal_utility_general.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_utility_general.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07214398573648993</v>
+        <v>0.07212183190971135</v>
       </c>
       <c r="C2">
-        <v>4577.203828750798</v>
+        <v>4533.519152323604</v>
       </c>
       <c r="D2">
-        <v>4544.403828750797</v>
+        <v>4545.416152323604</v>
       </c>
       <c r="E2">
-        <v>-2904</v>
+        <v>-2859.303</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>44.697</v>
       </c>
       <c r="G2">
         <v>32.8</v>
@@ -1457,28 +1457,28 @@
         <v>375.475</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.778957009930573</v>
       </c>
       <c r="N2">
-        <v>375.475</v>
+        <v>372.6960429900694</v>
       </c>
       <c r="O2">
-        <v>78.84975</v>
+        <v>78.26616902791457</v>
       </c>
       <c r="P2">
-        <v>296.6252500000001</v>
+        <v>294.4298739621548</v>
       </c>
       <c r="Q2">
-        <v>580.52525</v>
+        <v>578.3298739621548</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07214398573648993</v>
+        <v>0.0723542054206498</v>
       </c>
       <c r="T2">
-        <v>0.4441974458563937</v>
+        <v>0.4477420517374699</v>
       </c>
       <c r="U2">
         <v>0.0621732333250682</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>135.1136410740591</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07212183190971135</v>
+        <v>0.07209967808293276</v>
       </c>
       <c r="C3">
-        <v>4533.519152323604</v>
+        <v>4489.834927012726</v>
       </c>
       <c r="D3">
-        <v>4545.416152323604</v>
+        <v>4546.428927012726</v>
       </c>
       <c r="E3">
-        <v>-2859.303</v>
+        <v>-2814.606</v>
       </c>
       <c r="F3">
-        <v>44.697</v>
+        <v>89.39399999999999</v>
       </c>
       <c r="G3">
         <v>32.8</v>
@@ -1539,28 +1539,28 @@
         <v>375.475</v>
       </c>
       <c r="M3">
-        <v>2.778957009930573</v>
+        <v>5.557914019861147</v>
       </c>
       <c r="N3">
-        <v>372.6960429900694</v>
+        <v>369.9170859801389</v>
       </c>
       <c r="O3">
-        <v>78.26616902791457</v>
+        <v>77.68258805582917</v>
       </c>
       <c r="P3">
-        <v>294.4298739621548</v>
+        <v>292.2344979243097</v>
       </c>
       <c r="Q3">
-        <v>578.3298739621548</v>
+        <v>576.1344979243097</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0723542054206498</v>
+        <v>0.07256871530244559</v>
       </c>
       <c r="T3">
-        <v>0.4477420517374699</v>
+        <v>0.4513589965140785</v>
       </c>
       <c r="U3">
         <v>0.0621732333250682</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>135.1136410740591</v>
+        <v>67.55682053702957</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07209967808293276</v>
+        <v>0.07207752425615416</v>
       </c>
       <c r="C4">
-        <v>4489.834927012726</v>
+        <v>4446.151153119772</v>
       </c>
       <c r="D4">
-        <v>4546.428927012726</v>
+        <v>4547.442153119772</v>
       </c>
       <c r="E4">
-        <v>-2814.606</v>
+        <v>-2769.909</v>
       </c>
       <c r="F4">
-        <v>89.39399999999999</v>
+        <v>134.091</v>
       </c>
       <c r="G4">
         <v>32.8</v>
@@ -1621,28 +1621,28 @@
         <v>375.475</v>
       </c>
       <c r="M4">
-        <v>5.557914019861147</v>
+        <v>8.33687102979172</v>
       </c>
       <c r="N4">
-        <v>369.9170859801389</v>
+        <v>367.1381289702083</v>
       </c>
       <c r="O4">
-        <v>77.68258805582917</v>
+        <v>77.09900708374374</v>
       </c>
       <c r="P4">
-        <v>292.2344979243097</v>
+        <v>290.0391218864646</v>
       </c>
       <c r="Q4">
-        <v>576.1344979243097</v>
+        <v>573.9391218864646</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07256871530244559</v>
+        <v>0.07278764806840211</v>
       </c>
       <c r="T4">
-        <v>0.4513589965140785</v>
+        <v>0.4550505174716478</v>
       </c>
       <c r="U4">
         <v>0.0621732333250682</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.55682053702957</v>
+        <v>45.03788035801971</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07207752425615416</v>
+        <v>0.07205537042937557</v>
       </c>
       <c r="C5">
-        <v>4446.151153119772</v>
+        <v>4402.467830946624</v>
       </c>
       <c r="D5">
-        <v>4547.442153119772</v>
+        <v>4548.455830946623</v>
       </c>
       <c r="E5">
-        <v>-2769.909</v>
+        <v>-2725.212</v>
       </c>
       <c r="F5">
-        <v>134.091</v>
+        <v>178.788</v>
       </c>
       <c r="G5">
         <v>32.8</v>
@@ -1703,28 +1703,28 @@
         <v>375.475</v>
       </c>
       <c r="M5">
-        <v>8.33687102979172</v>
+        <v>11.11582803972229</v>
       </c>
       <c r="N5">
-        <v>367.1381289702083</v>
+        <v>364.3591719602777</v>
       </c>
       <c r="O5">
-        <v>77.09900708374374</v>
+        <v>76.51542611165831</v>
       </c>
       <c r="P5">
-        <v>290.0391218864646</v>
+        <v>287.8437458486194</v>
       </c>
       <c r="Q5">
-        <v>573.9391218864646</v>
+        <v>571.7437458486194</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07278764806840211</v>
+        <v>0.0730111419336494</v>
       </c>
       <c r="T5">
-        <v>0.4550505174716478</v>
+        <v>0.4588189451158333</v>
       </c>
       <c r="U5">
         <v>0.0621732333250682</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.03788035801971</v>
+        <v>33.77841026851478</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07205537042937557</v>
+        <v>0.07203321660259698</v>
       </c>
       <c r="C6">
-        <v>4402.467830946624</v>
+        <v>4358.784960795425</v>
       </c>
       <c r="D6">
-        <v>4548.455830946623</v>
+        <v>4549.469960795424</v>
       </c>
       <c r="E6">
-        <v>-2725.212</v>
+        <v>-2680.515</v>
       </c>
       <c r="F6">
-        <v>178.788</v>
+        <v>223.485</v>
       </c>
       <c r="G6">
         <v>32.8</v>
@@ -1785,28 +1785,28 @@
         <v>375.475</v>
       </c>
       <c r="M6">
-        <v>11.11582803972229</v>
+        <v>13.89478504965287</v>
       </c>
       <c r="N6">
-        <v>364.3591719602777</v>
+        <v>361.5802149503472</v>
       </c>
       <c r="O6">
-        <v>76.51542611165831</v>
+        <v>75.9318451395729</v>
       </c>
       <c r="P6">
-        <v>287.8437458486194</v>
+        <v>285.6483698107743</v>
       </c>
       <c r="Q6">
-        <v>571.7437458486194</v>
+        <v>569.5483698107743</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0730111419336494</v>
+        <v>0.07323934093290188</v>
       </c>
       <c r="T6">
-        <v>0.4588189451158333</v>
+        <v>0.4626667080788438</v>
       </c>
       <c r="U6">
         <v>0.0621732333250682</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.77841026851478</v>
+        <v>27.02272821481182</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07203321660259698</v>
+        <v>0.0720110627758184</v>
       </c>
       <c r="C7">
-        <v>4358.784960795425</v>
+        <v>4315.102542968596</v>
       </c>
       <c r="D7">
-        <v>4549.469960795424</v>
+        <v>4550.484542968596</v>
       </c>
       <c r="E7">
-        <v>-2680.515</v>
+        <v>-2635.818</v>
       </c>
       <c r="F7">
-        <v>223.485</v>
+        <v>268.182</v>
       </c>
       <c r="G7">
         <v>32.8</v>
@@ -1867,28 +1867,28 @@
         <v>375.475</v>
       </c>
       <c r="M7">
-        <v>13.89478504965287</v>
+        <v>16.67374205958344</v>
       </c>
       <c r="N7">
-        <v>361.5802149503472</v>
+        <v>358.8012579404166</v>
       </c>
       <c r="O7">
-        <v>75.9318451395729</v>
+        <v>75.34826416748747</v>
       </c>
       <c r="P7">
-        <v>285.6483698107743</v>
+        <v>283.4529937729291</v>
       </c>
       <c r="Q7">
-        <v>569.5483698107743</v>
+        <v>567.352993772929</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07323934093290188</v>
+        <v>0.07347239523001081</v>
       </c>
       <c r="T7">
-        <v>0.4626667080788438</v>
+        <v>0.4665963383389395</v>
       </c>
       <c r="U7">
         <v>0.0621732333250682</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.02272821481182</v>
+        <v>22.51894017900985</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0720110627758184</v>
+        <v>0.07198890894903981</v>
       </c>
       <c r="C8">
-        <v>4315.102542968596</v>
+        <v>4271.420577768824</v>
       </c>
       <c r="D8">
-        <v>4550.484542968596</v>
+        <v>4551.499577768824</v>
       </c>
       <c r="E8">
-        <v>-2635.818</v>
+        <v>-2591.121</v>
       </c>
       <c r="F8">
-        <v>268.182</v>
+        <v>312.879</v>
       </c>
       <c r="G8">
         <v>32.8</v>
@@ -1949,28 +1949,28 @@
         <v>375.475</v>
       </c>
       <c r="M8">
-        <v>16.67374205958344</v>
+        <v>19.45269906951401</v>
       </c>
       <c r="N8">
-        <v>358.8012579404166</v>
+        <v>356.022300930486</v>
       </c>
       <c r="O8">
-        <v>75.34826416748747</v>
+        <v>74.76468319540207</v>
       </c>
       <c r="P8">
-        <v>283.4529937729291</v>
+        <v>281.257617735084</v>
       </c>
       <c r="Q8">
-        <v>567.352993772929</v>
+        <v>565.1576177350839</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07347239523001081</v>
+        <v>0.07371046144748768</v>
       </c>
       <c r="T8">
-        <v>0.4665963383389395</v>
+        <v>0.4706104767766718</v>
       </c>
       <c r="U8">
         <v>0.0621732333250682</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.51894017900985</v>
+        <v>19.30194872486559</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07198890894903981</v>
+        <v>0.07196675512226121</v>
       </c>
       <c r="C9">
-        <v>4271.420577768824</v>
+        <v>4227.739065499068</v>
       </c>
       <c r="D9">
-        <v>4551.499577768824</v>
+        <v>4552.515065499068</v>
       </c>
       <c r="E9">
-        <v>-2591.121</v>
+        <v>-2546.424</v>
       </c>
       <c r="F9">
-        <v>312.879</v>
+        <v>357.576</v>
       </c>
       <c r="G9">
         <v>32.8</v>
@@ -2031,28 +2031,28 @@
         <v>375.475</v>
       </c>
       <c r="M9">
-        <v>19.45269906951401</v>
+        <v>22.23165607944459</v>
       </c>
       <c r="N9">
-        <v>356.022300930486</v>
+        <v>353.2433439205554</v>
       </c>
       <c r="O9">
-        <v>74.76468319540206</v>
+        <v>74.18110222331664</v>
       </c>
       <c r="P9">
-        <v>281.257617735084</v>
+        <v>279.0622416972388</v>
       </c>
       <c r="Q9">
-        <v>565.1576177350839</v>
+        <v>562.9622416972388</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07371046144748768</v>
+        <v>0.07395370301751837</v>
       </c>
       <c r="T9">
-        <v>0.4706104767766718</v>
+        <v>0.4747118790934851</v>
       </c>
       <c r="U9">
         <v>0.0621732333250682</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.30194872486559</v>
+        <v>16.88920513425739</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07196675512226121</v>
+        <v>0.07194460129548262</v>
       </c>
       <c r="C10">
-        <v>4227.739065499068</v>
+        <v>4184.058006462554</v>
       </c>
       <c r="D10">
-        <v>4552.515065499068</v>
+        <v>4553.531006462554</v>
       </c>
       <c r="E10">
-        <v>-2546.424</v>
+        <v>-2501.727</v>
       </c>
       <c r="F10">
-        <v>357.576</v>
+        <v>402.273</v>
       </c>
       <c r="G10">
         <v>32.8</v>
@@ -2113,28 +2113,28 @@
         <v>375.475</v>
       </c>
       <c r="M10">
-        <v>22.23165607944459</v>
+        <v>25.01061308937516</v>
       </c>
       <c r="N10">
-        <v>353.2433439205554</v>
+        <v>350.4643869106249</v>
       </c>
       <c r="O10">
-        <v>74.18110222331664</v>
+        <v>73.59752125123121</v>
       </c>
       <c r="P10">
-        <v>279.0622416972388</v>
+        <v>276.8668656593936</v>
       </c>
       <c r="Q10">
-        <v>562.9622416972388</v>
+        <v>560.7668656593936</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07395370301751837</v>
+        <v>0.07420229055612118</v>
       </c>
       <c r="T10">
-        <v>0.4747118790934851</v>
+        <v>0.4789034221205581</v>
       </c>
       <c r="U10">
         <v>0.0621732333250682</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.88920513425739</v>
+        <v>15.01262678600657</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07194460129548262</v>
+        <v>0.07192244746870403</v>
       </c>
       <c r="C11">
-        <v>4184.058006462554</v>
+        <v>4140.377400962781</v>
       </c>
       <c r="D11">
-        <v>4553.531006462554</v>
+        <v>4554.547400962781</v>
       </c>
       <c r="E11">
-        <v>-2501.727</v>
+        <v>-2457.03</v>
       </c>
       <c r="F11">
-        <v>402.273</v>
+        <v>446.97</v>
       </c>
       <c r="G11">
         <v>32.8</v>
@@ -2195,28 +2195,28 @@
         <v>375.475</v>
       </c>
       <c r="M11">
-        <v>25.01061308937516</v>
+        <v>27.78957009930573</v>
       </c>
       <c r="N11">
-        <v>350.4643869106249</v>
+        <v>347.6854299006943</v>
       </c>
       <c r="O11">
-        <v>73.59752125123121</v>
+        <v>73.0139402791458</v>
       </c>
       <c r="P11">
-        <v>276.8668656593936</v>
+        <v>274.6714896215485</v>
       </c>
       <c r="Q11">
-        <v>560.7668656593936</v>
+        <v>558.5714896215485</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07420229055612118</v>
+        <v>0.07445640226224849</v>
       </c>
       <c r="T11">
-        <v>0.4789034221205581</v>
+        <v>0.4831881105482327</v>
       </c>
       <c r="U11">
         <v>0.0621732333250682</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.01262678600657</v>
+        <v>13.51136410740591</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07192244746870403</v>
+        <v>0.07203064364192546</v>
       </c>
       <c r="C12">
-        <v>4140.377400962781</v>
+        <v>4090.720771844698</v>
       </c>
       <c r="D12">
-        <v>4554.547400962781</v>
+        <v>4549.587771844698</v>
       </c>
       <c r="E12">
-        <v>-2457.03</v>
+        <v>-2412.333</v>
       </c>
       <c r="F12">
-        <v>446.97</v>
+        <v>491.667</v>
       </c>
       <c r="G12">
         <v>32.8</v>
@@ -2277,45 +2277,45 @@
         <v>375.475</v>
       </c>
       <c r="M12">
-        <v>27.78957009930573</v>
+        <v>31.3060276092363</v>
       </c>
       <c r="N12">
-        <v>347.6854299006943</v>
+        <v>344.1689723907637</v>
       </c>
       <c r="O12">
-        <v>73.0139402791458</v>
+        <v>72.27548420206038</v>
       </c>
       <c r="P12">
-        <v>274.6714896215485</v>
+        <v>271.8934881887033</v>
       </c>
       <c r="Q12">
-        <v>558.5714896215485</v>
+        <v>555.7934881887033</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07445640226224849</v>
+        <v>0.07471622434379441</v>
       </c>
       <c r="T12">
-        <v>0.4831881105482327</v>
+        <v>0.4875690841091134</v>
       </c>
       <c r="U12">
-        <v>0.0621732333250682</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V12">
         <v>0.21</v>
       </c>
       <c r="W12">
-        <v>0.04911685432680388</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.51136410740591</v>
+        <v>11.99369669913735</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07203064364192546</v>
+        <v>0.07202033981514686</v>
       </c>
       <c r="C13">
-        <v>4090.720771844698</v>
+        <v>4046.495625920883</v>
       </c>
       <c r="D13">
-        <v>4549.587771844698</v>
+        <v>4550.059625920882</v>
       </c>
       <c r="E13">
-        <v>-2412.333</v>
+        <v>-2367.636</v>
       </c>
       <c r="F13">
-        <v>491.667</v>
+        <v>536.3639999999999</v>
       </c>
       <c r="G13">
         <v>32.8</v>
@@ -2359,28 +2359,28 @@
         <v>375.475</v>
       </c>
       <c r="M13">
-        <v>31.3060276092363</v>
+        <v>34.15203011916687</v>
       </c>
       <c r="N13">
-        <v>344.1689723907637</v>
+        <v>341.3229698808332</v>
       </c>
       <c r="O13">
-        <v>72.27548420206038</v>
+        <v>71.67782367497496</v>
       </c>
       <c r="P13">
-        <v>271.8934881887033</v>
+        <v>269.6451462058582</v>
       </c>
       <c r="Q13">
-        <v>555.7934881887033</v>
+        <v>553.5451462058581</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07471622434379441</v>
+        <v>0.07498195147264816</v>
       </c>
       <c r="T13">
-        <v>0.4875690841091134</v>
+        <v>0.4920496252509234</v>
       </c>
       <c r="U13">
         <v>0.06367323332506819</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.99369669913735</v>
+        <v>10.99422197420924</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07202033981514686</v>
+        <v>0.07201003598836826</v>
       </c>
       <c r="C14">
-        <v>4046.495625920883</v>
+        <v>4002.270577882578</v>
       </c>
       <c r="D14">
-        <v>4550.059625920882</v>
+        <v>4550.531577882578</v>
       </c>
       <c r="E14">
-        <v>-2367.636</v>
+        <v>-2322.939</v>
       </c>
       <c r="F14">
-        <v>536.3639999999999</v>
+        <v>581.061</v>
       </c>
       <c r="G14">
         <v>32.8</v>
@@ -2441,28 +2441,28 @@
         <v>375.475</v>
       </c>
       <c r="M14">
-        <v>34.15203011916687</v>
+        <v>36.99803262909745</v>
       </c>
       <c r="N14">
-        <v>341.3229698808332</v>
+        <v>338.4769673709026</v>
       </c>
       <c r="O14">
-        <v>71.67782367497496</v>
+        <v>71.08016314788954</v>
       </c>
       <c r="P14">
-        <v>269.6451462058582</v>
+        <v>267.396804223013</v>
       </c>
       <c r="Q14">
-        <v>553.5451462058581</v>
+        <v>551.2968042230129</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07498195147264816</v>
+        <v>0.07525378727113076</v>
       </c>
       <c r="T14">
-        <v>0.4920496252509234</v>
+        <v>0.496633167338522</v>
       </c>
       <c r="U14">
         <v>0.06367323332506819</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.99422197420924</v>
+        <v>10.14851259157775</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07201003598836826</v>
+        <v>0.07218775216158967</v>
       </c>
       <c r="C15">
-        <v>4002.270577882578</v>
+        <v>3949.44723790609</v>
       </c>
       <c r="D15">
-        <v>4550.531577882578</v>
+        <v>4542.405237906089</v>
       </c>
       <c r="E15">
-        <v>-2322.939</v>
+        <v>-2278.242</v>
       </c>
       <c r="F15">
-        <v>581.061</v>
+        <v>625.758</v>
       </c>
       <c r="G15">
         <v>32.8</v>
@@ -2523,45 +2523,45 @@
         <v>375.475</v>
       </c>
       <c r="M15">
-        <v>36.99803262909745</v>
+        <v>40.90782373902803</v>
       </c>
       <c r="N15">
-        <v>338.4769673709026</v>
+        <v>334.567176260972</v>
       </c>
       <c r="O15">
-        <v>71.08016314788954</v>
+        <v>70.25910701480412</v>
       </c>
       <c r="P15">
-        <v>267.396804223013</v>
+        <v>264.3080692461679</v>
       </c>
       <c r="Q15">
-        <v>551.2968042230129</v>
+        <v>548.208069246168</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07525378727113076</v>
+        <v>0.07553194483236876</v>
       </c>
       <c r="T15">
-        <v>0.496633167338522</v>
+        <v>0.5013233034281579</v>
       </c>
       <c r="U15">
-        <v>0.06367323332506819</v>
+        <v>0.0653732333250682</v>
       </c>
       <c r="V15">
         <v>0.21</v>
       </c>
       <c r="W15">
-        <v>0.05030185432680388</v>
+        <v>0.05164485432680388</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.14851259157775</v>
+        <v>9.178562086200124</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07218775216158967</v>
+        <v>0.07219087833481108</v>
       </c>
       <c r="C16">
-        <v>3949.44723790609</v>
+        <v>3904.607548682688</v>
       </c>
       <c r="D16">
-        <v>4542.405237906089</v>
+        <v>4542.262548682687</v>
       </c>
       <c r="E16">
-        <v>-2278.242</v>
+        <v>-2233.545</v>
       </c>
       <c r="F16">
-        <v>625.758</v>
+        <v>670.455</v>
       </c>
       <c r="G16">
         <v>32.8</v>
@@ -2605,28 +2605,28 @@
         <v>375.475</v>
       </c>
       <c r="M16">
-        <v>40.90782373902803</v>
+        <v>43.8298111489586</v>
       </c>
       <c r="N16">
-        <v>334.567176260972</v>
+        <v>331.6451888510414</v>
       </c>
       <c r="O16">
-        <v>70.25910701480412</v>
+        <v>69.6454896587187</v>
       </c>
       <c r="P16">
-        <v>264.3080692461679</v>
+        <v>261.9996991923227</v>
       </c>
       <c r="Q16">
-        <v>548.208069246168</v>
+        <v>545.8996991923227</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07553194483236876</v>
+        <v>0.07581664727740059</v>
       </c>
       <c r="T16">
-        <v>0.5013233034281579</v>
+        <v>0.5061237956610791</v>
       </c>
       <c r="U16">
         <v>0.0653732333250682</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.178562086200124</v>
+        <v>8.566657947120117</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07219087833481108</v>
+        <v>0.0721940045080325</v>
       </c>
       <c r="C17">
-        <v>3904.607548682688</v>
+        <v>3859.767868423512</v>
       </c>
       <c r="D17">
-        <v>4542.262548682687</v>
+        <v>4542.119868423512</v>
       </c>
       <c r="E17">
-        <v>-2233.545</v>
+        <v>-2188.848</v>
       </c>
       <c r="F17">
-        <v>670.4549999999999</v>
+        <v>715.1519999999999</v>
       </c>
       <c r="G17">
         <v>32.8</v>
@@ -2687,28 +2687,28 @@
         <v>375.475</v>
       </c>
       <c r="M17">
-        <v>43.82981114895859</v>
+        <v>46.75179855888917</v>
       </c>
       <c r="N17">
-        <v>331.6451888510414</v>
+        <v>328.7232014411109</v>
       </c>
       <c r="O17">
-        <v>69.6454896587187</v>
+        <v>69.03187230263327</v>
       </c>
       <c r="P17">
-        <v>261.9996991923227</v>
+        <v>259.6913291384776</v>
       </c>
       <c r="Q17">
-        <v>545.8996991923227</v>
+        <v>543.5913291384776</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07581664727740059</v>
+        <v>0.07610812835207603</v>
       </c>
       <c r="T17">
-        <v>0.5061237956610791</v>
+        <v>0.5110385853281176</v>
       </c>
       <c r="U17">
         <v>0.0653732333250682</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.566657947120117</v>
+        <v>8.031241825425109</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0721940045080325</v>
+        <v>0.0723045706812539</v>
       </c>
       <c r="C18">
-        <v>3859.767868423512</v>
+        <v>3810.030326065908</v>
       </c>
       <c r="D18">
-        <v>4542.119868423512</v>
+        <v>4537.079326065908</v>
       </c>
       <c r="E18">
-        <v>-2188.848</v>
+        <v>-2144.151</v>
       </c>
       <c r="F18">
-        <v>715.1519999999999</v>
+        <v>759.849</v>
       </c>
       <c r="G18">
         <v>32.8</v>
@@ -2769,45 +2769,45 @@
         <v>375.475</v>
       </c>
       <c r="M18">
-        <v>46.75179855888917</v>
+        <v>50.28166516881974</v>
       </c>
       <c r="N18">
-        <v>328.7232014411109</v>
+        <v>325.1933348311803</v>
       </c>
       <c r="O18">
-        <v>69.03187230263327</v>
+        <v>68.29060031454786</v>
       </c>
       <c r="P18">
-        <v>259.6913291384776</v>
+        <v>256.9027345166324</v>
       </c>
       <c r="Q18">
-        <v>543.5913291384776</v>
+        <v>540.8027345166324</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07610812835207603</v>
+        <v>0.07640663306710511</v>
       </c>
       <c r="T18">
-        <v>0.5110385853281176</v>
+        <v>0.5160718036618319</v>
       </c>
       <c r="U18">
-        <v>0.0653732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V18">
         <v>0.21</v>
       </c>
       <c r="W18">
-        <v>0.05164485432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>8.031241825425109</v>
+        <v>7.467433680633881</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0723045706812539</v>
+        <v>0.0723140168544753</v>
       </c>
       <c r="C19">
-        <v>3810.030326065908</v>
+        <v>3764.903208179255</v>
       </c>
       <c r="D19">
-        <v>4537.079326065908</v>
+        <v>4536.649208179255</v>
       </c>
       <c r="E19">
-        <v>-2144.151</v>
+        <v>-2099.454</v>
       </c>
       <c r="F19">
-        <v>759.849</v>
+        <v>804.546</v>
       </c>
       <c r="G19">
         <v>32.8</v>
@@ -2851,28 +2851,28 @@
         <v>375.475</v>
       </c>
       <c r="M19">
-        <v>50.28166516881974</v>
+        <v>53.23941017875032</v>
       </c>
       <c r="N19">
-        <v>325.1933348311803</v>
+        <v>322.2355898212497</v>
       </c>
       <c r="O19">
-        <v>68.29060031454786</v>
+        <v>67.66947386246244</v>
       </c>
       <c r="P19">
-        <v>256.9027345166324</v>
+        <v>254.5661159587873</v>
       </c>
       <c r="Q19">
-        <v>540.8027345166324</v>
+        <v>538.4661159587872</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07640663306710511</v>
+        <v>0.07671241838493978</v>
       </c>
       <c r="T19">
-        <v>0.5160718036618319</v>
+        <v>0.5212277834183195</v>
       </c>
       <c r="U19">
         <v>0.06617323332506819</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.467433680633881</v>
+        <v>7.052576253931999</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07231401685447532</v>
+        <v>0.07232346302769672</v>
       </c>
       <c r="C20">
-        <v>3764.903208179254</v>
+        <v>3719.776171835746</v>
       </c>
       <c r="D20">
-        <v>4536.649208179254</v>
+        <v>4536.219171835746</v>
       </c>
       <c r="E20">
-        <v>-2099.454</v>
+        <v>-2054.757</v>
       </c>
       <c r="F20">
-        <v>804.5459999999999</v>
+        <v>849.2429999999999</v>
       </c>
       <c r="G20">
         <v>32.8</v>
@@ -2933,28 +2933,28 @@
         <v>375.475</v>
       </c>
       <c r="M20">
-        <v>53.23941017875031</v>
+        <v>56.19715518868088</v>
       </c>
       <c r="N20">
-        <v>322.2355898212497</v>
+        <v>319.2778448113191</v>
       </c>
       <c r="O20">
-        <v>67.66947386246244</v>
+        <v>67.04834741037702</v>
       </c>
       <c r="P20">
-        <v>254.5661159587873</v>
+        <v>252.2294974009421</v>
       </c>
       <c r="Q20">
-        <v>538.4661159587872</v>
+        <v>536.1294974009421</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07671241838493978</v>
+        <v>0.07702575395753579</v>
       </c>
       <c r="T20">
-        <v>0.5212277834183195</v>
+        <v>0.5265110713169427</v>
       </c>
       <c r="U20">
         <v>0.06617323332506819</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.052576253932</v>
+        <v>6.681388030040842</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07232346302769672</v>
+        <v>0.07233290920091814</v>
       </c>
       <c r="C21">
-        <v>3719.776171835746</v>
+        <v>3674.649217012197</v>
       </c>
       <c r="D21">
-        <v>4536.219171835746</v>
+        <v>4535.789217012197</v>
       </c>
       <c r="E21">
-        <v>-2054.757</v>
+        <v>-2010.06</v>
       </c>
       <c r="F21">
-        <v>849.2429999999999</v>
+        <v>893.9400000000001</v>
       </c>
       <c r="G21">
         <v>32.8</v>
@@ -3015,28 +3015,28 @@
         <v>375.475</v>
       </c>
       <c r="M21">
-        <v>56.19715518868088</v>
+        <v>59.15490019861146</v>
       </c>
       <c r="N21">
-        <v>319.2778448113191</v>
+        <v>316.3200998013886</v>
       </c>
       <c r="O21">
-        <v>67.04834741037702</v>
+        <v>66.4272209582916</v>
       </c>
       <c r="P21">
-        <v>252.2294974009421</v>
+        <v>249.892878843097</v>
       </c>
       <c r="Q21">
-        <v>536.1294974009421</v>
+        <v>533.7928788430969</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07702575395753579</v>
+        <v>0.0773469229194467</v>
       </c>
       <c r="T21">
-        <v>0.5265110713169427</v>
+        <v>0.5319264414130315</v>
       </c>
       <c r="U21">
         <v>0.06617323332506819</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.681388030040842</v>
+        <v>6.347318628538798</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07233290920091814</v>
+        <v>0.07250825537413955</v>
       </c>
       <c r="C22">
-        <v>3674.649217012197</v>
+        <v>3621.98588114705</v>
       </c>
       <c r="D22">
-        <v>4535.789217012197</v>
+        <v>4527.82288114705</v>
       </c>
       <c r="E22">
-        <v>-2010.06</v>
+        <v>-1965.363</v>
       </c>
       <c r="F22">
-        <v>893.9400000000001</v>
+        <v>938.6370000000001</v>
       </c>
       <c r="G22">
         <v>32.8</v>
@@ -3097,45 +3097,45 @@
         <v>375.475</v>
       </c>
       <c r="M22">
-        <v>59.15490019861146</v>
+        <v>63.05128220854204</v>
       </c>
       <c r="N22">
-        <v>316.3200998013886</v>
+        <v>312.423717791458</v>
       </c>
       <c r="O22">
-        <v>66.4272209582916</v>
+        <v>65.60898073620618</v>
       </c>
       <c r="P22">
-        <v>249.892878843097</v>
+        <v>246.8147370552518</v>
       </c>
       <c r="Q22">
-        <v>533.7928788430969</v>
+        <v>530.7147370552518</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0773469229194467</v>
+        <v>0.07767622274115282</v>
       </c>
       <c r="T22">
-        <v>0.5319264414130315</v>
+        <v>0.5374789094862363</v>
       </c>
       <c r="U22">
-        <v>0.06617323332506819</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V22">
         <v>0.21</v>
       </c>
       <c r="W22">
-        <v>0.05227685432680387</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.347318628538798</v>
+        <v>5.955073185635098</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07250825537413955</v>
+        <v>0.07252560154736094</v>
       </c>
       <c r="C23">
-        <v>3621.98588114705</v>
+        <v>3576.502329735352</v>
       </c>
       <c r="D23">
-        <v>4527.82288114705</v>
+        <v>4527.036329735352</v>
       </c>
       <c r="E23">
-        <v>-1965.363</v>
+        <v>-1920.666</v>
       </c>
       <c r="F23">
-        <v>938.6369999999999</v>
+        <v>983.3339999999999</v>
       </c>
       <c r="G23">
         <v>32.8</v>
@@ -3179,28 +3179,28 @@
         <v>375.475</v>
       </c>
       <c r="M23">
-        <v>63.05128220854203</v>
+        <v>66.05372421847261</v>
       </c>
       <c r="N23">
-        <v>312.423717791458</v>
+        <v>309.4212757815274</v>
       </c>
       <c r="O23">
-        <v>65.60898073620618</v>
+        <v>64.97846791412076</v>
       </c>
       <c r="P23">
-        <v>246.8147370552518</v>
+        <v>244.4428078674067</v>
       </c>
       <c r="Q23">
-        <v>530.7147370552518</v>
+        <v>528.3428078674067</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07767622274115282</v>
+        <v>0.07801396614803088</v>
       </c>
       <c r="T23">
-        <v>0.5374789094862363</v>
+        <v>0.5431737485356772</v>
       </c>
       <c r="U23">
         <v>0.06717323332506819</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.955073185635099</v>
+        <v>5.684388040833503</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07252560154736094</v>
+        <v>0.07254294772058235</v>
       </c>
       <c r="C24">
-        <v>3576.502329735352</v>
+        <v>3531.019051547975</v>
       </c>
       <c r="D24">
-        <v>4527.036329735352</v>
+        <v>4526.250051547975</v>
       </c>
       <c r="E24">
-        <v>-1920.666</v>
+        <v>-1875.969</v>
       </c>
       <c r="F24">
-        <v>983.3339999999999</v>
+        <v>1028.031</v>
       </c>
       <c r="G24">
         <v>32.8</v>
@@ -3261,28 +3261,28 @@
         <v>375.475</v>
       </c>
       <c r="M24">
-        <v>66.05372421847261</v>
+        <v>69.05616622840317</v>
       </c>
       <c r="N24">
-        <v>309.4212757815274</v>
+        <v>306.4188337715968</v>
       </c>
       <c r="O24">
-        <v>64.97846791412076</v>
+        <v>64.34795509203533</v>
       </c>
       <c r="P24">
-        <v>244.4428078674067</v>
+        <v>242.0708786795615</v>
       </c>
       <c r="Q24">
-        <v>528.3428078674067</v>
+        <v>525.9708786795615</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07801396614803088</v>
+        <v>0.07836048211093177</v>
       </c>
       <c r="T24">
-        <v>0.5431737485356772</v>
+        <v>0.5490165054825064</v>
       </c>
       <c r="U24">
         <v>0.06717323332506819</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.684388040833503</v>
+        <v>5.437240734710308</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07254294772058235</v>
+        <v>0.07256029389380378</v>
       </c>
       <c r="C25">
-        <v>3531.019051547975</v>
+        <v>3485.536046442579</v>
       </c>
       <c r="D25">
-        <v>4526.250051547975</v>
+        <v>4525.464046442579</v>
       </c>
       <c r="E25">
-        <v>-1875.969</v>
+        <v>-1831.272</v>
       </c>
       <c r="F25">
-        <v>1028.031</v>
+        <v>1072.728</v>
       </c>
       <c r="G25">
         <v>32.8</v>
@@ -3343,28 +3343,28 @@
         <v>375.475</v>
       </c>
       <c r="M25">
-        <v>69.05616622840317</v>
+        <v>72.05860823833376</v>
       </c>
       <c r="N25">
-        <v>306.4188337715968</v>
+        <v>303.4163917616663</v>
       </c>
       <c r="O25">
-        <v>64.34795509203533</v>
+        <v>63.71744226994991</v>
       </c>
       <c r="P25">
-        <v>242.0708786795615</v>
+        <v>239.6989494917163</v>
       </c>
       <c r="Q25">
-        <v>525.9708786795615</v>
+        <v>523.5989494917163</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07836048211093177</v>
+        <v>0.07871611691496164</v>
       </c>
       <c r="T25">
-        <v>0.5490165054825064</v>
+        <v>0.555013019191094</v>
       </c>
       <c r="U25">
         <v>0.06717323332506819</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.437240734710308</v>
+        <v>5.21068903743071</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07256029389380378</v>
+        <v>0.07257764006702518</v>
       </c>
       <c r="C26">
-        <v>3485.536046442579</v>
+        <v>3440.053314276928</v>
       </c>
       <c r="D26">
-        <v>4525.464046442579</v>
+        <v>4524.678314276928</v>
       </c>
       <c r="E26">
-        <v>-1831.272</v>
+        <v>-1786.575</v>
       </c>
       <c r="F26">
-        <v>1072.728</v>
+        <v>1117.425</v>
       </c>
       <c r="G26">
         <v>32.8</v>
@@ -3425,28 +3425,28 @@
         <v>375.475</v>
       </c>
       <c r="M26">
-        <v>72.05860823833375</v>
+        <v>75.06105024826432</v>
       </c>
       <c r="N26">
-        <v>303.4163917616663</v>
+        <v>300.4139497517357</v>
       </c>
       <c r="O26">
-        <v>63.71744226994991</v>
+        <v>63.08692944786449</v>
       </c>
       <c r="P26">
-        <v>239.6989494917163</v>
+        <v>237.3270203038712</v>
       </c>
       <c r="Q26">
-        <v>523.5989494917163</v>
+        <v>521.2270203038712</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07871611691496164</v>
+        <v>0.07908123531376561</v>
       </c>
       <c r="T26">
-        <v>0.555013019191094</v>
+        <v>0.5611694399319106</v>
       </c>
       <c r="U26">
         <v>0.06717323332506819</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.210689037430711</v>
+        <v>5.002261475933483</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07257764006702518</v>
+        <v>0.07259498624024659</v>
       </c>
       <c r="C27">
-        <v>3440.053314276928</v>
+        <v>3394.570854908875</v>
       </c>
       <c r="D27">
-        <v>4524.678314276928</v>
+        <v>4523.892854908875</v>
       </c>
       <c r="E27">
-        <v>-1786.575</v>
+        <v>-1741.878</v>
       </c>
       <c r="F27">
-        <v>1117.425</v>
+        <v>1162.122</v>
       </c>
       <c r="G27">
         <v>32.8</v>
@@ -3507,28 +3507,28 @@
         <v>375.475</v>
       </c>
       <c r="M27">
-        <v>75.06105024826432</v>
+        <v>78.0634922581949</v>
       </c>
       <c r="N27">
-        <v>300.4139497517357</v>
+        <v>297.4115077418051</v>
       </c>
       <c r="O27">
-        <v>63.08692944786449</v>
+        <v>62.45641662577907</v>
       </c>
       <c r="P27">
-        <v>237.3270203038712</v>
+        <v>234.955091116026</v>
       </c>
       <c r="Q27">
-        <v>521.2270203038712</v>
+        <v>518.855091116026</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07908123531376561</v>
+        <v>0.07945622177740214</v>
       </c>
       <c r="T27">
-        <v>0.5611694399319106</v>
+        <v>0.5674922504224792</v>
       </c>
       <c r="U27">
         <v>0.06717323332506819</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.002261475933483</v>
+        <v>4.809866803782195</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07259498624024659</v>
+        <v>0.07261233241346801</v>
       </c>
       <c r="C28">
-        <v>3394.570854908875</v>
+        <v>3349.088668196376</v>
       </c>
       <c r="D28">
-        <v>4523.892854908875</v>
+        <v>4523.107668196376</v>
       </c>
       <c r="E28">
-        <v>-1741.878</v>
+        <v>-1697.181</v>
       </c>
       <c r="F28">
-        <v>1162.122</v>
+        <v>1206.819</v>
       </c>
       <c r="G28">
         <v>32.8</v>
@@ -3589,28 +3589,28 @@
         <v>375.475</v>
       </c>
       <c r="M28">
-        <v>78.0634922581949</v>
+        <v>81.06593426812547</v>
       </c>
       <c r="N28">
-        <v>297.4115077418051</v>
+        <v>294.4090657318745</v>
       </c>
       <c r="O28">
-        <v>62.45641662577907</v>
+        <v>61.82590380369365</v>
       </c>
       <c r="P28">
-        <v>234.955091116026</v>
+        <v>232.5831619281809</v>
       </c>
       <c r="Q28">
-        <v>518.855091116026</v>
+        <v>516.4831619281808</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07945622177740214</v>
+        <v>0.07984148184278214</v>
       </c>
       <c r="T28">
-        <v>0.5674922504224792</v>
+        <v>0.5739882885977208</v>
       </c>
       <c r="U28">
         <v>0.06717323332506819</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.809866803782195</v>
+        <v>4.631723588827299</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07261233241346801</v>
+        <v>0.07318267858668941</v>
       </c>
       <c r="C29">
-        <v>3349.088668196376</v>
+        <v>3278.725501697364</v>
       </c>
       <c r="D29">
-        <v>4523.107668196376</v>
+        <v>4497.441501697363</v>
       </c>
       <c r="E29">
-        <v>-1697.181</v>
+        <v>-1652.484</v>
       </c>
       <c r="F29">
-        <v>1206.819</v>
+        <v>1251.516</v>
       </c>
       <c r="G29">
         <v>32.8</v>
@@ -3671,45 +3671,45 @@
         <v>375.475</v>
       </c>
       <c r="M29">
-        <v>81.06593426812547</v>
+        <v>87.19716627805606</v>
       </c>
       <c r="N29">
-        <v>294.4090657318745</v>
+        <v>288.277833721944</v>
       </c>
       <c r="O29">
-        <v>61.82590380369365</v>
+        <v>60.53834508160823</v>
       </c>
       <c r="P29">
-        <v>232.5831619281809</v>
+        <v>227.7394886403357</v>
       </c>
       <c r="Q29">
-        <v>516.4831619281808</v>
+        <v>511.6394886403357</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07984148184278214</v>
+        <v>0.08023744357664489</v>
       </c>
       <c r="T29">
-        <v>0.5739882885977208</v>
+        <v>0.5806647722778302</v>
       </c>
       <c r="U29">
-        <v>0.06717323332506819</v>
+        <v>0.0696732333250682</v>
       </c>
       <c r="V29">
         <v>0.21</v>
       </c>
       <c r="W29">
-        <v>0.05306685432680387</v>
+        <v>0.05504185432680388</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.631723588827299</v>
+        <v>4.306045896063616</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07318267858668941</v>
+        <v>0.07321977475991083</v>
       </c>
       <c r="C30">
-        <v>3278.725501697364</v>
+        <v>3232.369220752458</v>
       </c>
       <c r="D30">
-        <v>4497.441501697363</v>
+        <v>4495.782220752458</v>
       </c>
       <c r="E30">
-        <v>-1652.484</v>
+        <v>-1607.787</v>
       </c>
       <c r="F30">
-        <v>1251.516</v>
+        <v>1296.213</v>
       </c>
       <c r="G30">
         <v>32.8</v>
@@ -3753,28 +3753,28 @@
         <v>375.475</v>
       </c>
       <c r="M30">
-        <v>87.19716627805606</v>
+        <v>90.31135078798664</v>
       </c>
       <c r="N30">
-        <v>288.277833721944</v>
+        <v>285.1636492120134</v>
       </c>
       <c r="O30">
-        <v>60.53834508160823</v>
+        <v>59.88436633452282</v>
       </c>
       <c r="P30">
-        <v>227.7394886403357</v>
+        <v>225.2792828774906</v>
       </c>
       <c r="Q30">
-        <v>511.6394886403357</v>
+        <v>509.1792828774906</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08023744357664489</v>
+        <v>0.08064455916216579</v>
       </c>
       <c r="T30">
-        <v>0.5806647722778302</v>
+        <v>0.5875293259207597</v>
       </c>
       <c r="U30">
         <v>0.0696732333250682</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.306045896063616</v>
+        <v>4.157561554820044</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07321977475991083</v>
+        <v>0.07325687093313223</v>
       </c>
       <c r="C31">
-        <v>3232.369220752458</v>
+        <v>3186.014163702454</v>
       </c>
       <c r="D31">
-        <v>4495.782220752458</v>
+        <v>4494.124163702454</v>
       </c>
       <c r="E31">
-        <v>-1607.787</v>
+        <v>-1563.09</v>
       </c>
       <c r="F31">
-        <v>1296.213</v>
+        <v>1340.91</v>
       </c>
       <c r="G31">
         <v>32.8</v>
@@ -3835,28 +3835,28 @@
         <v>375.475</v>
       </c>
       <c r="M31">
-        <v>90.31135078798661</v>
+        <v>93.42553529791718</v>
       </c>
       <c r="N31">
-        <v>285.1636492120134</v>
+        <v>282.0494647020828</v>
       </c>
       <c r="O31">
-        <v>59.88436633452282</v>
+        <v>59.23038758743739</v>
       </c>
       <c r="P31">
-        <v>225.2792828774906</v>
+        <v>222.8190771146454</v>
       </c>
       <c r="Q31">
-        <v>509.1792828774906</v>
+        <v>506.7190771146454</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08064455916216579</v>
+        <v>0.08106330662155867</v>
       </c>
       <c r="T31">
-        <v>0.5875293259207597</v>
+        <v>0.5945900096677726</v>
       </c>
       <c r="U31">
         <v>0.0696732333250682</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.157561554820044</v>
+        <v>4.018976169659377</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07325687093313223</v>
+        <v>0.07415111710635365</v>
       </c>
       <c r="C32">
-        <v>3186.014163702454</v>
+        <v>3101.714604383147</v>
       </c>
       <c r="D32">
-        <v>4494.124163702454</v>
+        <v>4454.521604383147</v>
       </c>
       <c r="E32">
-        <v>-1563.09</v>
+        <v>-1518.393</v>
       </c>
       <c r="F32">
-        <v>1340.91</v>
+        <v>1385.607</v>
       </c>
       <c r="G32">
         <v>32.8</v>
@@ -3917,45 +3917,45 @@
         <v>375.475</v>
       </c>
       <c r="M32">
-        <v>93.42553529791718</v>
+        <v>101.3893443078478</v>
       </c>
       <c r="N32">
-        <v>282.0494647020828</v>
+        <v>274.0856556921523</v>
       </c>
       <c r="O32">
-        <v>59.23038758743739</v>
+        <v>57.55798769535198</v>
       </c>
       <c r="P32">
-        <v>222.8190771146454</v>
+        <v>216.5276679968003</v>
       </c>
       <c r="Q32">
-        <v>506.7190771146454</v>
+        <v>500.4276679968003</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08106330662155867</v>
+        <v>0.08149419168847022</v>
       </c>
       <c r="T32">
-        <v>0.5945900096677726</v>
+        <v>0.6018553509146993</v>
       </c>
       <c r="U32">
-        <v>0.0696732333250682</v>
+        <v>0.0731732333250682</v>
       </c>
       <c r="V32">
         <v>0.21</v>
       </c>
       <c r="W32">
-        <v>0.05504185432680388</v>
+        <v>0.05780685432680388</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.018976169659377</v>
+        <v>3.703298434004543</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07415111710635365</v>
+        <v>0.07421586327957505</v>
       </c>
       <c r="C33">
-        <v>3101.714604383147</v>
+        <v>3054.177336718691</v>
       </c>
       <c r="D33">
-        <v>4454.521604383147</v>
+        <v>4451.681336718691</v>
       </c>
       <c r="E33">
-        <v>-1518.393</v>
+        <v>-1473.696</v>
       </c>
       <c r="F33">
-        <v>1385.607</v>
+        <v>1430.304</v>
       </c>
       <c r="G33">
         <v>32.8</v>
@@ -3999,28 +3999,28 @@
         <v>375.475</v>
       </c>
       <c r="M33">
-        <v>101.3893443078478</v>
+        <v>104.6599683177783</v>
       </c>
       <c r="N33">
-        <v>274.0856556921523</v>
+        <v>270.8150316822217</v>
       </c>
       <c r="O33">
-        <v>57.55798769535198</v>
+        <v>56.87115665326655</v>
       </c>
       <c r="P33">
-        <v>216.5276679968003</v>
+        <v>213.9438750289551</v>
       </c>
       <c r="Q33">
-        <v>500.4276679968003</v>
+        <v>497.8438750289551</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08149419168847022</v>
+        <v>0.08193774984558502</v>
       </c>
       <c r="T33">
-        <v>0.6018553509146993</v>
+        <v>0.6093343786688883</v>
       </c>
       <c r="U33">
         <v>0.0731732333250682</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.703298434004543</v>
+        <v>3.5875703579419</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07421586327957505</v>
+        <v>0.07501056945279647</v>
       </c>
       <c r="C34">
-        <v>3054.177336718691</v>
+        <v>2974.91115431123</v>
       </c>
       <c r="D34">
-        <v>4451.681336718691</v>
+        <v>4417.11215431123</v>
       </c>
       <c r="E34">
-        <v>-1473.696</v>
+        <v>-1428.999</v>
       </c>
       <c r="F34">
-        <v>1430.304</v>
+        <v>1475.001</v>
       </c>
       <c r="G34">
         <v>32.8</v>
@@ -4081,45 +4081,45 @@
         <v>375.475</v>
       </c>
       <c r="M34">
-        <v>104.6599683177783</v>
+        <v>112.0605951277089</v>
       </c>
       <c r="N34">
-        <v>270.8150316822217</v>
+        <v>263.4144048722911</v>
       </c>
       <c r="O34">
-        <v>56.87115665326655</v>
+        <v>55.31702502318114</v>
       </c>
       <c r="P34">
-        <v>213.9438750289551</v>
+        <v>208.09737984911</v>
       </c>
       <c r="Q34">
-        <v>497.8438750289551</v>
+        <v>491.99737984911</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08193774984558502</v>
+        <v>0.08239454854470327</v>
       </c>
       <c r="T34">
-        <v>0.6093343786688883</v>
+        <v>0.6170366609829039</v>
       </c>
       <c r="U34">
-        <v>0.0731732333250682</v>
+        <v>0.0759732333250682</v>
       </c>
       <c r="V34">
         <v>0.21</v>
       </c>
       <c r="W34">
-        <v>0.05780685432680388</v>
+        <v>0.06001885432680388</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.5875703579419</v>
+        <v>3.350642565944729</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07501056945279647</v>
+        <v>0.07509743562601787</v>
       </c>
       <c r="C35">
-        <v>2974.91115431123</v>
+        <v>2926.468056670222</v>
       </c>
       <c r="D35">
-        <v>4417.11215431123</v>
+        <v>4413.366056670222</v>
       </c>
       <c r="E35">
-        <v>-1428.999</v>
+        <v>-1384.302</v>
       </c>
       <c r="F35">
-        <v>1475.001</v>
+        <v>1519.698</v>
       </c>
       <c r="G35">
         <v>32.8</v>
@@ -4163,28 +4163,28 @@
         <v>375.475</v>
       </c>
       <c r="M35">
-        <v>112.0605951277089</v>
+        <v>115.4563707376395</v>
       </c>
       <c r="N35">
-        <v>263.4144048722911</v>
+        <v>260.0186292623605</v>
       </c>
       <c r="O35">
-        <v>55.31702502318114</v>
+        <v>54.60391214509571</v>
       </c>
       <c r="P35">
-        <v>208.09737984911</v>
+        <v>205.4147171172648</v>
       </c>
       <c r="Q35">
-        <v>491.99737984911</v>
+        <v>489.3147171172648</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08239454854470327</v>
+        <v>0.08286518962864327</v>
       </c>
       <c r="T35">
-        <v>0.6170366609829039</v>
+        <v>0.6249723457912837</v>
       </c>
       <c r="U35">
         <v>0.0759732333250682</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.350642565944729</v>
+        <v>3.252094255181649</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07509743562601787</v>
+        <v>0.07518430179923928</v>
       </c>
       <c r="C36">
-        <v>2926.468056670222</v>
+        <v>2878.031307682228</v>
       </c>
       <c r="D36">
-        <v>4413.366056670222</v>
+        <v>4409.626307682228</v>
       </c>
       <c r="E36">
-        <v>-1384.302</v>
+        <v>-1339.605</v>
       </c>
       <c r="F36">
-        <v>1519.698</v>
+        <v>1564.395</v>
       </c>
       <c r="G36">
         <v>32.8</v>
@@ -4245,28 +4245,28 @@
         <v>375.475</v>
       </c>
       <c r="M36">
-        <v>115.4563707376395</v>
+        <v>118.8521463475701</v>
       </c>
       <c r="N36">
-        <v>260.0186292623605</v>
+        <v>256.62285365243</v>
       </c>
       <c r="O36">
-        <v>54.60391214509571</v>
+        <v>53.89079926701029</v>
       </c>
       <c r="P36">
-        <v>205.4147171172648</v>
+        <v>202.7320543854197</v>
       </c>
       <c r="Q36">
-        <v>489.3147171172648</v>
+        <v>486.6320543854197</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08286518962864327</v>
+        <v>0.08335031197670451</v>
       </c>
       <c r="T36">
-        <v>0.6249723457912837</v>
+        <v>0.6331522055168443</v>
       </c>
       <c r="U36">
         <v>0.0759732333250682</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.252094255181649</v>
+        <v>3.159177276462173</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07518430179923928</v>
+        <v>0.0752711679724607</v>
       </c>
       <c r="C37">
-        <v>2878.031307682228</v>
+        <v>2829.600891221961</v>
       </c>
       <c r="D37">
-        <v>4409.626307682228</v>
+        <v>4405.892891221961</v>
       </c>
       <c r="E37">
-        <v>-1339.605</v>
+        <v>-1294.908</v>
       </c>
       <c r="F37">
-        <v>1564.395</v>
+        <v>1609.092</v>
       </c>
       <c r="G37">
         <v>32.8</v>
@@ -4327,28 +4327,28 @@
         <v>375.475</v>
       </c>
       <c r="M37">
-        <v>118.8521463475701</v>
+        <v>122.2479219575006</v>
       </c>
       <c r="N37">
-        <v>256.62285365243</v>
+        <v>253.2270780424994</v>
       </c>
       <c r="O37">
-        <v>53.89079926701029</v>
+        <v>53.17768638892487</v>
       </c>
       <c r="P37">
-        <v>202.7320543854197</v>
+        <v>200.0493916535745</v>
       </c>
       <c r="Q37">
-        <v>486.6320543854197</v>
+        <v>483.9493916535745</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08335031197670451</v>
+        <v>0.08385059439814266</v>
       </c>
       <c r="T37">
-        <v>0.6331522055168443</v>
+        <v>0.6415876858588287</v>
       </c>
       <c r="U37">
         <v>0.0759732333250682</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.159177276462173</v>
+        <v>3.071422352116002</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0752711679724607</v>
+        <v>0.07763797414568209</v>
       </c>
       <c r="C38">
-        <v>2829.600891221961</v>
+        <v>2685.558908705764</v>
       </c>
       <c r="D38">
-        <v>4405.892891221961</v>
+        <v>4306.547908705764</v>
       </c>
       <c r="E38">
-        <v>-1294.908</v>
+        <v>-1250.211</v>
       </c>
       <c r="F38">
-        <v>1609.092</v>
+        <v>1653.789</v>
       </c>
       <c r="G38">
         <v>32.8</v>
@@ -4409,45 +4409,45 @@
         <v>375.475</v>
       </c>
       <c r="M38">
-        <v>122.2479219575006</v>
+        <v>138.5432517674312</v>
       </c>
       <c r="N38">
-        <v>253.2270780424994</v>
+        <v>236.9317482325688</v>
       </c>
       <c r="O38">
-        <v>53.17768638892487</v>
+        <v>49.75566712883945</v>
       </c>
       <c r="P38">
-        <v>200.0493916535745</v>
+        <v>187.1760811037294</v>
       </c>
       <c r="Q38">
-        <v>483.9493916535745</v>
+        <v>471.0760811037293</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08385059439814266</v>
+        <v>0.08436675880121375</v>
       </c>
       <c r="T38">
-        <v>0.6415876858588286</v>
+        <v>0.6502909592275427</v>
       </c>
       <c r="U38">
-        <v>0.0759732333250682</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V38">
         <v>0.21</v>
       </c>
       <c r="W38">
-        <v>0.06001885432680388</v>
+        <v>0.06618085432680387</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.071422352116002</v>
+        <v>2.710164480838805</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07763797414568209</v>
+        <v>0.07778646031890352</v>
       </c>
       <c r="C39">
-        <v>2685.558908705764</v>
+        <v>2634.778448300885</v>
       </c>
       <c r="D39">
-        <v>4306.547908705764</v>
+        <v>4300.464448300884</v>
       </c>
       <c r="E39">
-        <v>-1250.211</v>
+        <v>-1205.514</v>
       </c>
       <c r="F39">
-        <v>1653.789</v>
+        <v>1698.486</v>
       </c>
       <c r="G39">
         <v>32.8</v>
@@ -4491,28 +4491,28 @@
         <v>375.475</v>
       </c>
       <c r="M39">
-        <v>138.5432517674312</v>
+        <v>142.2876639773618</v>
       </c>
       <c r="N39">
-        <v>236.9317482325688</v>
+        <v>233.1873360226382</v>
       </c>
       <c r="O39">
-        <v>49.75566712883945</v>
+        <v>48.96934056475403</v>
       </c>
       <c r="P39">
-        <v>187.1760811037294</v>
+        <v>184.2179954578842</v>
       </c>
       <c r="Q39">
-        <v>471.0760811037293</v>
+        <v>468.1179954578842</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08436675880121375</v>
+        <v>0.08489957366890008</v>
       </c>
       <c r="T39">
-        <v>0.6502909592275427</v>
+        <v>0.6592749833500864</v>
       </c>
       <c r="U39">
         <v>0.0837732333250682</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.710164480838805</v>
+        <v>2.638844362921994</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07778646031890352</v>
+        <v>0.07793494649212493</v>
       </c>
       <c r="C40">
-        <v>2634.778448300885</v>
+        <v>2584.015150731095</v>
       </c>
       <c r="D40">
-        <v>4300.464448300884</v>
+        <v>4294.398150731095</v>
       </c>
       <c r="E40">
-        <v>-1205.514</v>
+        <v>-1160.817</v>
       </c>
       <c r="F40">
-        <v>1698.486</v>
+        <v>1743.183</v>
       </c>
       <c r="G40">
         <v>32.8</v>
@@ -4573,28 +4573,28 @@
         <v>375.475</v>
       </c>
       <c r="M40">
-        <v>142.2876639773618</v>
+        <v>146.0320761872923</v>
       </c>
       <c r="N40">
-        <v>233.1873360226382</v>
+        <v>229.4429238127077</v>
       </c>
       <c r="O40">
-        <v>48.96934056475403</v>
+        <v>48.18301400066861</v>
       </c>
       <c r="P40">
-        <v>184.2179954578842</v>
+        <v>181.2599098120391</v>
       </c>
       <c r="Q40">
-        <v>468.1179954578842</v>
+        <v>465.159909812039</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08489957366890008</v>
+        <v>0.08544985787651052</v>
       </c>
       <c r="T40">
-        <v>0.6592749833500864</v>
+        <v>0.6685535656405821</v>
       </c>
       <c r="U40">
         <v>0.0837732333250682</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.638844362921994</v>
+        <v>2.571181686949635</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07793494649212493</v>
+        <v>0.07808343266534633</v>
       </c>
       <c r="C41">
-        <v>2584.015150731095</v>
+        <v>2533.268943468274</v>
       </c>
       <c r="D41">
-        <v>4294.398150731095</v>
+        <v>4288.348943468274</v>
       </c>
       <c r="E41">
-        <v>-1160.817</v>
+        <v>-1116.12</v>
       </c>
       <c r="F41">
-        <v>1743.183</v>
+        <v>1787.88</v>
       </c>
       <c r="G41">
         <v>32.8</v>
@@ -4655,28 +4655,28 @@
         <v>375.475</v>
       </c>
       <c r="M41">
-        <v>146.0320761872923</v>
+        <v>149.7764883972229</v>
       </c>
       <c r="N41">
-        <v>229.4429238127077</v>
+        <v>225.6985116027771</v>
       </c>
       <c r="O41">
-        <v>48.18301400066861</v>
+        <v>47.39668743658319</v>
       </c>
       <c r="P41">
-        <v>181.2599098120391</v>
+        <v>178.3018241661939</v>
       </c>
       <c r="Q41">
-        <v>465.159909812039</v>
+        <v>462.2018241661939</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08544985787651052</v>
+        <v>0.0860184848910413</v>
       </c>
       <c r="T41">
-        <v>0.6685535656405821</v>
+        <v>0.6781414340074278</v>
       </c>
       <c r="U41">
         <v>0.0837732333250682</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.571181686949635</v>
+        <v>2.506902144775894</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07808343266534633</v>
+        <v>0.07949512883856774</v>
       </c>
       <c r="C42">
-        <v>2533.268943468274</v>
+        <v>2431.900542733355</v>
       </c>
       <c r="D42">
-        <v>4288.348943468274</v>
+        <v>4231.677542733355</v>
       </c>
       <c r="E42">
-        <v>-1116.12</v>
+        <v>-1071.423</v>
       </c>
       <c r="F42">
-        <v>1787.88</v>
+        <v>1832.577</v>
       </c>
       <c r="G42">
         <v>32.8</v>
@@ -4737,45 +4737,45 @@
         <v>375.475</v>
       </c>
       <c r="M42">
-        <v>149.7764883972229</v>
+        <v>160.6679509071535</v>
       </c>
       <c r="N42">
-        <v>225.6985116027771</v>
+        <v>214.8070490928465</v>
       </c>
       <c r="O42">
-        <v>47.39668743658319</v>
+        <v>45.10948030949777</v>
       </c>
       <c r="P42">
-        <v>178.3018241661939</v>
+        <v>169.6975687833487</v>
       </c>
       <c r="Q42">
-        <v>462.2018241661939</v>
+        <v>453.5975687833487</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0860184848910413</v>
+        <v>0.08660638739759009</v>
       </c>
       <c r="T42">
-        <v>0.6781414340074278</v>
+        <v>0.6880543148612851</v>
       </c>
       <c r="U42">
-        <v>0.0837732333250682</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V42">
         <v>0.21</v>
       </c>
       <c r="W42">
-        <v>0.06618085432680387</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.506902144775894</v>
+        <v>2.336962647995547</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07949512883856774</v>
+        <v>0.07967442501178916</v>
       </c>
       <c r="C43">
-        <v>2431.900542733355</v>
+        <v>2380.112863201747</v>
       </c>
       <c r="D43">
-        <v>4231.677542733355</v>
+        <v>4224.586863201747</v>
       </c>
       <c r="E43">
-        <v>-1071.423</v>
+        <v>-1026.726</v>
       </c>
       <c r="F43">
-        <v>1832.577</v>
+        <v>1877.274</v>
       </c>
       <c r="G43">
         <v>32.8</v>
@@ -4819,28 +4819,28 @@
         <v>375.475</v>
       </c>
       <c r="M43">
-        <v>160.6679509071535</v>
+        <v>164.5866814170841</v>
       </c>
       <c r="N43">
-        <v>214.8070490928465</v>
+        <v>210.8883185829159</v>
       </c>
       <c r="O43">
-        <v>45.10948030949777</v>
+        <v>44.28654690241234</v>
       </c>
       <c r="P43">
-        <v>169.6975687833487</v>
+        <v>166.6017716805036</v>
       </c>
       <c r="Q43">
-        <v>453.5975687833487</v>
+        <v>450.5017716805036</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08660638739759009</v>
+        <v>0.0872145624043647</v>
       </c>
       <c r="T43">
-        <v>0.6880543148612851</v>
+        <v>0.6983090191928617</v>
       </c>
       <c r="U43">
         <v>0.0876732333250682</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.336962647995547</v>
+        <v>2.281320680186129</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07967442501178915</v>
+        <v>0.07985372118501056</v>
       </c>
       <c r="C44">
-        <v>2380.112863201748</v>
+        <v>2328.34890647525</v>
       </c>
       <c r="D44">
-        <v>4224.586863201748</v>
+        <v>4217.51990647525</v>
       </c>
       <c r="E44">
-        <v>-1026.726</v>
+        <v>-982.029</v>
       </c>
       <c r="F44">
-        <v>1877.274</v>
+        <v>1921.971</v>
       </c>
       <c r="G44">
         <v>32.8</v>
@@ -4901,28 +4901,28 @@
         <v>375.475</v>
       </c>
       <c r="M44">
-        <v>164.5866814170841</v>
+        <v>168.5054119270146</v>
       </c>
       <c r="N44">
-        <v>210.888318582916</v>
+        <v>206.9695880729854</v>
       </c>
       <c r="O44">
-        <v>44.28654690241235</v>
+        <v>43.46361349532692</v>
       </c>
       <c r="P44">
-        <v>166.6017716805036</v>
+        <v>163.5059745776584</v>
       </c>
       <c r="Q44">
-        <v>450.5017716805036</v>
+        <v>447.4059745776584</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08721456240436469</v>
+        <v>0.08784407688506121</v>
       </c>
       <c r="T44">
-        <v>0.6983090191928616</v>
+        <v>0.7089235377115111</v>
       </c>
       <c r="U44">
         <v>0.0876732333250682</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.28132068018613</v>
+        <v>2.228266710879475</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07985372118501056</v>
+        <v>0.08003301735823197</v>
       </c>
       <c r="C45">
-        <v>2328.34890647525</v>
+        <v>2276.608553701012</v>
       </c>
       <c r="D45">
-        <v>4217.51990647525</v>
+        <v>4210.476553701012</v>
       </c>
       <c r="E45">
-        <v>-982.029</v>
+        <v>-937.3320000000001</v>
       </c>
       <c r="F45">
-        <v>1921.971</v>
+        <v>1966.668</v>
       </c>
       <c r="G45">
         <v>32.8</v>
@@ -4983,28 +4983,28 @@
         <v>375.475</v>
       </c>
       <c r="M45">
-        <v>168.5054119270146</v>
+        <v>172.4241424369452</v>
       </c>
       <c r="N45">
-        <v>206.9695880729854</v>
+        <v>203.0508575630548</v>
       </c>
       <c r="O45">
-        <v>43.46361349532692</v>
+        <v>42.64068008824151</v>
       </c>
       <c r="P45">
-        <v>163.5059745776584</v>
+        <v>160.4101774748133</v>
       </c>
       <c r="Q45">
-        <v>447.4059745776584</v>
+        <v>444.3101774748133</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08784407688506121</v>
+        <v>0.08849607402578262</v>
       </c>
       <c r="T45">
-        <v>0.7089235377115111</v>
+        <v>0.7199171461772552</v>
       </c>
       <c r="U45">
         <v>0.0876732333250682</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.228266710879475</v>
+        <v>2.177624285632215</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08003301735823197</v>
+        <v>0.08021231353145339</v>
       </c>
       <c r="C46">
-        <v>2276.608553701012</v>
+        <v>2224.89168681881</v>
       </c>
       <c r="D46">
-        <v>4210.476553701012</v>
+        <v>4203.456686818809</v>
       </c>
       <c r="E46">
-        <v>-937.3320000000001</v>
+        <v>-892.635</v>
       </c>
       <c r="F46">
-        <v>1966.668</v>
+        <v>2011.365</v>
       </c>
       <c r="G46">
         <v>32.8</v>
@@ -5065,28 +5065,28 @@
         <v>375.475</v>
       </c>
       <c r="M46">
-        <v>172.4241424369452</v>
+        <v>176.3428729468758</v>
       </c>
       <c r="N46">
-        <v>203.0508575630548</v>
+        <v>199.1321270531242</v>
       </c>
       <c r="O46">
-        <v>42.64068008824151</v>
+        <v>41.81774668115609</v>
       </c>
       <c r="P46">
-        <v>160.4101774748133</v>
+        <v>157.3143803719682</v>
       </c>
       <c r="Q46">
-        <v>444.3101774748133</v>
+        <v>441.2143803719681</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08849607402578262</v>
+        <v>0.08917178015343935</v>
       </c>
       <c r="T46">
-        <v>0.7199171461772552</v>
+        <v>0.7313105222235718</v>
       </c>
       <c r="U46">
         <v>0.0876732333250682</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.177624285632215</v>
+        <v>2.129232634840387</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08021231353145339</v>
+        <v>0.08039160970467479</v>
       </c>
       <c r="C47">
-        <v>2224.89168681881</v>
+        <v>2173.198188554446</v>
       </c>
       <c r="D47">
-        <v>4203.456686818809</v>
+        <v>4196.460188554446</v>
       </c>
       <c r="E47">
-        <v>-892.635</v>
+        <v>-847.9380000000001</v>
       </c>
       <c r="F47">
-        <v>2011.365</v>
+        <v>2056.062</v>
       </c>
       <c r="G47">
         <v>32.8</v>
@@ -5147,28 +5147,28 @@
         <v>375.475</v>
       </c>
       <c r="M47">
-        <v>176.3428729468758</v>
+        <v>180.2616034568064</v>
       </c>
       <c r="N47">
-        <v>199.1321270531242</v>
+        <v>195.2133965431937</v>
       </c>
       <c r="O47">
-        <v>41.81774668115609</v>
+        <v>40.99481327407067</v>
       </c>
       <c r="P47">
-        <v>157.3143803719682</v>
+        <v>154.218583269123</v>
       </c>
       <c r="Q47">
-        <v>441.2143803719681</v>
+        <v>438.118583269123</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08917178015343935</v>
+        <v>0.08987251243397223</v>
       </c>
       <c r="T47">
-        <v>0.7313105222235718</v>
+        <v>0.7431258751604928</v>
       </c>
       <c r="U47">
         <v>0.0876732333250682</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.129232634840387</v>
+        <v>2.082944968865596</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08039160970467479</v>
+        <v>0.0805709058778962</v>
       </c>
       <c r="C48">
-        <v>2173.198188554446</v>
+        <v>2121.52794241322</v>
       </c>
       <c r="D48">
-        <v>4196.460188554446</v>
+        <v>4189.48694241322</v>
       </c>
       <c r="E48">
-        <v>-847.9380000000001</v>
+        <v>-803.241</v>
       </c>
       <c r="F48">
-        <v>2056.062</v>
+        <v>2100.759</v>
       </c>
       <c r="G48">
         <v>32.8</v>
@@ -5229,28 +5229,28 @@
         <v>375.475</v>
       </c>
       <c r="M48">
-        <v>180.2616034568064</v>
+        <v>184.180333966737</v>
       </c>
       <c r="N48">
-        <v>195.2133965431937</v>
+        <v>191.2946660332631</v>
       </c>
       <c r="O48">
-        <v>40.99481327407067</v>
+        <v>40.17187986698524</v>
       </c>
       <c r="P48">
-        <v>154.218583269123</v>
+        <v>151.1227861662778</v>
       </c>
       <c r="Q48">
-        <v>438.118583269123</v>
+        <v>435.0227861662778</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08987251243397223</v>
+        <v>0.09059968744207242</v>
       </c>
       <c r="T48">
-        <v>0.7431258751604928</v>
+        <v>0.7553870904723918</v>
       </c>
       <c r="U48">
         <v>0.0876732333250682</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.082944968865596</v>
+        <v>2.038626990804626</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0805709058778962</v>
+        <v>0.08613484205111761</v>
       </c>
       <c r="C49">
-        <v>2121.52794241322</v>
+        <v>1871.389841503453</v>
       </c>
       <c r="D49">
-        <v>4189.48694241322</v>
+        <v>3984.045841503453</v>
       </c>
       <c r="E49">
-        <v>-803.241</v>
+        <v>-758.5439999999999</v>
       </c>
       <c r="F49">
-        <v>2100.759</v>
+        <v>2145.456</v>
       </c>
       <c r="G49">
         <v>32.8</v>
@@ -5311,45 +5311,45 @@
         <v>375.475</v>
       </c>
       <c r="M49">
-        <v>184.180333966737</v>
+        <v>218.5645396766676</v>
       </c>
       <c r="N49">
-        <v>191.2946660332631</v>
+        <v>156.9104603233325</v>
       </c>
       <c r="O49">
-        <v>40.17187986698524</v>
+        <v>32.95119666789981</v>
       </c>
       <c r="P49">
-        <v>151.1227861662778</v>
+        <v>123.9592636554327</v>
       </c>
       <c r="Q49">
-        <v>435.0227861662778</v>
+        <v>407.8592636554326</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09059968744207242</v>
+        <v>0.0913548307197149</v>
       </c>
       <c r="T49">
-        <v>0.7553870904723918</v>
+        <v>0.7681198909885947</v>
       </c>
       <c r="U49">
-        <v>0.0876732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V49">
         <v>0.21</v>
       </c>
       <c r="W49">
-        <v>0.06926185432680387</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.038626990804626</v>
+        <v>1.717913622015068</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0861348420511176</v>
+        <v>0.08642631822433902</v>
       </c>
       <c r="C50">
-        <v>1871.389841503454</v>
+        <v>1816.484445471647</v>
       </c>
       <c r="D50">
-        <v>3984.045841503453</v>
+        <v>3973.837445471646</v>
       </c>
       <c r="E50">
-        <v>-758.5440000000003</v>
+        <v>-713.8470000000002</v>
       </c>
       <c r="F50">
-        <v>2145.456</v>
+        <v>2190.153</v>
       </c>
       <c r="G50">
         <v>32.8</v>
@@ -5393,28 +5393,28 @@
         <v>375.475</v>
       </c>
       <c r="M50">
-        <v>218.5645396766675</v>
+        <v>223.1179675865981</v>
       </c>
       <c r="N50">
-        <v>156.9104603233325</v>
+        <v>152.357032413402</v>
       </c>
       <c r="O50">
-        <v>32.95119666789983</v>
+        <v>31.99497680681441</v>
       </c>
       <c r="P50">
-        <v>123.9592636554327</v>
+        <v>120.3620556065875</v>
       </c>
       <c r="Q50">
-        <v>407.8592636554326</v>
+        <v>404.2620556065875</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0913548307197149</v>
+        <v>0.09213958745922574</v>
       </c>
       <c r="T50">
-        <v>0.7681198909885946</v>
+        <v>0.7813520170152368</v>
       </c>
       <c r="U50">
         <v>0.1018732333250682</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.717913622015069</v>
+        <v>1.682854160341292</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08642631822433902</v>
+        <v>0.08671779439756043</v>
       </c>
       <c r="C51">
-        <v>1816.484445471647</v>
+        <v>1761.631230068986</v>
       </c>
       <c r="D51">
-        <v>3973.837445471646</v>
+        <v>3963.681230068986</v>
       </c>
       <c r="E51">
-        <v>-713.8470000000002</v>
+        <v>-669.1500000000001</v>
       </c>
       <c r="F51">
-        <v>2190.153</v>
+        <v>2234.85</v>
       </c>
       <c r="G51">
         <v>32.8</v>
@@ -5475,28 +5475,28 @@
         <v>375.475</v>
       </c>
       <c r="M51">
-        <v>223.1179675865981</v>
+        <v>227.6713954965287</v>
       </c>
       <c r="N51">
-        <v>152.357032413402</v>
+        <v>147.8036045034713</v>
       </c>
       <c r="O51">
-        <v>31.99497680681441</v>
+        <v>31.03875694572898</v>
       </c>
       <c r="P51">
-        <v>120.3620556065875</v>
+        <v>116.7648475577424</v>
       </c>
       <c r="Q51">
-        <v>404.2620556065875</v>
+        <v>400.6648475577423</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09213958745922574</v>
+        <v>0.09295573446831698</v>
       </c>
       <c r="T51">
-        <v>0.7813520170152368</v>
+        <v>0.7951134280829447</v>
       </c>
       <c r="U51">
         <v>0.1018732333250682</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.682854160341292</v>
+        <v>1.649197077134466</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08671779439756043</v>
+        <v>0.08700927057078184</v>
       </c>
       <c r="C52">
-        <v>1761.631230068986</v>
+        <v>1706.829796230297</v>
       </c>
       <c r="D52">
-        <v>3963.681230068986</v>
+        <v>3953.576796230297</v>
       </c>
       <c r="E52">
-        <v>-669.1500000000001</v>
+        <v>-624.453</v>
       </c>
       <c r="F52">
-        <v>2234.85</v>
+        <v>2279.547</v>
       </c>
       <c r="G52">
         <v>32.8</v>
@@ -5557,28 +5557,28 @@
         <v>375.475</v>
       </c>
       <c r="M52">
-        <v>227.6713954965287</v>
+        <v>232.2248234064593</v>
       </c>
       <c r="N52">
-        <v>147.8036045034713</v>
+        <v>143.2501765935408</v>
       </c>
       <c r="O52">
-        <v>31.03875694572898</v>
+        <v>30.08253708464356</v>
       </c>
       <c r="P52">
-        <v>116.7648475577424</v>
+        <v>113.1676395088972</v>
       </c>
       <c r="Q52">
-        <v>400.6648475577423</v>
+        <v>397.0676395088972</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09295573446831698</v>
+        <v>0.09380519360022829</v>
       </c>
       <c r="T52">
-        <v>0.7951134280829447</v>
+        <v>0.8094365293983142</v>
       </c>
       <c r="U52">
         <v>0.1018732333250682</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.649197077134466</v>
+        <v>1.616859879543594</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08700927057078184</v>
+        <v>0.08730074674400326</v>
       </c>
       <c r="C53">
-        <v>1706.829796230297</v>
+        <v>1652.079748949331</v>
       </c>
       <c r="D53">
-        <v>3953.576796230297</v>
+        <v>3943.523748949331</v>
       </c>
       <c r="E53">
-        <v>-624.453</v>
+        <v>-579.7559999999999</v>
       </c>
       <c r="F53">
-        <v>2279.547</v>
+        <v>2324.244</v>
       </c>
       <c r="G53">
         <v>32.8</v>
@@ -5639,28 +5639,28 @@
         <v>375.475</v>
       </c>
       <c r="M53">
-        <v>232.2248234064593</v>
+        <v>236.7782513163898</v>
       </c>
       <c r="N53">
-        <v>143.2501765935408</v>
+        <v>138.6967486836102</v>
       </c>
       <c r="O53">
-        <v>30.08253708464356</v>
+        <v>29.12631722355814</v>
       </c>
       <c r="P53">
-        <v>113.1676395088972</v>
+        <v>109.570431460052</v>
       </c>
       <c r="Q53">
-        <v>397.0676395088972</v>
+        <v>393.4704314600521</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09380519360022829</v>
+        <v>0.09469004686263591</v>
       </c>
       <c r="T53">
-        <v>0.8094365293983142</v>
+        <v>0.8243564266018241</v>
       </c>
       <c r="U53">
         <v>0.1018732333250682</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.616859879543594</v>
+        <v>1.585766420321602</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08730074674400326</v>
+        <v>0.08759222291722465</v>
       </c>
       <c r="C54">
-        <v>1652.079748949331</v>
+        <v>1597.380697227297</v>
       </c>
       <c r="D54">
-        <v>3943.523748949331</v>
+        <v>3933.521697227297</v>
       </c>
       <c r="E54">
-        <v>-579.7559999999999</v>
+        <v>-535.0590000000002</v>
       </c>
       <c r="F54">
-        <v>2324.244</v>
+        <v>2368.941</v>
       </c>
       <c r="G54">
         <v>32.8</v>
@@ -5721,28 +5721,28 @@
         <v>375.475</v>
       </c>
       <c r="M54">
-        <v>236.7782513163898</v>
+        <v>241.3316792263204</v>
       </c>
       <c r="N54">
-        <v>138.6967486836102</v>
+        <v>134.1433207736796</v>
       </c>
       <c r="O54">
-        <v>29.12631722355814</v>
+        <v>28.17009736247272</v>
       </c>
       <c r="P54">
-        <v>109.570431460052</v>
+        <v>105.9732234112069</v>
       </c>
       <c r="Q54">
-        <v>393.4704314600521</v>
+        <v>389.8732234112069</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09469004686263591</v>
+        <v>0.09561255345535874</v>
       </c>
       <c r="T54">
-        <v>0.8243564266018241</v>
+        <v>0.8399112130480364</v>
       </c>
       <c r="U54">
         <v>0.1018732333250682</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.585766420321602</v>
+        <v>1.555846299183458</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08759222291722465</v>
+        <v>0.08788369909044608</v>
       </c>
       <c r="C55">
-        <v>1597.380697227297</v>
+        <v>1542.732254022163</v>
       </c>
       <c r="D55">
-        <v>3933.521697227297</v>
+        <v>3923.570254022163</v>
       </c>
       <c r="E55">
-        <v>-535.0590000000002</v>
+        <v>-490.3620000000001</v>
       </c>
       <c r="F55">
-        <v>2368.941</v>
+        <v>2413.638</v>
       </c>
       <c r="G55">
         <v>32.8</v>
@@ -5803,28 +5803,28 @@
         <v>375.475</v>
       </c>
       <c r="M55">
-        <v>241.3316792263204</v>
+        <v>245.885107136251</v>
       </c>
       <c r="N55">
-        <v>134.1433207736796</v>
+        <v>129.5898928637491</v>
       </c>
       <c r="O55">
-        <v>28.17009736247272</v>
+        <v>27.21387750138731</v>
       </c>
       <c r="P55">
-        <v>105.9732234112069</v>
+        <v>102.3760153623618</v>
       </c>
       <c r="Q55">
-        <v>389.8732234112069</v>
+        <v>386.2760153623618</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09561255345535874</v>
+        <v>0.09657516903037386</v>
       </c>
       <c r="T55">
-        <v>0.8399112130480364</v>
+        <v>0.8561422945571275</v>
       </c>
       <c r="U55">
         <v>0.1018732333250682</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.555846299183458</v>
+        <v>1.527034330680061</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08788369909044608</v>
+        <v>0.1136544472932001</v>
       </c>
       <c r="C56">
-        <v>1542.732254022163</v>
+        <v>780.8327206526733</v>
       </c>
       <c r="D56">
-        <v>3923.570254022163</v>
+        <v>3206.367720652673</v>
       </c>
       <c r="E56">
-        <v>-490.3620000000001</v>
+        <v>-445.665</v>
       </c>
       <c r="F56">
-        <v>2413.638</v>
+        <v>2458.335</v>
       </c>
       <c r="G56">
         <v>32.8</v>
@@ -5885,45 +5885,45 @@
         <v>375.475</v>
       </c>
       <c r="M56">
-        <v>245.885107136251</v>
+        <v>390.0719630461816</v>
       </c>
       <c r="N56">
-        <v>129.5898928637491</v>
+        <v>-14.59696304618154</v>
       </c>
       <c r="O56">
-        <v>27.21387750138731</v>
+        <v>-3.065362239698124</v>
       </c>
       <c r="P56">
-        <v>102.3760153623618</v>
+        <v>-11.53160080648342</v>
       </c>
       <c r="Q56">
-        <v>386.2760153623618</v>
+        <v>272.3683991935166</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09657516903037386</v>
+        <v>0.09783359560310273</v>
       </c>
       <c r="T56">
-        <v>0.8561422945571275</v>
+        <v>0.8773611744561437</v>
       </c>
       <c r="U56">
-        <v>0.1018732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V56">
-        <v>0.21</v>
+        <v>0.2021415468680193</v>
       </c>
       <c r="W56">
-        <v>0.08047985432680388</v>
+        <v>0.1265987804941888</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.527034330680061</v>
+        <v>0.9625787946096157</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1136544472932001</v>
+        <v>0.1147831796264507</v>
       </c>
       <c r="C57">
-        <v>780.8327206526733</v>
+        <v>710.6689157635783</v>
       </c>
       <c r="D57">
-        <v>3206.367720652673</v>
+        <v>3180.900915763578</v>
       </c>
       <c r="E57">
-        <v>-445.665</v>
+        <v>-400.9679999999998</v>
       </c>
       <c r="F57">
-        <v>2458.335</v>
+        <v>2503.032</v>
       </c>
       <c r="G57">
         <v>32.8</v>
@@ -5967,37 +5967,37 @@
         <v>375.475</v>
       </c>
       <c r="M57">
-        <v>390.0719630461816</v>
+        <v>397.1641805561122</v>
       </c>
       <c r="N57">
-        <v>-14.59696304618154</v>
+        <v>-21.68918055611215</v>
       </c>
       <c r="O57">
-        <v>-3.065362239698124</v>
+        <v>-4.554727916783551</v>
       </c>
       <c r="P57">
-        <v>-11.53160080648342</v>
+        <v>-17.1344526393286</v>
       </c>
       <c r="Q57">
-        <v>272.3683991935166</v>
+        <v>266.7655473606714</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09783359560310273</v>
+        <v>0.09901617732135506</v>
       </c>
       <c r="T57">
-        <v>0.8773611744561437</v>
+        <v>0.8973012011483288</v>
       </c>
       <c r="U57">
         <v>0.1586732333250682</v>
       </c>
       <c r="V57">
-        <v>0.2021415468680193</v>
+        <v>0.1985318763882332</v>
       </c>
       <c r="W57">
-        <v>0.1265987804941888</v>
+        <v>0.1271715385804545</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9625787946096157</v>
+        <v>0.9453898875630153</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1147831796264507</v>
+        <v>0.1159119119597014</v>
       </c>
       <c r="C58">
-        <v>710.6689157635783</v>
+        <v>640.9064669130635</v>
       </c>
       <c r="D58">
-        <v>3180.900915763578</v>
+        <v>3155.835466913064</v>
       </c>
       <c r="E58">
-        <v>-400.9679999999998</v>
+        <v>-356.2709999999997</v>
       </c>
       <c r="F58">
-        <v>2503.032</v>
+        <v>2547.729</v>
       </c>
       <c r="G58">
         <v>32.8</v>
@@ -6049,37 +6049,37 @@
         <v>375.475</v>
       </c>
       <c r="M58">
-        <v>397.1641805561122</v>
+        <v>404.2563980660428</v>
       </c>
       <c r="N58">
-        <v>-21.68918055611215</v>
+        <v>-28.78139806604275</v>
       </c>
       <c r="O58">
-        <v>-4.554727916783551</v>
+        <v>-6.044093593868978</v>
       </c>
       <c r="P58">
-        <v>-17.1344526393286</v>
+        <v>-22.73730447217378</v>
       </c>
       <c r="Q58">
-        <v>266.7655473606714</v>
+        <v>261.1626955278262</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09901617732135506</v>
+        <v>0.1002537628404563</v>
       </c>
       <c r="T58">
-        <v>0.8973012011483288</v>
+        <v>0.918168670942476</v>
       </c>
       <c r="U58">
         <v>0.1586732333250682</v>
       </c>
       <c r="V58">
-        <v>0.1985318763882332</v>
+        <v>0.195048861013001</v>
       </c>
       <c r="W58">
-        <v>0.1271715385804545</v>
+        <v>0.1277241998917635</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9453898875630153</v>
+        <v>0.9288041000619097</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1159119119597014</v>
+        <v>0.1170406442929521</v>
       </c>
       <c r="C59">
-        <v>640.9064669130635</v>
+        <v>571.5359602444823</v>
       </c>
       <c r="D59">
-        <v>3155.835466913064</v>
+        <v>3131.161960244483</v>
       </c>
       <c r="E59">
-        <v>-356.2709999999997</v>
+        <v>-311.5739999999996</v>
       </c>
       <c r="F59">
-        <v>2547.729</v>
+        <v>2592.426</v>
       </c>
       <c r="G59">
         <v>32.8</v>
@@ -6131,37 +6131,37 @@
         <v>375.475</v>
       </c>
       <c r="M59">
-        <v>404.2563980660428</v>
+        <v>411.3486155759734</v>
       </c>
       <c r="N59">
-        <v>-28.78139806604275</v>
+        <v>-35.87361557597336</v>
       </c>
       <c r="O59">
-        <v>-6.044093593868978</v>
+        <v>-7.533459270954405</v>
       </c>
       <c r="P59">
-        <v>-22.73730447217378</v>
+        <v>-28.34015630501895</v>
       </c>
       <c r="Q59">
-        <v>261.1626955278262</v>
+        <v>255.559843694981</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1002537628404563</v>
+        <v>0.1015502810033244</v>
       </c>
       <c r="T59">
-        <v>0.918168670942476</v>
+        <v>0.9400298297744398</v>
       </c>
       <c r="U59">
         <v>0.1586732333250682</v>
       </c>
       <c r="V59">
-        <v>0.195048861013001</v>
+        <v>0.1916859496162251</v>
       </c>
       <c r="W59">
-        <v>0.1277241998917635</v>
+        <v>0.1282578039164757</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9288041000619097</v>
+        <v>0.9127902362677388</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1170406442929521</v>
+        <v>0.1181693766262028</v>
       </c>
       <c r="C60">
-        <v>571.5359602444832</v>
+        <v>502.5482740215502</v>
       </c>
       <c r="D60">
-        <v>3131.161960244483</v>
+        <v>3106.87127402155</v>
       </c>
       <c r="E60">
-        <v>-311.5740000000001</v>
+        <v>-266.8770000000004</v>
       </c>
       <c r="F60">
-        <v>2592.426</v>
+        <v>2637.123</v>
       </c>
       <c r="G60">
         <v>32.8</v>
@@ -6213,37 +6213,37 @@
         <v>375.475</v>
       </c>
       <c r="M60">
-        <v>411.3486155759733</v>
+        <v>418.4408330859038</v>
       </c>
       <c r="N60">
-        <v>-35.87361557597325</v>
+        <v>-42.9658330859038</v>
       </c>
       <c r="O60">
-        <v>-7.533459270954381</v>
+        <v>-9.022824948039796</v>
       </c>
       <c r="P60">
-        <v>-28.34015630501887</v>
+        <v>-33.943008137864</v>
       </c>
       <c r="Q60">
-        <v>255.5598436949811</v>
+        <v>249.956991862136</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1015502810033243</v>
+        <v>0.1029100439546249</v>
       </c>
       <c r="T60">
-        <v>0.9400298297744395</v>
+        <v>0.9629573865982063</v>
       </c>
       <c r="U60">
         <v>0.1586732333250682</v>
       </c>
       <c r="V60">
-        <v>0.1916859496162252</v>
+        <v>0.1884370352159502</v>
       </c>
       <c r="W60">
-        <v>0.1282578039164756</v>
+        <v>0.1287733196691636</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9127902362677391</v>
+        <v>0.8973192153140487</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1181693766262028</v>
+        <v>0.1192981089594535</v>
       </c>
       <c r="C61">
-        <v>502.5482740215502</v>
+        <v>433.9345673846133</v>
       </c>
       <c r="D61">
-        <v>3106.87127402155</v>
+        <v>3082.954567384613</v>
       </c>
       <c r="E61">
-        <v>-266.8770000000004</v>
+        <v>-222.1800000000003</v>
       </c>
       <c r="F61">
-        <v>2637.123</v>
+        <v>2681.82</v>
       </c>
       <c r="G61">
         <v>32.8</v>
@@ -6295,37 +6295,37 @@
         <v>375.475</v>
       </c>
       <c r="M61">
-        <v>418.4408330859038</v>
+        <v>425.5330505958344</v>
       </c>
       <c r="N61">
-        <v>-42.9658330859038</v>
+        <v>-50.0580505958344</v>
       </c>
       <c r="O61">
-        <v>-9.022824948039796</v>
+        <v>-10.51219062512522</v>
       </c>
       <c r="P61">
-        <v>-33.943008137864</v>
+        <v>-39.54585997070917</v>
       </c>
       <c r="Q61">
-        <v>249.956991862136</v>
+        <v>244.3541400292908</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1029100439546249</v>
+        <v>0.1043377950534906</v>
       </c>
       <c r="T61">
-        <v>0.9629573865982063</v>
+        <v>0.9870313212631614</v>
       </c>
       <c r="U61">
         <v>0.1586732333250682</v>
       </c>
       <c r="V61">
-        <v>0.1884370352159502</v>
+        <v>0.185296417962351</v>
       </c>
       <c r="W61">
-        <v>0.1287733196691636</v>
+        <v>0.1292716515634287</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8973192153140487</v>
+        <v>0.8823638950588144</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1192981089594535</v>
+        <v>0.1204268412927041</v>
       </c>
       <c r="C62">
-        <v>433.9345673846133</v>
+        <v>365.6862696223066</v>
       </c>
       <c r="D62">
-        <v>3082.954567384613</v>
+        <v>3059.403269622306</v>
       </c>
       <c r="E62">
-        <v>-222.1800000000003</v>
+        <v>-177.4830000000002</v>
       </c>
       <c r="F62">
-        <v>2681.82</v>
+        <v>2726.517</v>
       </c>
       <c r="G62">
         <v>32.8</v>
@@ -6377,37 +6377,37 @@
         <v>375.475</v>
       </c>
       <c r="M62">
-        <v>425.5330505958344</v>
+        <v>432.625268105765</v>
       </c>
       <c r="N62">
-        <v>-50.0580505958344</v>
+        <v>-57.15026810576495</v>
       </c>
       <c r="O62">
-        <v>-10.51219062512522</v>
+        <v>-12.00155630221064</v>
       </c>
       <c r="P62">
-        <v>-39.54585997070917</v>
+        <v>-45.14871180355431</v>
       </c>
       <c r="Q62">
-        <v>244.3541400292908</v>
+        <v>238.7512881964457</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1043377950534906</v>
+        <v>0.1058387641574262</v>
       </c>
       <c r="T62">
-        <v>0.9870313212631614</v>
+        <v>1.012339816680166</v>
       </c>
       <c r="U62">
         <v>0.1586732333250682</v>
       </c>
       <c r="V62">
-        <v>0.185296417962351</v>
+        <v>0.1822587717662469</v>
       </c>
       <c r="W62">
-        <v>0.1292716515634287</v>
+        <v>0.1297536447070622</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8823638950588144</v>
+        <v>0.8678989131726045</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1204268412927041</v>
+        <v>0.1215555736259548</v>
       </c>
       <c r="C63">
-        <v>365.6862696223066</v>
+        <v>297.7950699311873</v>
       </c>
       <c r="D63">
-        <v>3059.403269622306</v>
+        <v>3036.209069931187</v>
       </c>
       <c r="E63">
-        <v>-177.4830000000002</v>
+        <v>-132.7860000000001</v>
       </c>
       <c r="F63">
-        <v>2726.517</v>
+        <v>2771.214</v>
       </c>
       <c r="G63">
         <v>32.8</v>
@@ -6459,37 +6459,37 @@
         <v>375.475</v>
       </c>
       <c r="M63">
-        <v>432.625268105765</v>
+        <v>439.7174856156956</v>
       </c>
       <c r="N63">
-        <v>-57.15026810576495</v>
+        <v>-64.24248561569556</v>
       </c>
       <c r="O63">
-        <v>-12.00155630221064</v>
+        <v>-13.49092197929607</v>
       </c>
       <c r="P63">
-        <v>-45.14871180355431</v>
+        <v>-50.75156363639949</v>
       </c>
       <c r="Q63">
-        <v>238.7512881964457</v>
+        <v>233.1484363636005</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1058387641574262</v>
+        <v>0.1074187316352532</v>
       </c>
       <c r="T63">
-        <v>1.012339816680166</v>
+        <v>1.038980338171749</v>
       </c>
       <c r="U63">
         <v>0.1586732333250682</v>
       </c>
       <c r="V63">
-        <v>0.1822587717662469</v>
+        <v>0.1793191141571139</v>
       </c>
       <c r="W63">
-        <v>0.1297536447070622</v>
+        <v>0.1302200896847719</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8678989131726045</v>
+        <v>0.8539005436053043</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1215555736259548</v>
+        <v>0.1226843059592055</v>
       </c>
       <c r="C64">
-        <v>297.7950699311873</v>
+        <v>230.2529076376959</v>
       </c>
       <c r="D64">
-        <v>3036.209069931187</v>
+        <v>3013.363907637696</v>
       </c>
       <c r="E64">
-        <v>-132.7860000000001</v>
+        <v>-88.08899999999994</v>
       </c>
       <c r="F64">
-        <v>2771.214</v>
+        <v>2815.911</v>
       </c>
       <c r="G64">
         <v>32.8</v>
@@ -6541,37 +6541,37 @@
         <v>375.475</v>
       </c>
       <c r="M64">
-        <v>439.7174856156956</v>
+        <v>446.8097031256262</v>
       </c>
       <c r="N64">
-        <v>-64.24248561569556</v>
+        <v>-71.33470312562616</v>
       </c>
       <c r="O64">
-        <v>-13.49092197929607</v>
+        <v>-14.98028765638149</v>
       </c>
       <c r="P64">
-        <v>-50.75156363639949</v>
+        <v>-56.35441546924467</v>
       </c>
       <c r="Q64">
-        <v>233.1484363636005</v>
+        <v>227.5455845307553</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1074187316352532</v>
+        <v>0.1090841027605303</v>
       </c>
       <c r="T64">
-        <v>1.038980338171749</v>
+        <v>1.067060887852067</v>
       </c>
       <c r="U64">
         <v>0.1586732333250682</v>
       </c>
       <c r="V64">
-        <v>0.1793191141571139</v>
+        <v>0.1764727790117629</v>
       </c>
       <c r="W64">
-        <v>0.1302200896847719</v>
+        <v>0.1306717268854116</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8539005436053043</v>
+        <v>0.8403465667226804</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1226843059592055</v>
+        <v>0.1238130382924562</v>
       </c>
       <c r="C65">
-        <v>230.2529076376959</v>
+        <v>163.0519628582451</v>
       </c>
       <c r="D65">
-        <v>3013.363907637696</v>
+        <v>2990.859962858245</v>
       </c>
       <c r="E65">
-        <v>-88.08899999999994</v>
+        <v>-43.39200000000028</v>
       </c>
       <c r="F65">
-        <v>2815.911</v>
+        <v>2860.608</v>
       </c>
       <c r="G65">
         <v>32.8</v>
@@ -6623,37 +6623,37 @@
         <v>375.475</v>
       </c>
       <c r="M65">
-        <v>446.8097031256262</v>
+        <v>453.9019206355567</v>
       </c>
       <c r="N65">
-        <v>-71.33470312562616</v>
+        <v>-78.42692063555666</v>
       </c>
       <c r="O65">
-        <v>-14.98028765638149</v>
+        <v>-16.4696533334669</v>
       </c>
       <c r="P65">
-        <v>-56.35441546924467</v>
+        <v>-61.95726730208976</v>
       </c>
       <c r="Q65">
-        <v>227.5455845307553</v>
+        <v>221.9427326979102</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1090841027605303</v>
+        <v>0.1108419945038784</v>
       </c>
       <c r="T65">
-        <v>1.067060887852067</v>
+        <v>1.096701468070179</v>
       </c>
       <c r="U65">
         <v>0.1586732333250682</v>
       </c>
       <c r="V65">
-        <v>0.1764727790117629</v>
+        <v>0.1737153918397041</v>
       </c>
       <c r="W65">
-        <v>0.1306717268854116</v>
+        <v>0.1311092504235312</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8403465667226804</v>
+        <v>0.8272161516176386</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1238130382924562</v>
+        <v>0.1249417706257069</v>
       </c>
       <c r="C66">
-        <v>163.0519628582451</v>
+        <v>96.18464757470974</v>
       </c>
       <c r="D66">
-        <v>2990.859962858245</v>
+        <v>2968.689647574709</v>
       </c>
       <c r="E66">
-        <v>-43.39200000000028</v>
+        <v>1.304999999999836</v>
       </c>
       <c r="F66">
-        <v>2860.608</v>
+        <v>2905.305</v>
       </c>
       <c r="G66">
         <v>32.8</v>
@@ -6705,37 +6705,37 @@
         <v>375.475</v>
       </c>
       <c r="M66">
-        <v>453.9019206355567</v>
+        <v>460.9941381454873</v>
       </c>
       <c r="N66">
-        <v>-78.42692063555666</v>
+        <v>-85.51913814548726</v>
       </c>
       <c r="O66">
-        <v>-16.4696533334669</v>
+        <v>-17.95901901055232</v>
       </c>
       <c r="P66">
-        <v>-61.95726730208976</v>
+        <v>-67.56011913493494</v>
       </c>
       <c r="Q66">
-        <v>221.9427326979102</v>
+        <v>216.339880865065</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1108419945038784</v>
+        <v>0.1127003372039892</v>
       </c>
       <c r="T66">
-        <v>1.096701468070179</v>
+        <v>1.128035795729328</v>
       </c>
       <c r="U66">
         <v>0.1586732333250682</v>
       </c>
       <c r="V66">
-        <v>0.1737153918397041</v>
+        <v>0.1710428473498625</v>
       </c>
       <c r="W66">
-        <v>0.1311092504235312</v>
+        <v>0.1315333116989395</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8272161516176386</v>
+        <v>0.8144897492850595</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1249417706257069</v>
+        <v>0.1260705029589576</v>
       </c>
       <c r="C67">
-        <v>96.18464757470974</v>
+        <v>29.64359710393683</v>
       </c>
       <c r="D67">
-        <v>2968.689647574709</v>
+        <v>2946.845597103937</v>
       </c>
       <c r="E67">
-        <v>1.304999999999836</v>
+        <v>46.00199999999995</v>
       </c>
       <c r="F67">
-        <v>2905.305</v>
+        <v>2950.002</v>
       </c>
       <c r="G67">
         <v>32.8</v>
@@ -6787,37 +6787,37 @@
         <v>375.475</v>
       </c>
       <c r="M67">
-        <v>460.9941381454873</v>
+        <v>468.0863556554179</v>
       </c>
       <c r="N67">
-        <v>-85.51913814548726</v>
+        <v>-92.61135565541787</v>
       </c>
       <c r="O67">
-        <v>-17.95901901055232</v>
+        <v>-19.44838468763775</v>
       </c>
       <c r="P67">
-        <v>-67.56011913493494</v>
+        <v>-73.16297096778011</v>
       </c>
       <c r="Q67">
-        <v>216.339880865065</v>
+        <v>210.7370290322199</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1127003372039892</v>
+        <v>0.1146679941805771</v>
       </c>
       <c r="T67">
-        <v>1.128035795729328</v>
+        <v>1.161213319133131</v>
       </c>
       <c r="U67">
         <v>0.1586732333250682</v>
       </c>
       <c r="V67">
-        <v>0.1710428473498625</v>
+        <v>0.1684512890566827</v>
       </c>
       <c r="W67">
-        <v>0.1315333116989395</v>
+        <v>0.1319445226326687</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8144897492850595</v>
+        <v>0.8021489955080131</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1260705029589576</v>
+        <v>0.1641229060125067</v>
       </c>
       <c r="C68">
-        <v>29.64359710393683</v>
+        <v>-600.7610099005137</v>
       </c>
       <c r="D68">
-        <v>2946.845597103937</v>
+        <v>2361.137990099486</v>
       </c>
       <c r="E68">
-        <v>46.00199999999995</v>
+        <v>90.69900000000007</v>
       </c>
       <c r="F68">
-        <v>2950.002</v>
+        <v>2994.699</v>
       </c>
       <c r="G68">
         <v>32.8</v>
@@ -6869,45 +6869,45 @@
         <v>375.475</v>
       </c>
       <c r="M68">
-        <v>468.0863556554179</v>
+        <v>636.8923191653485</v>
       </c>
       <c r="N68">
-        <v>-92.61135565541787</v>
+        <v>-261.4173191653484</v>
       </c>
       <c r="O68">
-        <v>-19.44838468763775</v>
+        <v>-54.89763702472317</v>
       </c>
       <c r="P68">
-        <v>-73.16297096778011</v>
+        <v>-206.5196821406253</v>
       </c>
       <c r="Q68">
-        <v>210.7370290322199</v>
+        <v>77.38031785937471</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1146679941805771</v>
+        <v>0.1190084507324082</v>
       </c>
       <c r="T68">
-        <v>1.161213319133131</v>
+        <v>1.234399652190678</v>
       </c>
       <c r="U68">
-        <v>0.1586732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V68">
-        <v>0.1684512890566827</v>
+        <v>0.1238038953010662</v>
       </c>
       <c r="W68">
-        <v>0.1319445226326687</v>
+        <v>0.1863434586131522</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8021489955080131</v>
+        <v>0.5895423585765054</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1641229060125067</v>
+        <v>0.1657916383457574</v>
       </c>
       <c r="C69">
-        <v>-600.7610099005137</v>
+        <v>-665.8603715581858</v>
       </c>
       <c r="D69">
-        <v>2361.137990099486</v>
+        <v>2340.735628441814</v>
       </c>
       <c r="E69">
-        <v>90.69900000000007</v>
+        <v>135.3960000000002</v>
       </c>
       <c r="F69">
-        <v>2994.699</v>
+        <v>3039.396</v>
       </c>
       <c r="G69">
         <v>32.8</v>
@@ -6951,37 +6951,37 @@
         <v>375.475</v>
       </c>
       <c r="M69">
-        <v>636.8923191653485</v>
+        <v>646.3981746752791</v>
       </c>
       <c r="N69">
-        <v>-261.4173191653484</v>
+        <v>-270.923174675279</v>
       </c>
       <c r="O69">
-        <v>-54.89763702472317</v>
+        <v>-56.8938666818086</v>
       </c>
       <c r="P69">
-        <v>-206.5196821406253</v>
+        <v>-214.0293079934704</v>
       </c>
       <c r="Q69">
-        <v>77.38031785937471</v>
+        <v>69.87069200652954</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1190084507324082</v>
+        <v>0.121296214817796</v>
       </c>
       <c r="T69">
-        <v>1.234399652190678</v>
+        <v>1.272974641321637</v>
       </c>
       <c r="U69">
         <v>0.2126732333250682</v>
       </c>
       <c r="V69">
-        <v>0.1238038953010662</v>
+        <v>0.1219832497819328</v>
       </c>
       <c r="W69">
-        <v>0.1863434586131522</v>
+        <v>0.1867306611824451</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5895423585765054</v>
+        <v>0.5808726180092039</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1657916383457574</v>
+        <v>0.1674603706790081</v>
       </c>
       <c r="C70">
-        <v>-665.8603715581858</v>
+        <v>-730.6101641977193</v>
       </c>
       <c r="D70">
-        <v>2340.735628441814</v>
+        <v>2320.682835802281</v>
       </c>
       <c r="E70">
-        <v>135.3960000000002</v>
+        <v>180.0930000000003</v>
       </c>
       <c r="F70">
-        <v>3039.396</v>
+        <v>3084.093</v>
       </c>
       <c r="G70">
         <v>32.8</v>
@@ -7033,37 +7033,37 @@
         <v>375.475</v>
       </c>
       <c r="M70">
-        <v>646.3981746752791</v>
+        <v>655.9040301852096</v>
       </c>
       <c r="N70">
-        <v>-270.923174675279</v>
+        <v>-280.4290301852096</v>
       </c>
       <c r="O70">
-        <v>-56.8938666818086</v>
+        <v>-58.89009633889402</v>
       </c>
       <c r="P70">
-        <v>-214.0293079934704</v>
+        <v>-221.5389338463156</v>
       </c>
       <c r="Q70">
-        <v>69.87069200652954</v>
+        <v>62.36106615368436</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.121296214817796</v>
+        <v>0.123731576586112</v>
       </c>
       <c r="T70">
-        <v>1.272974641321637</v>
+        <v>1.314038339428786</v>
       </c>
       <c r="U70">
         <v>0.2126732333250682</v>
       </c>
       <c r="V70">
-        <v>0.1219832497819328</v>
+        <v>0.1202153765966874</v>
       </c>
       <c r="W70">
-        <v>0.1867306611824451</v>
+        <v>0.18710664048886</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5808726180092039</v>
+        <v>0.5724541742699401</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1674603706790081</v>
+        <v>0.1691291030122588</v>
       </c>
       <c r="C71">
-        <v>-730.6101641977193</v>
+        <v>-795.0192956504607</v>
       </c>
       <c r="D71">
-        <v>2320.682835802281</v>
+        <v>2300.970704349539</v>
       </c>
       <c r="E71">
-        <v>180.0930000000003</v>
+        <v>224.79</v>
       </c>
       <c r="F71">
-        <v>3084.093</v>
+        <v>3128.79</v>
       </c>
       <c r="G71">
         <v>32.8</v>
@@ -7115,37 +7115,37 @@
         <v>375.475</v>
       </c>
       <c r="M71">
-        <v>655.9040301852096</v>
+        <v>665.4098856951401</v>
       </c>
       <c r="N71">
-        <v>-280.4290301852096</v>
+        <v>-289.9348856951401</v>
       </c>
       <c r="O71">
-        <v>-58.89009633889402</v>
+        <v>-60.88632599597942</v>
       </c>
       <c r="P71">
-        <v>-221.5389338463156</v>
+        <v>-229.0485596991607</v>
       </c>
       <c r="Q71">
-        <v>62.36106615368436</v>
+        <v>54.85144030083927</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.123731576586112</v>
+        <v>0.126329295805649</v>
       </c>
       <c r="T71">
-        <v>1.314038339428786</v>
+        <v>1.357839617409746</v>
       </c>
       <c r="U71">
         <v>0.2126732333250682</v>
       </c>
       <c r="V71">
-        <v>0.1202153765966874</v>
+        <v>0.1184980140738776</v>
       </c>
       <c r="W71">
-        <v>0.18710664048886</v>
+        <v>0.1874718775293772</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5724541742699401</v>
+        <v>0.5642762574946553</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1691291030122588</v>
+        <v>0.1707978353455095</v>
       </c>
       <c r="C72">
-        <v>-795.0192956504607</v>
+        <v>-859.0963736405643</v>
       </c>
       <c r="D72">
-        <v>2300.970704349539</v>
+        <v>2281.590626359436</v>
       </c>
       <c r="E72">
-        <v>224.79</v>
+        <v>269.4870000000001</v>
       </c>
       <c r="F72">
-        <v>3128.79</v>
+        <v>3173.487</v>
       </c>
       <c r="G72">
         <v>32.8</v>
@@ -7197,37 +7197,37 @@
         <v>375.475</v>
       </c>
       <c r="M72">
-        <v>665.4098856951401</v>
+        <v>674.9157412050707</v>
       </c>
       <c r="N72">
-        <v>-289.9348856951401</v>
+        <v>-299.4407412050707</v>
       </c>
       <c r="O72">
-        <v>-60.88632599597942</v>
+        <v>-62.88255565306485</v>
       </c>
       <c r="P72">
-        <v>-229.0485596991607</v>
+        <v>-236.5581855520059</v>
       </c>
       <c r="Q72">
-        <v>54.85144030083927</v>
+        <v>47.34181444799412</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.126329295805649</v>
+        <v>0.1291061680748093</v>
       </c>
       <c r="T72">
-        <v>1.357839617409746</v>
+        <v>1.404661673182496</v>
       </c>
       <c r="U72">
         <v>0.2126732333250682</v>
       </c>
       <c r="V72">
-        <v>0.1184980140738776</v>
+        <v>0.116829027960161</v>
       </c>
       <c r="W72">
-        <v>0.1874718775293772</v>
+        <v>0.187826826202556</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5642762574946553</v>
+        <v>0.5563287045721953</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1707978353455094</v>
+        <v>0.1724665676787601</v>
       </c>
       <c r="C73">
-        <v>-859.0963736405638</v>
+        <v>-922.8497183177883</v>
       </c>
       <c r="D73">
-        <v>2281.590626359436</v>
+        <v>2262.534281682211</v>
       </c>
       <c r="E73">
-        <v>269.4869999999996</v>
+        <v>314.1839999999997</v>
       </c>
       <c r="F73">
-        <v>3173.487</v>
+        <v>3218.184</v>
       </c>
       <c r="G73">
         <v>32.8</v>
@@ -7279,37 +7279,37 @@
         <v>375.475</v>
       </c>
       <c r="M73">
-        <v>674.9157412050706</v>
+        <v>684.4215967150012</v>
       </c>
       <c r="N73">
-        <v>-299.4407412050706</v>
+        <v>-308.9465967150012</v>
       </c>
       <c r="O73">
-        <v>-62.88255565306482</v>
+        <v>-64.87878531015025</v>
       </c>
       <c r="P73">
-        <v>-236.5581855520058</v>
+        <v>-244.0678114048509</v>
       </c>
       <c r="Q73">
-        <v>47.34181444799421</v>
+        <v>39.83218859514903</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1291061680748093</v>
+        <v>0.1320813883631954</v>
       </c>
       <c r="T73">
-        <v>1.404661673182495</v>
+        <v>1.454828161510442</v>
       </c>
       <c r="U73">
         <v>0.2126732333250682</v>
       </c>
       <c r="V73">
-        <v>0.116829027960161</v>
+        <v>0.1152064025718254</v>
       </c>
       <c r="W73">
-        <v>0.187826826202556</v>
+        <v>0.1881719151903686</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5563287045721954</v>
+        <v>0.5486019170086927</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1724665676787601</v>
+        <v>0.1741353000120108</v>
       </c>
       <c r="C74">
-        <v>-922.8497183177883</v>
+        <v>-986.2873741674548</v>
       </c>
       <c r="D74">
-        <v>2262.534281682211</v>
+        <v>2243.793625832545</v>
       </c>
       <c r="E74">
-        <v>314.1839999999997</v>
+        <v>358.8809999999999</v>
       </c>
       <c r="F74">
-        <v>3218.184</v>
+        <v>3262.881</v>
       </c>
       <c r="G74">
         <v>32.8</v>
@@ -7361,37 +7361,37 @@
         <v>375.475</v>
       </c>
       <c r="M74">
-        <v>684.4215967150012</v>
+        <v>693.9274522249318</v>
       </c>
       <c r="N74">
-        <v>-308.9465967150012</v>
+        <v>-318.4524522249318</v>
       </c>
       <c r="O74">
-        <v>-64.87878531015025</v>
+        <v>-66.87501496723567</v>
       </c>
       <c r="P74">
-        <v>-244.0678114048509</v>
+        <v>-251.5774372576961</v>
       </c>
       <c r="Q74">
-        <v>39.83218859514903</v>
+        <v>32.32256274230386</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1320813883631954</v>
+        <v>0.13527699533961</v>
       </c>
       <c r="T74">
-        <v>1.454828161510442</v>
+        <v>1.508710686010828</v>
       </c>
       <c r="U74">
         <v>0.2126732333250682</v>
       </c>
       <c r="V74">
-        <v>0.1152064025718254</v>
+        <v>0.1136282326735813</v>
       </c>
       <c r="W74">
-        <v>0.1881719151903686</v>
+        <v>0.1885075496853645</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5486019170086927</v>
+        <v>0.5410868222551489</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1741353000120108</v>
+        <v>0.1758040323452615</v>
       </c>
       <c r="C75">
-        <v>-986.2873741674548</v>
+        <v>-1049.417121333343</v>
       </c>
       <c r="D75">
-        <v>2243.793625832545</v>
+        <v>2225.360878666657</v>
       </c>
       <c r="E75">
-        <v>358.8809999999999</v>
+        <v>403.578</v>
       </c>
       <c r="F75">
-        <v>3262.881</v>
+        <v>3307.578</v>
       </c>
       <c r="G75">
         <v>32.8</v>
@@ -7443,37 +7443,37 @@
         <v>375.475</v>
       </c>
       <c r="M75">
-        <v>693.9274522249318</v>
+        <v>703.4333077348624</v>
       </c>
       <c r="N75">
-        <v>-318.4524522249318</v>
+        <v>-327.9583077348624</v>
       </c>
       <c r="O75">
-        <v>-66.87501496723567</v>
+        <v>-68.87124462432109</v>
       </c>
       <c r="P75">
-        <v>-251.5774372576961</v>
+        <v>-259.0870631105413</v>
       </c>
       <c r="Q75">
-        <v>32.32256274230386</v>
+        <v>24.81293688945868</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.13527699533961</v>
+        <v>0.1387184182372873</v>
       </c>
       <c r="T75">
-        <v>1.508710686010828</v>
+        <v>1.566738020088168</v>
       </c>
       <c r="U75">
         <v>0.2126732333250682</v>
       </c>
       <c r="V75">
-        <v>0.1136282326735813</v>
+        <v>0.1120927160158302</v>
       </c>
       <c r="W75">
-        <v>0.1885075496853645</v>
+        <v>0.188834112977793</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5410868222551489</v>
+        <v>0.5337748381706199</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1758040323452615</v>
+        <v>0.1774727646785122</v>
       </c>
       <c r="C76">
-        <v>-1049.417121333343</v>
+        <v>-1112.246486387045</v>
       </c>
       <c r="D76">
-        <v>2225.360878666657</v>
+        <v>2207.228513612954</v>
       </c>
       <c r="E76">
-        <v>403.578</v>
+        <v>448.2749999999996</v>
       </c>
       <c r="F76">
-        <v>3307.578</v>
+        <v>3352.275</v>
       </c>
       <c r="G76">
         <v>32.8</v>
@@ -7525,37 +7525,37 @@
         <v>375.475</v>
       </c>
       <c r="M76">
-        <v>703.4333077348624</v>
+        <v>712.939163244793</v>
       </c>
       <c r="N76">
-        <v>-327.9583077348624</v>
+        <v>-337.464163244793</v>
       </c>
       <c r="O76">
-        <v>-68.87124462432109</v>
+        <v>-70.86747428140653</v>
       </c>
       <c r="P76">
-        <v>-259.0870631105413</v>
+        <v>-266.5966889633864</v>
       </c>
       <c r="Q76">
-        <v>24.81293688945868</v>
+        <v>17.30331103661354</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1387184182372873</v>
+        <v>0.1424351549667788</v>
       </c>
       <c r="T76">
-        <v>1.566738020088168</v>
+        <v>1.629407540891695</v>
       </c>
       <c r="U76">
         <v>0.2126732333250682</v>
       </c>
       <c r="V76">
-        <v>0.1120927160158302</v>
+        <v>0.1105981464689524</v>
       </c>
       <c r="W76">
-        <v>0.188834112977793</v>
+        <v>0.1891519679157566</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5337748381706199</v>
+        <v>0.5266578403283448</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1774727646785122</v>
+        <v>0.1791414970117629</v>
       </c>
       <c r="C77">
-        <v>-1112.246486387045</v>
+        <v>-1174.782752575074</v>
       </c>
       <c r="D77">
-        <v>2207.228513612954</v>
+        <v>2189.389247424926</v>
       </c>
       <c r="E77">
-        <v>448.2749999999996</v>
+        <v>492.9719999999998</v>
       </c>
       <c r="F77">
-        <v>3352.275</v>
+        <v>3396.972</v>
       </c>
       <c r="G77">
         <v>32.8</v>
@@ -7607,37 +7607,37 @@
         <v>375.475</v>
       </c>
       <c r="M77">
-        <v>712.939163244793</v>
+        <v>722.4450187547236</v>
       </c>
       <c r="N77">
-        <v>-337.464163244793</v>
+        <v>-346.9700187547236</v>
       </c>
       <c r="O77">
-        <v>-70.86747428140653</v>
+        <v>-72.86370393849195</v>
       </c>
       <c r="P77">
-        <v>-266.5966889633864</v>
+        <v>-274.1063148162316</v>
       </c>
       <c r="Q77">
-        <v>17.30331103661354</v>
+        <v>9.793685183768332</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1424351549667788</v>
+        <v>0.1464616197570613</v>
       </c>
       <c r="T77">
-        <v>1.629407540891695</v>
+        <v>1.697299521762182</v>
       </c>
       <c r="U77">
         <v>0.2126732333250682</v>
       </c>
       <c r="V77">
-        <v>0.1105981464689524</v>
+        <v>0.1091429076996241</v>
       </c>
       <c r="W77">
-        <v>0.1891519679157566</v>
+        <v>0.1894614582500897</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5266578403283448</v>
+        <v>0.519728131902972</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1791414970117629</v>
+        <v>0.1808102293450135</v>
       </c>
       <c r="C78">
-        <v>-1174.782752575074</v>
+        <v>-1237.032969573036</v>
       </c>
       <c r="D78">
-        <v>2189.389247424926</v>
+        <v>2171.836030426964</v>
       </c>
       <c r="E78">
-        <v>492.9719999999998</v>
+        <v>537.6689999999999</v>
       </c>
       <c r="F78">
-        <v>3396.972</v>
+        <v>3441.669</v>
       </c>
       <c r="G78">
         <v>32.8</v>
@@ -7689,37 +7689,37 @@
         <v>375.475</v>
       </c>
       <c r="M78">
-        <v>722.4450187547236</v>
+        <v>731.9508742646542</v>
       </c>
       <c r="N78">
-        <v>-346.9700187547236</v>
+        <v>-356.4758742646542</v>
       </c>
       <c r="O78">
-        <v>-72.86370393849195</v>
+        <v>-74.85993359557737</v>
       </c>
       <c r="P78">
-        <v>-274.1063148162316</v>
+        <v>-281.6159406690768</v>
       </c>
       <c r="Q78">
-        <v>9.793685183768332</v>
+        <v>2.284059330923185</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1464616197570613</v>
+        <v>0.1508382119204118</v>
       </c>
       <c r="T78">
-        <v>1.697299521762182</v>
+        <v>1.771095153143147</v>
       </c>
       <c r="U78">
         <v>0.2126732333250682</v>
       </c>
       <c r="V78">
-        <v>0.1091429076996241</v>
+        <v>0.1077254673398887</v>
       </c>
       <c r="W78">
-        <v>0.1894614582500897</v>
+        <v>0.18976290987444</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.519728131902972</v>
+        <v>0.5129784159042321</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1808102293450135</v>
+        <v>0.1824789616782642</v>
       </c>
       <c r="C79">
-        <v>-1237.032969573036</v>
+        <v>-1299.003962774325</v>
       </c>
       <c r="D79">
-        <v>2171.836030426964</v>
+        <v>2154.562037225675</v>
       </c>
       <c r="E79">
-        <v>537.6689999999999</v>
+        <v>582.366</v>
       </c>
       <c r="F79">
-        <v>3441.669</v>
+        <v>3486.366</v>
       </c>
       <c r="G79">
         <v>32.8</v>
@@ -7771,37 +7771,37 @@
         <v>375.475</v>
       </c>
       <c r="M79">
-        <v>731.9508742646542</v>
+        <v>741.4567297745848</v>
       </c>
       <c r="N79">
-        <v>-356.4758742646542</v>
+        <v>-365.9817297745848</v>
       </c>
       <c r="O79">
-        <v>-74.85993359557737</v>
+        <v>-76.8561632526628</v>
       </c>
       <c r="P79">
-        <v>-281.6159406690768</v>
+        <v>-289.125566521922</v>
       </c>
       <c r="Q79">
-        <v>2.284059330923185</v>
+        <v>-5.225566521922019</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1508382119204118</v>
+        <v>0.1556126760986123</v>
       </c>
       <c r="T79">
-        <v>1.771095153143147</v>
+        <v>1.851599478286017</v>
       </c>
       <c r="U79">
         <v>0.2126732333250682</v>
       </c>
       <c r="V79">
-        <v>0.1077254673398887</v>
+        <v>0.1063443716047619</v>
       </c>
       <c r="W79">
-        <v>0.18976290987444</v>
+        <v>0.1900566319699609</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5129784159042321</v>
+        <v>0.5064017695464854</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1824789616782642</v>
+        <v>0.2121064956280281</v>
       </c>
       <c r="C80">
-        <v>-1299.003962774325</v>
+        <v>-1610.305075893431</v>
       </c>
       <c r="D80">
-        <v>2154.562037225675</v>
+        <v>1887.957924106569</v>
       </c>
       <c r="E80">
-        <v>582.366</v>
+        <v>627.0630000000001</v>
       </c>
       <c r="F80">
-        <v>3486.366</v>
+        <v>3531.063</v>
       </c>
       <c r="G80">
         <v>32.8</v>
@@ -7853,45 +7853,45 @@
         <v>375.475</v>
       </c>
       <c r="M80">
-        <v>741.4567297745848</v>
+        <v>874.5497902845153</v>
       </c>
       <c r="N80">
-        <v>-365.9817297745848</v>
+        <v>-499.0747902845153</v>
       </c>
       <c r="O80">
-        <v>-76.8561632526628</v>
+        <v>-104.8057059597482</v>
       </c>
       <c r="P80">
-        <v>-289.125566521922</v>
+        <v>-394.2690843247671</v>
       </c>
       <c r="Q80">
-        <v>-5.225566521922019</v>
+        <v>-110.3690843247671</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1556126760986123</v>
+        <v>0.1623123350390853</v>
       </c>
       <c r="T80">
-        <v>1.851599478286017</v>
+        <v>1.964565352897198</v>
       </c>
       <c r="U80">
-        <v>0.2126732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V80">
-        <v>0.1063443716047619</v>
+        <v>0.09016038980965051</v>
       </c>
       <c r="W80">
-        <v>0.1900566319699609</v>
+        <v>0.2253429180630636</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.5064017695464854</v>
+        <v>0.4293351895697644</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2121064956280281</v>
+        <v>0.2141252279612788</v>
       </c>
       <c r="C81">
-        <v>-1610.305075893431</v>
+        <v>-1670.786803786481</v>
       </c>
       <c r="D81">
-        <v>1887.957924106569</v>
+        <v>1872.17319621352</v>
       </c>
       <c r="E81">
-        <v>627.0630000000001</v>
+        <v>671.7600000000002</v>
       </c>
       <c r="F81">
-        <v>3531.063</v>
+        <v>3575.76</v>
       </c>
       <c r="G81">
         <v>32.8</v>
@@ -7935,37 +7935,37 @@
         <v>375.475</v>
       </c>
       <c r="M81">
-        <v>874.5497902845153</v>
+        <v>885.620040794446</v>
       </c>
       <c r="N81">
-        <v>-499.0747902845153</v>
+        <v>-510.145040794446</v>
       </c>
       <c r="O81">
-        <v>-104.8057059597482</v>
+        <v>-107.1304585668337</v>
       </c>
       <c r="P81">
-        <v>-394.2690843247671</v>
+        <v>-403.0145822276123</v>
       </c>
       <c r="Q81">
-        <v>-110.3690843247671</v>
+        <v>-119.1145822276123</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1623123350390853</v>
+        <v>0.1681379517910396</v>
       </c>
       <c r="T81">
-        <v>1.964565352897198</v>
+        <v>2.062793620542058</v>
       </c>
       <c r="U81">
         <v>0.2476732333250682</v>
       </c>
       <c r="V81">
-        <v>0.09016038980965051</v>
+        <v>0.08903338493702986</v>
       </c>
       <c r="W81">
-        <v>0.2253429180630636</v>
+        <v>0.2256220470038386</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4293351895697644</v>
+        <v>0.4239684997001422</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2141252279612788</v>
+        <v>0.2161439602945295</v>
       </c>
       <c r="C82">
-        <v>-1670.786803786481</v>
+        <v>-1731.006776095711</v>
       </c>
       <c r="D82">
-        <v>1872.17319621352</v>
+        <v>1856.650223904289</v>
       </c>
       <c r="E82">
-        <v>671.7600000000002</v>
+        <v>716.4569999999999</v>
       </c>
       <c r="F82">
-        <v>3575.76</v>
+        <v>3620.457</v>
       </c>
       <c r="G82">
         <v>32.8</v>
@@ -8017,37 +8017,37 @@
         <v>375.475</v>
       </c>
       <c r="M82">
-        <v>885.620040794446</v>
+        <v>896.6902913043765</v>
       </c>
       <c r="N82">
-        <v>-510.145040794446</v>
+        <v>-521.2152913043765</v>
       </c>
       <c r="O82">
-        <v>-107.1304585668337</v>
+        <v>-109.4552111739191</v>
       </c>
       <c r="P82">
-        <v>-403.0145822276123</v>
+        <v>-411.7600801304574</v>
       </c>
       <c r="Q82">
-        <v>-119.1145822276123</v>
+        <v>-127.8600801304574</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1681379517910396</v>
+        <v>0.174576791358989</v>
       </c>
       <c r="T82">
-        <v>2.062793620542058</v>
+        <v>2.171361705833745</v>
       </c>
       <c r="U82">
         <v>0.2476732333250682</v>
       </c>
       <c r="V82">
-        <v>0.08903338493702986</v>
+        <v>0.08793420734521469</v>
       </c>
       <c r="W82">
-        <v>0.2256220470038386</v>
+        <v>0.2258942838720019</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4239684997001422</v>
+        <v>0.4187343206914985</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2161439602945295</v>
+        <v>0.2181626926277802</v>
       </c>
       <c r="C83">
-        <v>-1731.006776095711</v>
+        <v>-1790.97145025545</v>
       </c>
       <c r="D83">
-        <v>1856.650223904289</v>
+        <v>1841.38254974455</v>
       </c>
       <c r="E83">
-        <v>716.4569999999999</v>
+        <v>761.154</v>
       </c>
       <c r="F83">
-        <v>3620.457</v>
+        <v>3665.154</v>
       </c>
       <c r="G83">
         <v>32.8</v>
@@ -8099,37 +8099,37 @@
         <v>375.475</v>
       </c>
       <c r="M83">
-        <v>896.6902913043765</v>
+        <v>907.7605418143071</v>
       </c>
       <c r="N83">
-        <v>-521.2152913043765</v>
+        <v>-532.2855418143071</v>
       </c>
       <c r="O83">
-        <v>-109.4552111739191</v>
+        <v>-111.7799637810045</v>
       </c>
       <c r="P83">
-        <v>-411.7600801304574</v>
+        <v>-420.5055780333026</v>
       </c>
       <c r="Q83">
-        <v>-127.8600801304574</v>
+        <v>-136.6055780333026</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.174576791358989</v>
+        <v>0.1817310575455995</v>
       </c>
       <c r="T83">
-        <v>2.171361705833745</v>
+        <v>2.291992911713398</v>
       </c>
       <c r="U83">
         <v>0.2476732333250682</v>
       </c>
       <c r="V83">
-        <v>0.08793420734521469</v>
+        <v>0.08686183896295598</v>
       </c>
       <c r="W83">
-        <v>0.2258942838720019</v>
+        <v>0.2261598808165515</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4187343206914985</v>
+        <v>0.4136278045855046</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2181626926277802</v>
+        <v>0.2201814249610309</v>
       </c>
       <c r="C84">
-        <v>-1790.97145025545</v>
+        <v>-1850.687073028387</v>
       </c>
       <c r="D84">
-        <v>1841.38254974455</v>
+        <v>1826.363926971614</v>
       </c>
       <c r="E84">
-        <v>761.154</v>
+        <v>805.8510000000001</v>
       </c>
       <c r="F84">
-        <v>3665.154</v>
+        <v>3709.851</v>
       </c>
       <c r="G84">
         <v>32.8</v>
@@ -8181,37 +8181,37 @@
         <v>375.475</v>
       </c>
       <c r="M84">
-        <v>907.7605418143071</v>
+        <v>918.8307923242377</v>
       </c>
       <c r="N84">
-        <v>-532.2855418143071</v>
+        <v>-543.3557923242377</v>
       </c>
       <c r="O84">
-        <v>-111.7799637810045</v>
+        <v>-114.1047163880899</v>
       </c>
       <c r="P84">
-        <v>-420.5055780333026</v>
+        <v>-429.2510759361477</v>
       </c>
       <c r="Q84">
-        <v>-136.6055780333026</v>
+        <v>-145.3510759361478</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1817310575455995</v>
+        <v>0.1897270021071054</v>
       </c>
       <c r="T84">
-        <v>2.291992911713398</v>
+        <v>2.426816024167127</v>
       </c>
       <c r="U84">
         <v>0.2476732333250682</v>
       </c>
       <c r="V84">
-        <v>0.08686183896295598</v>
+        <v>0.08581531078267939</v>
       </c>
       <c r="W84">
-        <v>0.2261598808165515</v>
+        <v>0.2264190778347264</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4136278045855046</v>
+        <v>0.4086443370603781</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2201814249610309</v>
+        <v>0.2222001572942815</v>
       </c>
       <c r="C85">
-        <v>-1850.687073028387</v>
+        <v>-1910.159689027425</v>
       </c>
       <c r="D85">
-        <v>1826.363926971614</v>
+        <v>1811.588310972576</v>
       </c>
       <c r="E85">
-        <v>805.8510000000001</v>
+        <v>850.5480000000002</v>
       </c>
       <c r="F85">
-        <v>3709.851</v>
+        <v>3754.548</v>
       </c>
       <c r="G85">
         <v>32.8</v>
@@ -8263,37 +8263,37 @@
         <v>375.475</v>
       </c>
       <c r="M85">
-        <v>918.8307923242377</v>
+        <v>929.9010428341683</v>
       </c>
       <c r="N85">
-        <v>-543.3557923242377</v>
+        <v>-554.4260428341682</v>
       </c>
       <c r="O85">
-        <v>-114.1047163880899</v>
+        <v>-116.4294689951753</v>
       </c>
       <c r="P85">
-        <v>-429.2510759361477</v>
+        <v>-437.9965738389929</v>
       </c>
       <c r="Q85">
-        <v>-145.3510759361478</v>
+        <v>-154.0965738389929</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1897270021071054</v>
+        <v>0.1987224397387995</v>
       </c>
       <c r="T85">
-        <v>2.426816024167127</v>
+        <v>2.578492025677573</v>
       </c>
       <c r="U85">
         <v>0.2476732333250682</v>
       </c>
       <c r="V85">
-        <v>0.08581531078267939</v>
+        <v>0.08479369994002844</v>
       </c>
       <c r="W85">
-        <v>0.2264190778347264</v>
+        <v>0.2266721034953257</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4086443370603781</v>
+        <v>0.403779523523945</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2222001572942815</v>
+        <v>0.2242188896275322</v>
       </c>
       <c r="C86">
-        <v>-1910.159689027424</v>
+        <v>-1969.395148827212</v>
       </c>
       <c r="D86">
-        <v>1811.588310972576</v>
+        <v>1797.049851172788</v>
       </c>
       <c r="E86">
-        <v>850.5479999999998</v>
+        <v>895.2449999999999</v>
       </c>
       <c r="F86">
-        <v>3754.548</v>
+        <v>3799.245</v>
       </c>
       <c r="G86">
         <v>32.8</v>
@@ -8345,37 +8345,37 @@
         <v>375.475</v>
       </c>
       <c r="M86">
-        <v>929.9010428341682</v>
+        <v>940.9712933440987</v>
       </c>
       <c r="N86">
-        <v>-554.4260428341681</v>
+        <v>-565.4962933440987</v>
       </c>
       <c r="O86">
-        <v>-116.4294689951753</v>
+        <v>-118.7542216022607</v>
       </c>
       <c r="P86">
-        <v>-437.9965738389928</v>
+        <v>-446.742071741838</v>
       </c>
       <c r="Q86">
-        <v>-154.0965738389929</v>
+        <v>-162.842071741838</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1987224397387994</v>
+        <v>0.2089172690547194</v>
       </c>
       <c r="T86">
-        <v>2.578492025677571</v>
+        <v>2.750391494056076</v>
       </c>
       <c r="U86">
         <v>0.2476732333250682</v>
       </c>
       <c r="V86">
-        <v>0.08479369994002846</v>
+        <v>0.08379612699955753</v>
       </c>
       <c r="W86">
-        <v>0.2266721034953257</v>
+        <v>0.2269191756109697</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4037795235239451</v>
+        <v>0.3990291761883692</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2242188896275322</v>
+        <v>0.2262376219607829</v>
       </c>
       <c r="C87">
-        <v>-1969.395148827212</v>
+        <v>-2028.399116688178</v>
       </c>
       <c r="D87">
-        <v>1797.049851172788</v>
+        <v>1782.742883311822</v>
       </c>
       <c r="E87">
-        <v>895.2449999999999</v>
+        <v>939.942</v>
       </c>
       <c r="F87">
-        <v>3799.245</v>
+        <v>3843.942</v>
       </c>
       <c r="G87">
         <v>32.8</v>
@@ -8427,37 +8427,37 @@
         <v>375.475</v>
       </c>
       <c r="M87">
-        <v>940.9712933440987</v>
+        <v>952.0415438540293</v>
       </c>
       <c r="N87">
-        <v>-565.4962933440987</v>
+        <v>-576.5665438540293</v>
       </c>
       <c r="O87">
-        <v>-118.7542216022607</v>
+        <v>-121.0789742093461</v>
       </c>
       <c r="P87">
-        <v>-446.742071741838</v>
+        <v>-455.4875696446832</v>
       </c>
       <c r="Q87">
-        <v>-162.842071741838</v>
+        <v>-171.5875696446832</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2089172690547194</v>
+        <v>0.2205685025586279</v>
       </c>
       <c r="T87">
-        <v>2.750391494056076</v>
+        <v>2.946848029345796</v>
       </c>
       <c r="U87">
         <v>0.2476732333250682</v>
       </c>
       <c r="V87">
-        <v>0.08379612699955753</v>
+        <v>0.08282175342979523</v>
       </c>
       <c r="W87">
-        <v>0.2269191756109697</v>
+        <v>0.2271605018634593</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3990291761883692</v>
+        <v>0.394389302046644</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2262376219607829</v>
+        <v>0.2282563542940336</v>
       </c>
       <c r="C88">
-        <v>-2028.399116688178</v>
+        <v>-2087.177077914532</v>
       </c>
       <c r="D88">
-        <v>1782.742883311822</v>
+        <v>1768.661922085467</v>
       </c>
       <c r="E88">
-        <v>939.942</v>
+        <v>984.6389999999997</v>
       </c>
       <c r="F88">
-        <v>3843.942</v>
+        <v>3888.639</v>
       </c>
       <c r="G88">
         <v>32.8</v>
@@ -8509,37 +8509,37 @@
         <v>375.475</v>
       </c>
       <c r="M88">
-        <v>952.0415438540293</v>
+        <v>963.1117943639598</v>
       </c>
       <c r="N88">
-        <v>-576.5665438540293</v>
+        <v>-587.6367943639598</v>
       </c>
       <c r="O88">
-        <v>-121.0789742093461</v>
+        <v>-123.4037268164315</v>
       </c>
       <c r="P88">
-        <v>-455.4875696446832</v>
+        <v>-464.2330675475282</v>
       </c>
       <c r="Q88">
-        <v>-171.5875696446832</v>
+        <v>-180.3330675475282</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2205685025586279</v>
+        <v>0.2340122335246762</v>
       </c>
       <c r="T88">
-        <v>2.946848029345796</v>
+        <v>3.17352864698778</v>
       </c>
       <c r="U88">
         <v>0.2476732333250682</v>
       </c>
       <c r="V88">
-        <v>0.08282175342979523</v>
+        <v>0.08186977925244127</v>
       </c>
       <c r="W88">
-        <v>0.2271605018634593</v>
+        <v>0.2273962803860065</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.394389302046644</v>
+        <v>0.3898560916782918</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2282563542940336</v>
+        <v>0.2302750866272843</v>
       </c>
       <c r="C89">
-        <v>-2087.177077914532</v>
+        <v>-2145.734345866295</v>
       </c>
       <c r="D89">
-        <v>1768.661922085467</v>
+        <v>1754.801654133704</v>
       </c>
       <c r="E89">
-        <v>984.6389999999997</v>
+        <v>1029.336</v>
       </c>
       <c r="F89">
-        <v>3888.639</v>
+        <v>3933.336</v>
       </c>
       <c r="G89">
         <v>32.8</v>
@@ -8591,37 +8591,37 @@
         <v>375.475</v>
       </c>
       <c r="M89">
-        <v>963.1117943639598</v>
+        <v>974.1820448738905</v>
       </c>
       <c r="N89">
-        <v>-587.6367943639598</v>
+        <v>-598.7070448738905</v>
       </c>
       <c r="O89">
-        <v>-123.4037268164315</v>
+        <v>-125.728479423517</v>
       </c>
       <c r="P89">
-        <v>-464.2330675475282</v>
+        <v>-472.9785654503735</v>
       </c>
       <c r="Q89">
-        <v>-180.3330675475282</v>
+        <v>-189.0785654503735</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2340122335246762</v>
+        <v>0.2496965863183993</v>
       </c>
       <c r="T89">
-        <v>3.17352864698778</v>
+        <v>3.437989367570096</v>
       </c>
       <c r="U89">
         <v>0.2476732333250682</v>
       </c>
       <c r="V89">
-        <v>0.08186977925244127</v>
+        <v>0.08093944085184533</v>
       </c>
       <c r="W89">
-        <v>0.2273962803860065</v>
+        <v>0.2276267003057686</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3898560916782918</v>
+        <v>0.3854259088183112</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2302750866272843</v>
+        <v>0.2322938189605349</v>
       </c>
       <c r="C90">
-        <v>-2145.734345866295</v>
+        <v>-2204.076068644182</v>
       </c>
       <c r="D90">
-        <v>1754.801654133704</v>
+        <v>1741.156931355818</v>
       </c>
       <c r="E90">
-        <v>1029.336</v>
+        <v>1074.033</v>
       </c>
       <c r="F90">
-        <v>3933.336</v>
+        <v>3978.033</v>
       </c>
       <c r="G90">
         <v>32.8</v>
@@ -8673,37 +8673,37 @@
         <v>375.475</v>
       </c>
       <c r="M90">
-        <v>974.1820448738905</v>
+        <v>985.2522953838211</v>
       </c>
       <c r="N90">
-        <v>-598.7070448738905</v>
+        <v>-609.7772953838211</v>
       </c>
       <c r="O90">
-        <v>-125.728479423517</v>
+        <v>-128.0532320306024</v>
       </c>
       <c r="P90">
-        <v>-472.9785654503735</v>
+        <v>-481.7240633532186</v>
       </c>
       <c r="Q90">
-        <v>-189.0785654503735</v>
+        <v>-197.8240633532187</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2496965863183993</v>
+        <v>0.2682326396200719</v>
       </c>
       <c r="T90">
-        <v>3.437989367570096</v>
+        <v>3.750533855531014</v>
       </c>
       <c r="U90">
         <v>0.2476732333250682</v>
       </c>
       <c r="V90">
-        <v>0.08093944085184533</v>
+        <v>0.08003000893216168</v>
       </c>
       <c r="W90">
-        <v>0.2276267003057686</v>
+        <v>0.2278519422498056</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3854259088183112</v>
+        <v>0.3810952806293414</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2322938189605349</v>
+        <v>0.2343125512937856</v>
       </c>
       <c r="C91">
-        <v>-2204.076068644182</v>
+        <v>-2262.207235465026</v>
       </c>
       <c r="D91">
-        <v>1741.156931355818</v>
+        <v>1727.722764534974</v>
       </c>
       <c r="E91">
-        <v>1074.033</v>
+        <v>1118.73</v>
       </c>
       <c r="F91">
-        <v>3978.033</v>
+        <v>4022.73</v>
       </c>
       <c r="G91">
         <v>32.8</v>
@@ -8755,37 +8755,37 @@
         <v>375.475</v>
       </c>
       <c r="M91">
-        <v>985.2522953838211</v>
+        <v>996.3225458937517</v>
       </c>
       <c r="N91">
-        <v>-609.7772953838211</v>
+        <v>-620.8475458937517</v>
       </c>
       <c r="O91">
-        <v>-128.0532320306024</v>
+        <v>-130.3779846376878</v>
       </c>
       <c r="P91">
-        <v>-481.7240633532186</v>
+        <v>-490.4695612560638</v>
       </c>
       <c r="Q91">
-        <v>-197.8240633532187</v>
+        <v>-206.5695612560638</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2682326396200719</v>
+        <v>0.2904759035820791</v>
       </c>
       <c r="T91">
-        <v>3.750533855531014</v>
+        <v>4.125587241084116</v>
       </c>
       <c r="U91">
         <v>0.2476732333250682</v>
       </c>
       <c r="V91">
-        <v>0.08003000893216168</v>
+        <v>0.07914078661069322</v>
       </c>
       <c r="W91">
-        <v>0.2278519422498056</v>
+        <v>0.2280721788173085</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3810952806293414</v>
+        <v>0.3768608886223487</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2343125512937856</v>
+        <v>0.2363312836270363</v>
       </c>
       <c r="C92">
-        <v>-2262.207235465026</v>
+        <v>-2320.13268274431</v>
       </c>
       <c r="D92">
-        <v>1727.722764534974</v>
+        <v>1714.49431725569</v>
       </c>
       <c r="E92">
-        <v>1118.73</v>
+        <v>1163.427</v>
       </c>
       <c r="F92">
-        <v>4022.73</v>
+        <v>4067.427</v>
       </c>
       <c r="G92">
         <v>32.8</v>
@@ -8837,37 +8837,37 @@
         <v>375.475</v>
       </c>
       <c r="M92">
-        <v>996.3225458937517</v>
+        <v>1007.392796403682</v>
       </c>
       <c r="N92">
-        <v>-620.8475458937517</v>
+        <v>-631.9177964036822</v>
       </c>
       <c r="O92">
-        <v>-130.3779846376878</v>
+        <v>-132.7027372447733</v>
       </c>
       <c r="P92">
-        <v>-490.4695612560638</v>
+        <v>-499.215059158909</v>
       </c>
       <c r="Q92">
-        <v>-206.5695612560638</v>
+        <v>-215.315059158909</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2904759035820791</v>
+        <v>0.3176621150911991</v>
       </c>
       <c r="T92">
-        <v>4.125587241084116</v>
+        <v>4.583985823426795</v>
       </c>
       <c r="U92">
         <v>0.2476732333250682</v>
       </c>
       <c r="V92">
-        <v>0.07914078661069322</v>
+        <v>0.07827110763694933</v>
       </c>
       <c r="W92">
-        <v>0.2280721788173085</v>
+        <v>0.2282875750206905</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3768608886223487</v>
+        <v>0.3727195601759492</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2363312836270363</v>
+        <v>0.238350015960287</v>
       </c>
       <c r="C93">
-        <v>-2320.13268274431</v>
+        <v>-2377.857099901402</v>
       </c>
       <c r="D93">
-        <v>1714.49431725569</v>
+        <v>1701.466900098598</v>
       </c>
       <c r="E93">
-        <v>1163.427</v>
+        <v>1208.124</v>
       </c>
       <c r="F93">
-        <v>4067.427</v>
+        <v>4112.124</v>
       </c>
       <c r="G93">
         <v>32.8</v>
@@ -8919,37 +8919,37 @@
         <v>375.475</v>
       </c>
       <c r="M93">
-        <v>1007.392796403682</v>
+        <v>1018.463046913613</v>
       </c>
       <c r="N93">
-        <v>-631.9177964036822</v>
+        <v>-642.9880469136127</v>
       </c>
       <c r="O93">
-        <v>-132.7027372447733</v>
+        <v>-135.0274898518587</v>
       </c>
       <c r="P93">
-        <v>-499.215059158909</v>
+        <v>-507.9605570617541</v>
       </c>
       <c r="Q93">
-        <v>-215.315059158909</v>
+        <v>-224.0605570617541</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3176621150911991</v>
+        <v>0.351644879477599</v>
       </c>
       <c r="T93">
-        <v>4.583985823426795</v>
+        <v>5.156984051355146</v>
       </c>
       <c r="U93">
         <v>0.2476732333250682</v>
       </c>
       <c r="V93">
-        <v>0.07827110763694933</v>
+        <v>0.07742033472785208</v>
       </c>
       <c r="W93">
-        <v>0.2282875750206905</v>
+        <v>0.228498288697912</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3727195601759492</v>
+        <v>0.3686682606088194</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.238350015960287</v>
+        <v>0.2403687482935377</v>
       </c>
       <c r="C94">
-        <v>-2377.857099901402</v>
+        <v>-2435.385034902115</v>
       </c>
       <c r="D94">
-        <v>1701.466900098598</v>
+        <v>1688.635965097885</v>
       </c>
       <c r="E94">
-        <v>1208.124</v>
+        <v>1252.821</v>
       </c>
       <c r="F94">
-        <v>4112.124</v>
+        <v>4156.821</v>
       </c>
       <c r="G94">
         <v>32.8</v>
@@ -9001,37 +9001,37 @@
         <v>375.475</v>
       </c>
       <c r="M94">
-        <v>1018.463046913613</v>
+        <v>1029.533297423543</v>
       </c>
       <c r="N94">
-        <v>-642.9880469136127</v>
+        <v>-654.0582974235434</v>
       </c>
       <c r="O94">
-        <v>-135.0274898518587</v>
+        <v>-137.3522424589441</v>
       </c>
       <c r="P94">
-        <v>-507.9605570617541</v>
+        <v>-516.7060549645993</v>
       </c>
       <c r="Q94">
-        <v>-224.0605570617541</v>
+        <v>-232.8060549645993</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.351644879477599</v>
+        <v>0.3953370051172561</v>
       </c>
       <c r="T94">
-        <v>5.156984051355146</v>
+        <v>5.893696058691597</v>
       </c>
       <c r="U94">
         <v>0.2476732333250682</v>
       </c>
       <c r="V94">
-        <v>0.07742033472785208</v>
+        <v>0.07658785801034827</v>
       </c>
       <c r="W94">
-        <v>0.228498288697912</v>
+        <v>0.228704470898204</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3686682606088194</v>
+        <v>0.3647040857635632</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2403687482935377</v>
+        <v>0.2423874806267883</v>
       </c>
       <c r="C95">
-        <v>-2435.385034902115</v>
+        <v>-2492.720899552365</v>
       </c>
       <c r="D95">
-        <v>1688.635965097885</v>
+        <v>1675.997100447635</v>
       </c>
       <c r="E95">
-        <v>1252.821</v>
+        <v>1297.518</v>
       </c>
       <c r="F95">
-        <v>4156.821</v>
+        <v>4201.518</v>
       </c>
       <c r="G95">
         <v>32.8</v>
@@ -9083,37 +9083,37 @@
         <v>375.475</v>
       </c>
       <c r="M95">
-        <v>1029.533297423543</v>
+        <v>1040.603547933474</v>
       </c>
       <c r="N95">
-        <v>-654.0582974235434</v>
+        <v>-665.1285479334739</v>
       </c>
       <c r="O95">
-        <v>-137.3522424589441</v>
+        <v>-139.6769950660295</v>
       </c>
       <c r="P95">
-        <v>-516.7060549645993</v>
+        <v>-525.4515528674444</v>
       </c>
       <c r="Q95">
-        <v>-232.8060549645993</v>
+        <v>-241.5515528674445</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3953370051172561</v>
+        <v>0.4535931726367989</v>
       </c>
       <c r="T95">
-        <v>5.893696058691597</v>
+        <v>6.875978735140198</v>
       </c>
       <c r="U95">
         <v>0.2476732333250682</v>
       </c>
       <c r="V95">
-        <v>0.07658785801034827</v>
+        <v>0.07577309356342968</v>
       </c>
       <c r="W95">
-        <v>0.228704470898204</v>
+        <v>0.2289062662431707</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3647040857635632</v>
+        <v>0.3608242550639509</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2423874806267883</v>
+        <v>0.244406212960039</v>
       </c>
       <c r="C96">
-        <v>-2492.720899552365</v>
+        <v>-2549.86897455587</v>
       </c>
       <c r="D96">
-        <v>1675.997100447635</v>
+        <v>1663.54602544413</v>
       </c>
       <c r="E96">
-        <v>1297.518</v>
+        <v>1342.215</v>
       </c>
       <c r="F96">
-        <v>4201.518</v>
+        <v>4246.215</v>
       </c>
       <c r="G96">
         <v>32.8</v>
@@ -9165,37 +9165,37 @@
         <v>375.475</v>
       </c>
       <c r="M96">
-        <v>1040.603547933474</v>
+        <v>1051.673798443405</v>
       </c>
       <c r="N96">
-        <v>-665.1285479334739</v>
+        <v>-676.1987984434046</v>
       </c>
       <c r="O96">
-        <v>-139.6769950660295</v>
+        <v>-142.0017476731149</v>
       </c>
       <c r="P96">
-        <v>-525.4515528674444</v>
+        <v>-534.1970507702897</v>
       </c>
       <c r="Q96">
-        <v>-241.5515528674445</v>
+        <v>-250.2970507702897</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4535931726367989</v>
+        <v>0.5351518071641589</v>
       </c>
       <c r="T96">
-        <v>6.875978735140198</v>
+        <v>8.251174482168242</v>
       </c>
       <c r="U96">
         <v>0.2476732333250682</v>
       </c>
       <c r="V96">
-        <v>0.07577309356342968</v>
+        <v>0.07497548205223567</v>
       </c>
       <c r="W96">
-        <v>0.2289062662431707</v>
+        <v>0.2291038132650854</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3608242550639509</v>
+        <v>0.3570261050106461</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.244406212960039</v>
+        <v>0.2464249452932897</v>
       </c>
       <c r="C97">
-        <v>-2549.86897455587</v>
+        <v>-2606.833414348065</v>
       </c>
       <c r="D97">
-        <v>1663.54602544413</v>
+        <v>1651.278585651936</v>
       </c>
       <c r="E97">
-        <v>1342.215</v>
+        <v>1386.912</v>
       </c>
       <c r="F97">
-        <v>4246.215</v>
+        <v>4290.912</v>
       </c>
       <c r="G97">
         <v>32.8</v>
@@ -9247,37 +9247,37 @@
         <v>375.475</v>
       </c>
       <c r="M97">
-        <v>1051.673798443405</v>
+        <v>1062.744048953335</v>
       </c>
       <c r="N97">
-        <v>-676.1987984434046</v>
+        <v>-687.2690489533351</v>
       </c>
       <c r="O97">
-        <v>-142.0017476731149</v>
+        <v>-144.3265002802003</v>
       </c>
       <c r="P97">
-        <v>-534.1970507702897</v>
+        <v>-542.9425486731348</v>
       </c>
       <c r="Q97">
-        <v>-250.2970507702897</v>
+        <v>-259.0425486731348</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5351518071641589</v>
+        <v>0.6574897589551988</v>
       </c>
       <c r="T97">
-        <v>8.251174482168242</v>
+        <v>10.31396810271031</v>
       </c>
       <c r="U97">
         <v>0.2476732333250682</v>
       </c>
       <c r="V97">
-        <v>0.07497548205223567</v>
+        <v>0.0741944874475249</v>
       </c>
       <c r="W97">
-        <v>0.2291038132650854</v>
+        <v>0.2292972447240435</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3570261050106461</v>
+        <v>0.3533070830834519</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2464249452932897</v>
+        <v>0.2484436776265404</v>
       </c>
       <c r="C98">
-        <v>-2606.833414348064</v>
+        <v>-2663.618251717701</v>
       </c>
       <c r="D98">
-        <v>1651.278585651936</v>
+        <v>1639.190748282299</v>
       </c>
       <c r="E98">
-        <v>1386.911999999999</v>
+        <v>1431.608999999999</v>
       </c>
       <c r="F98">
-        <v>4290.911999999999</v>
+        <v>4335.608999999999</v>
       </c>
       <c r="G98">
         <v>32.8</v>
@@ -9329,37 +9329,37 @@
         <v>375.475</v>
       </c>
       <c r="M98">
-        <v>1062.744048953335</v>
+        <v>1073.814299463266</v>
       </c>
       <c r="N98">
-        <v>-687.2690489533348</v>
+        <v>-698.3392994632655</v>
       </c>
       <c r="O98">
-        <v>-144.3265002802003</v>
+        <v>-146.6512528872858</v>
       </c>
       <c r="P98">
-        <v>-542.9425486731345</v>
+        <v>-551.6880465759798</v>
       </c>
       <c r="Q98">
-        <v>-259.0425486731345</v>
+        <v>-267.7880465759798</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6574897589551971</v>
+        <v>0.8613863452735964</v>
       </c>
       <c r="T98">
-        <v>10.31396810271028</v>
+        <v>13.75195747028037</v>
       </c>
       <c r="U98">
         <v>0.2476732333250682</v>
       </c>
       <c r="V98">
-        <v>0.07419448744752491</v>
+        <v>0.07342959582435454</v>
       </c>
       <c r="W98">
-        <v>0.2292972447240435</v>
+        <v>0.2294866879054974</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3533070830834519</v>
+        <v>0.3496647420207359</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2484436776265404</v>
+        <v>0.2504624099597911</v>
       </c>
       <c r="C99">
-        <v>-2663.618251717701</v>
+        <v>-2720.227402226942</v>
       </c>
       <c r="D99">
-        <v>1639.190748282299</v>
+        <v>1627.278597773058</v>
       </c>
       <c r="E99">
-        <v>1431.608999999999</v>
+        <v>1476.306</v>
       </c>
       <c r="F99">
-        <v>4335.608999999999</v>
+        <v>4380.306</v>
       </c>
       <c r="G99">
         <v>32.8</v>
@@ -9411,37 +9411,37 @@
         <v>375.475</v>
       </c>
       <c r="M99">
-        <v>1073.814299463266</v>
+        <v>1084.884549973196</v>
       </c>
       <c r="N99">
-        <v>-698.3392994632655</v>
+        <v>-709.409549973196</v>
       </c>
       <c r="O99">
-        <v>-146.6512528872858</v>
+        <v>-148.9760054943712</v>
       </c>
       <c r="P99">
-        <v>-551.6880465759798</v>
+        <v>-560.4335444788248</v>
       </c>
       <c r="Q99">
-        <v>-267.7880465759798</v>
+        <v>-276.5335444788249</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8613863452735964</v>
+        <v>1.269179517910394</v>
       </c>
       <c r="T99">
-        <v>13.75195747028037</v>
+        <v>20.62793620542055</v>
       </c>
       <c r="U99">
         <v>0.2476732333250682</v>
       </c>
       <c r="V99">
-        <v>0.07342959582435454</v>
+        <v>0.07268031423431011</v>
       </c>
       <c r="W99">
-        <v>0.2294866879054974</v>
+        <v>0.2296722648995747</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3496647420207359</v>
+        <v>0.3460967344490958</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2504624099597911</v>
+        <v>0.2524811422930417</v>
       </c>
       <c r="C100">
-        <v>-2720.227402226942</v>
+        <v>-2776.664668440106</v>
       </c>
       <c r="D100">
-        <v>1627.278597773058</v>
+        <v>1615.538331559894</v>
       </c>
       <c r="E100">
-        <v>1476.306</v>
+        <v>1521.003</v>
       </c>
       <c r="F100">
-        <v>4380.306</v>
+        <v>4425.003</v>
       </c>
       <c r="G100">
         <v>32.8</v>
@@ -9493,37 +9493,37 @@
         <v>375.475</v>
       </c>
       <c r="M100">
-        <v>1084.884549973196</v>
+        <v>1095.954800483127</v>
       </c>
       <c r="N100">
-        <v>-709.409549973196</v>
+        <v>-720.4798004831267</v>
       </c>
       <c r="O100">
-        <v>-148.9760054943712</v>
+        <v>-151.3007581014566</v>
       </c>
       <c r="P100">
-        <v>-560.4335444788248</v>
+        <v>-569.1790423816701</v>
       </c>
       <c r="Q100">
-        <v>-276.5335444788249</v>
+        <v>-285.2790423816701</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.269179517910394</v>
+        <v>2.492559035820789</v>
       </c>
       <c r="T100">
-        <v>20.62793620542055</v>
+        <v>41.25587241084111</v>
       </c>
       <c r="U100">
         <v>0.2476732333250682</v>
       </c>
       <c r="V100">
-        <v>0.07268031423431011</v>
+        <v>0.07194616964608475</v>
       </c>
       <c r="W100">
-        <v>0.2296722648995747</v>
+        <v>0.2298540928634685</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3460967344490958</v>
+        <v>0.3426008078384988</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2524811422930417</v>
-      </c>
-      <c r="C101">
-        <v>-2776.664668440106</v>
-      </c>
-      <c r="D101">
-        <v>1615.538331559894</v>
-      </c>
-      <c r="E101">
-        <v>1521.003</v>
-      </c>
-      <c r="F101">
-        <v>4425.003</v>
-      </c>
-      <c r="G101">
-        <v>32.8</v>
-      </c>
-      <c r="H101">
-        <v>1565.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>659.375</v>
-      </c>
-      <c r="K101">
-        <v>283.9</v>
-      </c>
-      <c r="L101">
-        <v>375.475</v>
-      </c>
-      <c r="M101">
-        <v>1095.954800483127</v>
-      </c>
-      <c r="N101">
-        <v>-720.4798004831267</v>
-      </c>
-      <c r="O101">
-        <v>-151.3007581014566</v>
-      </c>
-      <c r="P101">
-        <v>-569.1790423816701</v>
-      </c>
-      <c r="Q101">
-        <v>-285.2790423816701</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.492559035820789</v>
-      </c>
-      <c r="T101">
-        <v>41.25587241084111</v>
-      </c>
-      <c r="U101">
-        <v>0.2476732333250682</v>
-      </c>
-      <c r="V101">
-        <v>0.07194616964608475</v>
-      </c>
-      <c r="W101">
-        <v>0.2298540928634685</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3426008078384988</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
